--- a/pipeline/names-accounts.xlsx
+++ b/pipeline/names-accounts.xlsx
@@ -52,12 +52,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EAF1FB"/>
+        <fgColor rgb="00E7F7F0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E7F7F0"/>
+        <fgColor rgb="00EAF1FB"/>
       </patternFill>
     </fill>
   </fills>
@@ -460,12 +460,12 @@
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
     <col width="44" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="62" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="26" customWidth="1" min="10" max="10"/>
   </cols>
@@ -595,24 +595,52 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Adaobi</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Chiwueze</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="2" t="inlineStr"/>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Bono Energy</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>HR Officer</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>Univ. of Lagos. Energy sector.</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>Adaobi Chiwueze</t>
         </is>
@@ -643,132 +671,132 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>Adreena</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>Perry</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>Bridgestone</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>HRBP, Retail Ops</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr"/>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr"/>
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>Provided</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr"/>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="H7" s="7" t="inlineStr"/>
+      <c r="I7" s="6" t="inlineStr">
         <is>
           <t>Supplied by Jess</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="J7" s="6" t="inlineStr">
         <is>
           <t>Adreena Perry</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>Adriana</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Assad</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>Cytek</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>Sr. HR Generalist</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr"/>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>Provided</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr"/>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="H8" s="7" t="inlineStr"/>
+      <c r="I8" s="6" t="inlineStr">
         <is>
           <t>Supplied by Jess</t>
         </is>
       </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="J8" s="6" t="inlineStr">
         <is>
           <t>Adriana Assad</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>Adrienne</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>Hoag</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>FIRMAN Power Equipment</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>HR Director</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr"/>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>Provided</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr"/>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="H9" s="7" t="inlineStr"/>
+      <c r="I9" s="6" t="inlineStr">
         <is>
           <t>Supplied by Jess</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="J9" s="6" t="inlineStr">
         <is>
           <t>Adrienne Hoag</t>
         </is>
@@ -823,44 +851,44 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>Alec</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>Verone</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>US Navy</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>Talent Management &amp; Recruitment</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr"/>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr"/>
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>Provided</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="H12" s="7" t="inlineStr"/>
+      <c r="I12" s="6" t="inlineStr">
         <is>
           <t>Supplied by Jess</t>
         </is>
       </c>
-      <c r="J12" s="4" t="inlineStr">
+      <c r="J12" s="6" t="inlineStr">
         <is>
           <t>Alec Verone</t>
         </is>
@@ -891,88 +919,88 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>Alex</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>Dutton</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>Sony Music Entertainment</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>Director, Talent Acquisition</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr"/>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>Provided</t>
         </is>
       </c>
-      <c r="H14" s="5" t="inlineStr"/>
-      <c r="I14" s="4" t="inlineStr">
+      <c r="H14" s="7" t="inlineStr"/>
+      <c r="I14" s="6" t="inlineStr">
         <is>
           <t>Supplied by Jess</t>
         </is>
       </c>
-      <c r="J14" s="4" t="inlineStr">
+      <c r="J14" s="6" t="inlineStr">
         <is>
           <t>Alex Dutton</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>Alexandra</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>McClarnon</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>Husqvarna Group</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>HRBP</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr"/>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>Provided</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr"/>
-      <c r="I15" s="4" t="inlineStr">
+      <c r="H15" s="7" t="inlineStr"/>
+      <c r="I15" s="6" t="inlineStr">
         <is>
           <t>Supplied by Jess</t>
         </is>
       </c>
-      <c r="J15" s="4" t="inlineStr">
+      <c r="J15" s="6" t="inlineStr">
         <is>
           <t>Alexandra McClarnon</t>
         </is>
@@ -1003,88 +1031,88 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>Alexus</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>Taylor</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>Foundation for Healthy St. Petersburg</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>HR Generalist</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E17" s="6" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr"/>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="F17" s="6" t="inlineStr"/>
+      <c r="G17" s="6" t="inlineStr">
         <is>
           <t>Provided</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="H17" s="7" t="inlineStr"/>
+      <c r="I17" s="6" t="inlineStr">
         <is>
           <t>Supplied by Jess</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="J17" s="6" t="inlineStr">
         <is>
           <t>Alexus Taylor</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>Alicia</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>Asbill</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>Forshaw, Inc.</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E18" s="6" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr"/>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="F18" s="6" t="inlineStr"/>
+      <c r="G18" s="6" t="inlineStr">
         <is>
           <t>Provided</t>
         </is>
       </c>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="4" t="inlineStr">
+      <c r="H18" s="7" t="inlineStr"/>
+      <c r="I18" s="6" t="inlineStr">
         <is>
           <t>Supplied by Jess</t>
         </is>
       </c>
-      <c r="J18" s="4" t="inlineStr">
+      <c r="J18" s="6" t="inlineStr">
         <is>
           <t>Alicia Asbill</t>
         </is>
@@ -1211,44 +1239,44 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>Alise</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>Faircloth</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>Twin Health</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D24" s="6" t="inlineStr">
         <is>
           <t>Benefits Manager</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="E24" s="6" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr"/>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="F24" s="6" t="inlineStr"/>
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>Provided</t>
         </is>
       </c>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="4" t="inlineStr">
+      <c r="H24" s="7" t="inlineStr"/>
+      <c r="I24" s="6" t="inlineStr">
         <is>
           <t>Supplied by Jess</t>
         </is>
       </c>
-      <c r="J24" s="4" t="inlineStr">
+      <c r="J24" s="6" t="inlineStr">
         <is>
           <t>Alise Faircloth</t>
         </is>
@@ -1279,44 +1307,44 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>Allison</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>Richards</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>Deckers Brands</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D26" s="6" t="inlineStr">
         <is>
           <t>Sr. Recruiter</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="E26" s="6" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr"/>
-      <c r="G26" s="4" t="inlineStr">
+      <c r="F26" s="6" t="inlineStr"/>
+      <c r="G26" s="6" t="inlineStr">
         <is>
           <t>Provided</t>
         </is>
       </c>
-      <c r="H26" s="5" t="inlineStr"/>
-      <c r="I26" s="4" t="inlineStr">
+      <c r="H26" s="7" t="inlineStr"/>
+      <c r="I26" s="6" t="inlineStr">
         <is>
           <t>Supplied by Jess</t>
         </is>
       </c>
-      <c r="J26" s="4" t="inlineStr">
+      <c r="J26" s="6" t="inlineStr">
         <is>
           <t>Allison Richards</t>
         </is>
@@ -1347,176 +1375,176 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>Alma</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>Bunch</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
         <is>
           <t>Hasa Pool</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D28" s="6" t="inlineStr">
         <is>
           <t>Director, HR</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="E28" s="6" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F28" s="4" t="inlineStr"/>
-      <c r="G28" s="4" t="inlineStr">
+      <c r="F28" s="6" t="inlineStr"/>
+      <c r="G28" s="6" t="inlineStr">
         <is>
           <t>Provided</t>
         </is>
       </c>
-      <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="4" t="inlineStr">
+      <c r="H28" s="7" t="inlineStr"/>
+      <c r="I28" s="6" t="inlineStr">
         <is>
           <t>Supplied by Jess</t>
         </is>
       </c>
-      <c r="J28" s="4" t="inlineStr">
+      <c r="J28" s="6" t="inlineStr">
         <is>
           <t>Alma Bunch</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>Alondria</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>Hamilton</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>Transco</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D29" s="6" t="inlineStr">
         <is>
           <t>Manager, HR</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="E29" s="6" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F29" s="4" t="inlineStr"/>
-      <c r="G29" s="4" t="inlineStr">
+      <c r="F29" s="6" t="inlineStr"/>
+      <c r="G29" s="6" t="inlineStr">
         <is>
           <t>Provided</t>
         </is>
       </c>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="4" t="inlineStr">
+      <c r="H29" s="7" t="inlineStr"/>
+      <c r="I29" s="6" t="inlineStr">
         <is>
           <t>Supplied by Jess</t>
         </is>
       </c>
-      <c r="J29" s="4" t="inlineStr">
+      <c r="J29" s="6" t="inlineStr">
         <is>
           <t>Alondria Hamilton</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>Alphy</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>Jurarim</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>EFG Companies</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D30" s="6" t="inlineStr">
         <is>
           <t>Sr. Director, Financial Planning &amp; Business Operations</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="E30" s="6" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr"/>
-      <c r="G30" s="4" t="inlineStr">
+      <c r="F30" s="6" t="inlineStr"/>
+      <c r="G30" s="6" t="inlineStr">
         <is>
           <t>Provided</t>
         </is>
       </c>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="4" t="inlineStr">
+      <c r="H30" s="7" t="inlineStr"/>
+      <c r="I30" s="6" t="inlineStr">
         <is>
           <t>Supplied by Jess</t>
         </is>
       </c>
-      <c r="J30" s="4" t="inlineStr">
+      <c r="J30" s="6" t="inlineStr">
         <is>
           <t>Alphy Jurarim</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>Althea</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>Battle</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>American Family Insurance</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D31" s="6" t="inlineStr">
         <is>
           <t>Lead HRBP</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="E31" s="6" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr"/>
-      <c r="G31" s="4" t="inlineStr">
+      <c r="F31" s="6" t="inlineStr"/>
+      <c r="G31" s="6" t="inlineStr">
         <is>
           <t>Provided</t>
         </is>
       </c>
-      <c r="H31" s="5" t="inlineStr"/>
-      <c r="I31" s="4" t="inlineStr">
+      <c r="H31" s="7" t="inlineStr"/>
+      <c r="I31" s="6" t="inlineStr">
         <is>
           <t>Supplied by Jess</t>
         </is>
       </c>
-      <c r="J31" s="4" t="inlineStr">
+      <c r="J31" s="6" t="inlineStr">
         <is>
           <t>Althea Battle</t>
         </is>
@@ -1619,24 +1647,52 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>Amanda</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>Bebernitz</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr"/>
-      <c r="D36" s="2" t="inlineStr"/>
-      <c r="E36" s="2" t="inlineStr"/>
-      <c r="F36" s="2" t="inlineStr"/>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="3" t="inlineStr"/>
-      <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>Perinton Schools</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>Office Clerk</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>Perinton, NY</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>HR background: Director of Onboarding at Northwestern Mutual; HR Asst, Harter Secrest &amp; Emery. Current role is not HR.</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
         <is>
           <t>Amanda Bebernitz</t>
         </is>
@@ -1667,44 +1723,44 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>Amanda</t>
         </is>
       </c>
-      <c r="B38" s="4" t="inlineStr">
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>Floyd-Pittman</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t>Reserv</t>
         </is>
       </c>
-      <c r="D38" s="4" t="inlineStr">
+      <c r="D38" s="6" t="inlineStr">
         <is>
           <t>People Operations Business Partner</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr">
+      <c r="E38" s="6" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F38" s="4" t="inlineStr"/>
-      <c r="G38" s="4" t="inlineStr">
+      <c r="F38" s="6" t="inlineStr"/>
+      <c r="G38" s="6" t="inlineStr">
         <is>
           <t>Provided</t>
         </is>
       </c>
-      <c r="H38" s="5" t="inlineStr"/>
-      <c r="I38" s="4" t="inlineStr">
+      <c r="H38" s="7" t="inlineStr"/>
+      <c r="I38" s="6" t="inlineStr">
         <is>
           <t>Supplied by Jess</t>
         </is>
       </c>
-      <c r="J38" s="4" t="inlineStr">
+      <c r="J38" s="6" t="inlineStr">
         <is>
           <t>Amanda Floyd-Pittman</t>
         </is>
@@ -1735,176 +1791,176 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>Amanda</t>
         </is>
       </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>Goodyear</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C40" s="6" t="inlineStr">
         <is>
           <t>Karsten Group</t>
         </is>
       </c>
-      <c r="D40" s="4" t="inlineStr">
+      <c r="D40" s="6" t="inlineStr">
         <is>
           <t>HR Coordinator</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
+      <c r="E40" s="6" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F40" s="4" t="inlineStr"/>
-      <c r="G40" s="4" t="inlineStr">
+      <c r="F40" s="6" t="inlineStr"/>
+      <c r="G40" s="6" t="inlineStr">
         <is>
           <t>Provided</t>
         </is>
       </c>
-      <c r="H40" s="5" t="inlineStr"/>
-      <c r="I40" s="4" t="inlineStr">
+      <c r="H40" s="7" t="inlineStr"/>
+      <c r="I40" s="6" t="inlineStr">
         <is>
           <t>Supplied by Jess</t>
         </is>
       </c>
-      <c r="J40" s="4" t="inlineStr">
+      <c r="J40" s="6" t="inlineStr">
         <is>
           <t>Amanda Goodyear</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+      <c r="A41" s="6" t="inlineStr">
         <is>
           <t>Amanda</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B41" s="6" t="inlineStr">
         <is>
           <t>Hunsaker</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C41" s="6" t="inlineStr">
         <is>
           <t>Mertec Engineering</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="D41" s="6" t="inlineStr">
         <is>
           <t>HR, Benefits &amp; Payroll</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
+      <c r="E41" s="6" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F41" s="4" t="inlineStr"/>
-      <c r="G41" s="4" t="inlineStr">
+      <c r="F41" s="6" t="inlineStr"/>
+      <c r="G41" s="6" t="inlineStr">
         <is>
           <t>Provided</t>
         </is>
       </c>
-      <c r="H41" s="5" t="inlineStr"/>
-      <c r="I41" s="4" t="inlineStr">
+      <c r="H41" s="7" t="inlineStr"/>
+      <c r="I41" s="6" t="inlineStr">
         <is>
           <t>Supplied by Jess</t>
         </is>
       </c>
-      <c r="J41" s="4" t="inlineStr">
+      <c r="J41" s="6" t="inlineStr">
         <is>
           <t>Amanda Hunsaker</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+      <c r="A42" s="6" t="inlineStr">
         <is>
           <t>Amanda</t>
         </is>
       </c>
-      <c r="B42" s="4" t="inlineStr">
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>Livingstone</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="C42" s="6" t="inlineStr">
         <is>
           <t>Fearless! Hudson Valley</t>
         </is>
       </c>
-      <c r="D42" s="4" t="inlineStr">
+      <c r="D42" s="6" t="inlineStr">
         <is>
           <t>Director, HR</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr">
+      <c r="E42" s="6" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F42" s="4" t="inlineStr"/>
-      <c r="G42" s="4" t="inlineStr">
+      <c r="F42" s="6" t="inlineStr"/>
+      <c r="G42" s="6" t="inlineStr">
         <is>
           <t>Provided</t>
         </is>
       </c>
-      <c r="H42" s="5" t="inlineStr"/>
-      <c r="I42" s="4" t="inlineStr">
+      <c r="H42" s="7" t="inlineStr"/>
+      <c r="I42" s="6" t="inlineStr">
         <is>
           <t>Supplied by Jess</t>
         </is>
       </c>
-      <c r="J42" s="4" t="inlineStr">
+      <c r="J42" s="6" t="inlineStr">
         <is>
           <t>Amanda Livingstone</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>Amanda</t>
         </is>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B43" s="6" t="inlineStr">
         <is>
           <t>Pancho</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C43" s="6" t="inlineStr">
         <is>
           <t>Universal Audio</t>
         </is>
       </c>
-      <c r="D43" s="4" t="inlineStr">
+      <c r="D43" s="6" t="inlineStr">
         <is>
           <t>HR Rep &amp; Events Coordinator</t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr">
+      <c r="E43" s="6" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F43" s="4" t="inlineStr"/>
-      <c r="G43" s="4" t="inlineStr">
+      <c r="F43" s="6" t="inlineStr"/>
+      <c r="G43" s="6" t="inlineStr">
         <is>
           <t>Provided</t>
         </is>
       </c>
-      <c r="H43" s="5" t="inlineStr"/>
-      <c r="I43" s="4" t="inlineStr">
+      <c r="H43" s="7" t="inlineStr"/>
+      <c r="I43" s="6" t="inlineStr">
         <is>
           <t>Supplied by Jess</t>
         </is>
       </c>
-      <c r="J43" s="4" t="inlineStr">
+      <c r="J43" s="6" t="inlineStr">
         <is>
           <t>Amanda Pancho</t>
         </is>
@@ -1959,88 +2015,88 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="inlineStr">
+      <c r="A46" s="6" t="inlineStr">
         <is>
           <t>Amber</t>
         </is>
       </c>
-      <c r="B46" s="4" t="inlineStr">
+      <c r="B46" s="6" t="inlineStr">
         <is>
           <t>Freitas</t>
         </is>
       </c>
-      <c r="C46" s="4" t="inlineStr">
+      <c r="C46" s="6" t="inlineStr">
         <is>
           <t>19six Architects</t>
         </is>
       </c>
-      <c r="D46" s="4" t="inlineStr">
+      <c r="D46" s="6" t="inlineStr">
         <is>
           <t>Director, HR</t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr">
+      <c r="E46" s="6" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F46" s="4" t="inlineStr"/>
-      <c r="G46" s="4" t="inlineStr">
+      <c r="F46" s="6" t="inlineStr"/>
+      <c r="G46" s="6" t="inlineStr">
         <is>
           <t>Provided</t>
         </is>
       </c>
-      <c r="H46" s="5" t="inlineStr"/>
-      <c r="I46" s="4" t="inlineStr">
+      <c r="H46" s="7" t="inlineStr"/>
+      <c r="I46" s="6" t="inlineStr">
         <is>
           <t>Supplied by Jess</t>
         </is>
       </c>
-      <c r="J46" s="4" t="inlineStr">
+      <c r="J46" s="6" t="inlineStr">
         <is>
           <t>Amber Freitas</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="inlineStr">
+      <c r="A47" s="6" t="inlineStr">
         <is>
           <t>Amber</t>
         </is>
       </c>
-      <c r="B47" s="4" t="inlineStr">
+      <c r="B47" s="6" t="inlineStr">
         <is>
           <t>Palomino</t>
         </is>
       </c>
-      <c r="C47" s="4" t="inlineStr">
+      <c r="C47" s="6" t="inlineStr">
         <is>
           <t>Pioneer Programs</t>
         </is>
       </c>
-      <c r="D47" s="4" t="inlineStr">
+      <c r="D47" s="6" t="inlineStr">
         <is>
           <t>Human Resources Director</t>
         </is>
       </c>
-      <c r="E47" s="4" t="inlineStr">
+      <c r="E47" s="6" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F47" s="4" t="inlineStr"/>
-      <c r="G47" s="4" t="inlineStr">
+      <c r="F47" s="6" t="inlineStr"/>
+      <c r="G47" s="6" t="inlineStr">
         <is>
           <t>Provided</t>
         </is>
       </c>
-      <c r="H47" s="5" t="inlineStr"/>
-      <c r="I47" s="4" t="inlineStr">
+      <c r="H47" s="7" t="inlineStr"/>
+      <c r="I47" s="6" t="inlineStr">
         <is>
           <t>Supplied by Jess</t>
         </is>
       </c>
-      <c r="J47" s="4" t="inlineStr">
+      <c r="J47" s="6" t="inlineStr">
         <is>
           <t>Amber Palomino</t>
         </is>
@@ -2071,44 +2127,44 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="inlineStr">
+      <c r="A49" s="6" t="inlineStr">
         <is>
           <t>Amy</t>
         </is>
       </c>
-      <c r="B49" s="4" t="inlineStr">
+      <c r="B49" s="6" t="inlineStr">
         <is>
           <t>Myers-Meeker</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="C49" s="6" t="inlineStr">
         <is>
           <t>MyUSA Credit Union</t>
         </is>
       </c>
-      <c r="D49" s="4" t="inlineStr">
+      <c r="D49" s="6" t="inlineStr">
         <is>
           <t>HR Manager</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr">
+      <c r="E49" s="6" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F49" s="4" t="inlineStr"/>
-      <c r="G49" s="4" t="inlineStr">
+      <c r="F49" s="6" t="inlineStr"/>
+      <c r="G49" s="6" t="inlineStr">
         <is>
           <t>Provided</t>
         </is>
       </c>
-      <c r="H49" s="5" t="inlineStr"/>
-      <c r="I49" s="4" t="inlineStr">
+      <c r="H49" s="7" t="inlineStr"/>
+      <c r="I49" s="6" t="inlineStr">
         <is>
           <t>Supplied by Jess</t>
         </is>
       </c>
-      <c r="J49" s="4" t="inlineStr">
+      <c r="J49" s="6" t="inlineStr">
         <is>
           <t>Amy Myers-Meeker</t>
         </is>
@@ -2211,44 +2267,44 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="inlineStr">
+      <c r="A54" s="6" t="inlineStr">
         <is>
           <t>Andrea</t>
         </is>
       </c>
-      <c r="B54" s="4" t="inlineStr">
+      <c r="B54" s="6" t="inlineStr">
         <is>
           <t>Albaugh</t>
         </is>
       </c>
-      <c r="C54" s="4" t="inlineStr">
+      <c r="C54" s="6" t="inlineStr">
         <is>
           <t>Sawdey Solution Services</t>
         </is>
       </c>
-      <c r="D54" s="4" t="inlineStr">
+      <c r="D54" s="6" t="inlineStr">
         <is>
           <t>Director, HR</t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr">
+      <c r="E54" s="6" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F54" s="4" t="inlineStr"/>
-      <c r="G54" s="4" t="inlineStr">
+      <c r="F54" s="6" t="inlineStr"/>
+      <c r="G54" s="6" t="inlineStr">
         <is>
           <t>Provided</t>
         </is>
       </c>
-      <c r="H54" s="5" t="inlineStr"/>
-      <c r="I54" s="4" t="inlineStr">
+      <c r="H54" s="7" t="inlineStr"/>
+      <c r="I54" s="6" t="inlineStr">
         <is>
           <t>Supplied by Jess</t>
         </is>
       </c>
-      <c r="J54" s="4" t="inlineStr">
+      <c r="J54" s="6" t="inlineStr">
         <is>
           <t>Andrea Albaugh</t>
         </is>
@@ -2303,176 +2359,176 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="4" t="inlineStr">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t>Andrea</t>
         </is>
       </c>
-      <c r="B57" s="4" t="inlineStr">
+      <c r="B57" s="6" t="inlineStr">
         <is>
           <t>Stelpflug</t>
         </is>
       </c>
-      <c r="C57" s="4" t="inlineStr">
+      <c r="C57" s="6" t="inlineStr">
         <is>
           <t>UW Health</t>
         </is>
       </c>
-      <c r="D57" s="4" t="inlineStr">
+      <c r="D57" s="6" t="inlineStr">
         <is>
           <t>Employee Relations Consultant</t>
         </is>
       </c>
-      <c r="E57" s="4" t="inlineStr">
+      <c r="E57" s="6" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F57" s="4" t="inlineStr"/>
-      <c r="G57" s="4" t="inlineStr">
+      <c r="F57" s="6" t="inlineStr"/>
+      <c r="G57" s="6" t="inlineStr">
         <is>
           <t>Provided</t>
         </is>
       </c>
-      <c r="H57" s="5" t="inlineStr"/>
-      <c r="I57" s="4" t="inlineStr">
+      <c r="H57" s="7" t="inlineStr"/>
+      <c r="I57" s="6" t="inlineStr">
         <is>
           <t>Supplied by Jess</t>
         </is>
       </c>
-      <c r="J57" s="4" t="inlineStr">
+      <c r="J57" s="6" t="inlineStr">
         <is>
           <t>Andrea Stelpflug</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="4" t="inlineStr">
+      <c r="A58" s="6" t="inlineStr">
         <is>
           <t>Andrea</t>
         </is>
       </c>
-      <c r="B58" s="4" t="inlineStr">
+      <c r="B58" s="6" t="inlineStr">
         <is>
           <t>Vela</t>
         </is>
       </c>
-      <c r="C58" s="4" t="inlineStr">
+      <c r="C58" s="6" t="inlineStr">
         <is>
           <t>BMO</t>
         </is>
       </c>
-      <c r="D58" s="4" t="inlineStr">
+      <c r="D58" s="6" t="inlineStr">
         <is>
           <t>US Benefits Advisor</t>
         </is>
       </c>
-      <c r="E58" s="4" t="inlineStr">
+      <c r="E58" s="6" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F58" s="4" t="inlineStr"/>
-      <c r="G58" s="4" t="inlineStr">
+      <c r="F58" s="6" t="inlineStr"/>
+      <c r="G58" s="6" t="inlineStr">
         <is>
           <t>Provided</t>
         </is>
       </c>
-      <c r="H58" s="5" t="inlineStr"/>
-      <c r="I58" s="4" t="inlineStr">
+      <c r="H58" s="7" t="inlineStr"/>
+      <c r="I58" s="6" t="inlineStr">
         <is>
           <t>Supplied by Jess</t>
         </is>
       </c>
-      <c r="J58" s="4" t="inlineStr">
+      <c r="J58" s="6" t="inlineStr">
         <is>
           <t>Andrea Vela</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="inlineStr">
+      <c r="A59" s="6" t="inlineStr">
         <is>
           <t>Andrew</t>
         </is>
       </c>
-      <c r="B59" s="4" t="inlineStr">
+      <c r="B59" s="6" t="inlineStr">
         <is>
           <t>Beach</t>
         </is>
       </c>
-      <c r="C59" s="4" t="inlineStr">
+      <c r="C59" s="6" t="inlineStr">
         <is>
           <t>IQVIA</t>
         </is>
       </c>
-      <c r="D59" s="4" t="inlineStr">
+      <c r="D59" s="6" t="inlineStr">
         <is>
           <t>Global Sr. HRBP</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr">
+      <c r="E59" s="6" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F59" s="4" t="inlineStr"/>
-      <c r="G59" s="4" t="inlineStr">
+      <c r="F59" s="6" t="inlineStr"/>
+      <c r="G59" s="6" t="inlineStr">
         <is>
           <t>Provided</t>
         </is>
       </c>
-      <c r="H59" s="5" t="inlineStr"/>
-      <c r="I59" s="4" t="inlineStr">
+      <c r="H59" s="7" t="inlineStr"/>
+      <c r="I59" s="6" t="inlineStr">
         <is>
           <t>Supplied by Jess</t>
         </is>
       </c>
-      <c r="J59" s="4" t="inlineStr">
+      <c r="J59" s="6" t="inlineStr">
         <is>
           <t>Andrew Beach</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="4" t="inlineStr">
+      <c r="A60" s="6" t="inlineStr">
         <is>
           <t>Andrew</t>
         </is>
       </c>
-      <c r="B60" s="4" t="inlineStr">
+      <c r="B60" s="6" t="inlineStr">
         <is>
           <t>Creath</t>
         </is>
       </c>
-      <c r="C60" s="4" t="inlineStr">
+      <c r="C60" s="6" t="inlineStr">
         <is>
           <t>GardaWorld</t>
         </is>
       </c>
-      <c r="D60" s="4" t="inlineStr">
+      <c r="D60" s="6" t="inlineStr">
         <is>
           <t>HR Generalist</t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr">
+      <c r="E60" s="6" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F60" s="4" t="inlineStr"/>
-      <c r="G60" s="4" t="inlineStr">
+      <c r="F60" s="6" t="inlineStr"/>
+      <c r="G60" s="6" t="inlineStr">
         <is>
           <t>Provided</t>
         </is>
       </c>
-      <c r="H60" s="5" t="inlineStr"/>
-      <c r="I60" s="4" t="inlineStr">
+      <c r="H60" s="7" t="inlineStr"/>
+      <c r="I60" s="6" t="inlineStr">
         <is>
           <t>Supplied by Jess</t>
         </is>
       </c>
-      <c r="J60" s="4" t="inlineStr">
+      <c r="J60" s="6" t="inlineStr">
         <is>
           <t>Andrew Creath</t>
         </is>
@@ -2503,88 +2559,88 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="4" t="inlineStr">
+      <c r="A62" s="6" t="inlineStr">
         <is>
           <t>Andy</t>
         </is>
       </c>
-      <c r="B62" s="4" t="inlineStr">
+      <c r="B62" s="6" t="inlineStr">
         <is>
           <t>Khaliqi</t>
         </is>
       </c>
-      <c r="C62" s="4" t="inlineStr">
+      <c r="C62" s="6" t="inlineStr">
         <is>
           <t>American College of Education</t>
         </is>
       </c>
-      <c r="D62" s="4" t="inlineStr">
+      <c r="D62" s="6" t="inlineStr">
         <is>
           <t>HR Manager</t>
         </is>
       </c>
-      <c r="E62" s="4" t="inlineStr">
+      <c r="E62" s="6" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F62" s="4" t="inlineStr"/>
-      <c r="G62" s="4" t="inlineStr">
+      <c r="F62" s="6" t="inlineStr"/>
+      <c r="G62" s="6" t="inlineStr">
         <is>
           <t>Provided</t>
         </is>
       </c>
-      <c r="H62" s="5" t="inlineStr"/>
-      <c r="I62" s="4" t="inlineStr">
+      <c r="H62" s="7" t="inlineStr"/>
+      <c r="I62" s="6" t="inlineStr">
         <is>
           <t>Supplied by Jess</t>
         </is>
       </c>
-      <c r="J62" s="4" t="inlineStr">
+      <c r="J62" s="6" t="inlineStr">
         <is>
           <t>Andy Khaliqi</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="4" t="inlineStr">
+      <c r="A63" s="6" t="inlineStr">
         <is>
           <t>Anetra</t>
         </is>
       </c>
-      <c r="B63" s="4" t="inlineStr">
+      <c r="B63" s="6" t="inlineStr">
         <is>
           <t>Howard</t>
         </is>
       </c>
-      <c r="C63" s="4" t="inlineStr">
+      <c r="C63" s="6" t="inlineStr">
         <is>
           <t>Ochsner LSU Health Shreveport</t>
         </is>
       </c>
-      <c r="D63" s="4" t="inlineStr">
+      <c r="D63" s="6" t="inlineStr">
         <is>
           <t>Employee Relations Consultant</t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr">
+      <c r="E63" s="6" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F63" s="4" t="inlineStr"/>
-      <c r="G63" s="4" t="inlineStr">
+      <c r="F63" s="6" t="inlineStr"/>
+      <c r="G63" s="6" t="inlineStr">
         <is>
           <t>Provided</t>
         </is>
       </c>
-      <c r="H63" s="5" t="inlineStr"/>
-      <c r="I63" s="4" t="inlineStr">
+      <c r="H63" s="7" t="inlineStr"/>
+      <c r="I63" s="6" t="inlineStr">
         <is>
           <t>Supplied by Jess</t>
         </is>
       </c>
-      <c r="J63" s="4" t="inlineStr">
+      <c r="J63" s="6" t="inlineStr">
         <is>
           <t>Anetra Howard</t>
         </is>
@@ -2615,132 +2671,132 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="4" t="inlineStr">
+      <c r="A65" s="6" t="inlineStr">
         <is>
           <t>Angela</t>
         </is>
       </c>
-      <c r="B65" s="4" t="inlineStr">
+      <c r="B65" s="6" t="inlineStr">
         <is>
           <t>Doney</t>
         </is>
       </c>
-      <c r="C65" s="4" t="inlineStr">
+      <c r="C65" s="6" t="inlineStr">
         <is>
           <t>Archdiocese of Milwaukee</t>
         </is>
       </c>
-      <c r="D65" s="4" t="inlineStr">
+      <c r="D65" s="6" t="inlineStr">
         <is>
           <t>HR Coordinator</t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr">
+      <c r="E65" s="6" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F65" s="4" t="inlineStr"/>
-      <c r="G65" s="4" t="inlineStr">
+      <c r="F65" s="6" t="inlineStr"/>
+      <c r="G65" s="6" t="inlineStr">
         <is>
           <t>Provided</t>
         </is>
       </c>
-      <c r="H65" s="5" t="inlineStr"/>
-      <c r="I65" s="4" t="inlineStr">
+      <c r="H65" s="7" t="inlineStr"/>
+      <c r="I65" s="6" t="inlineStr">
         <is>
           <t>Supplied by Jess</t>
         </is>
       </c>
-      <c r="J65" s="4" t="inlineStr">
+      <c r="J65" s="6" t="inlineStr">
         <is>
           <t>Angela Doney</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="4" t="inlineStr">
+      <c r="A66" s="6" t="inlineStr">
         <is>
           <t>Angela</t>
         </is>
       </c>
-      <c r="B66" s="4" t="inlineStr">
+      <c r="B66" s="6" t="inlineStr">
         <is>
           <t>Malakiman</t>
         </is>
       </c>
-      <c r="C66" s="4" t="inlineStr">
+      <c r="C66" s="6" t="inlineStr">
         <is>
           <t>Stars Behavioral Group</t>
         </is>
       </c>
-      <c r="D66" s="4" t="inlineStr">
+      <c r="D66" s="6" t="inlineStr">
         <is>
           <t>HR Generalist</t>
         </is>
       </c>
-      <c r="E66" s="4" t="inlineStr">
+      <c r="E66" s="6" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F66" s="4" t="inlineStr"/>
-      <c r="G66" s="4" t="inlineStr">
+      <c r="F66" s="6" t="inlineStr"/>
+      <c r="G66" s="6" t="inlineStr">
         <is>
           <t>Provided</t>
         </is>
       </c>
-      <c r="H66" s="5" t="inlineStr"/>
-      <c r="I66" s="4" t="inlineStr">
+      <c r="H66" s="7" t="inlineStr"/>
+      <c r="I66" s="6" t="inlineStr">
         <is>
           <t>Supplied by Jess</t>
         </is>
       </c>
-      <c r="J66" s="4" t="inlineStr">
+      <c r="J66" s="6" t="inlineStr">
         <is>
           <t>Angela Malakiman</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="4" t="inlineStr">
+      <c r="A67" s="6" t="inlineStr">
         <is>
           <t>Angela</t>
         </is>
       </c>
-      <c r="B67" s="4" t="inlineStr">
+      <c r="B67" s="6" t="inlineStr">
         <is>
           <t>Mazik-Black</t>
         </is>
       </c>
-      <c r="C67" s="4" t="inlineStr">
+      <c r="C67" s="6" t="inlineStr">
         <is>
           <t>Ashley Global Retail</t>
         </is>
       </c>
-      <c r="D67" s="4" t="inlineStr">
+      <c r="D67" s="6" t="inlineStr">
         <is>
           <t>VP, Global HR</t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr">
+      <c r="E67" s="6" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F67" s="4" t="inlineStr"/>
-      <c r="G67" s="4" t="inlineStr">
+      <c r="F67" s="6" t="inlineStr"/>
+      <c r="G67" s="6" t="inlineStr">
         <is>
           <t>Provided</t>
         </is>
       </c>
-      <c r="H67" s="5" t="inlineStr"/>
-      <c r="I67" s="4" t="inlineStr">
+      <c r="H67" s="7" t="inlineStr"/>
+      <c r="I67" s="6" t="inlineStr">
         <is>
           <t>Supplied by Jess</t>
         </is>
       </c>
-      <c r="J67" s="4" t="inlineStr">
+      <c r="J67" s="6" t="inlineStr">
         <is>
           <t>Angela Mazik-Black</t>
         </is>
@@ -2795,176 +2851,176 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="4" t="inlineStr">
+      <c r="A70" s="6" t="inlineStr">
         <is>
           <t>Angelia</t>
         </is>
       </c>
-      <c r="B70" s="4" t="inlineStr">
+      <c r="B70" s="6" t="inlineStr">
         <is>
           <t>Couch</t>
         </is>
       </c>
-      <c r="C70" s="4" t="inlineStr">
+      <c r="C70" s="6" t="inlineStr">
         <is>
           <t>ICE</t>
         </is>
       </c>
-      <c r="D70" s="4" t="inlineStr">
+      <c r="D70" s="6" t="inlineStr">
         <is>
           <t>HR Programs &amp; Services Analyst</t>
         </is>
       </c>
-      <c r="E70" s="4" t="inlineStr">
+      <c r="E70" s="6" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F70" s="4" t="inlineStr"/>
-      <c r="G70" s="4" t="inlineStr">
+      <c r="F70" s="6" t="inlineStr"/>
+      <c r="G70" s="6" t="inlineStr">
         <is>
           <t>Provided</t>
         </is>
       </c>
-      <c r="H70" s="5" t="inlineStr"/>
-      <c r="I70" s="4" t="inlineStr">
+      <c r="H70" s="7" t="inlineStr"/>
+      <c r="I70" s="6" t="inlineStr">
         <is>
           <t>Supplied by Jess</t>
         </is>
       </c>
-      <c r="J70" s="4" t="inlineStr">
+      <c r="J70" s="6" t="inlineStr">
         <is>
           <t>Angelia Couch</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="4" t="inlineStr">
+      <c r="A71" s="6" t="inlineStr">
         <is>
           <t>Angelica</t>
         </is>
       </c>
-      <c r="B71" s="4" t="inlineStr">
+      <c r="B71" s="6" t="inlineStr">
         <is>
           <t>Riepe</t>
         </is>
       </c>
-      <c r="C71" s="4" t="inlineStr">
+      <c r="C71" s="6" t="inlineStr">
         <is>
           <t>American College of Surgeons</t>
         </is>
       </c>
-      <c r="D71" s="4" t="inlineStr">
+      <c r="D71" s="6" t="inlineStr">
         <is>
           <t>AVP, HR</t>
         </is>
       </c>
-      <c r="E71" s="4" t="inlineStr">
+      <c r="E71" s="6" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F71" s="4" t="inlineStr"/>
-      <c r="G71" s="4" t="inlineStr">
+      <c r="F71" s="6" t="inlineStr"/>
+      <c r="G71" s="6" t="inlineStr">
         <is>
           <t>Provided</t>
         </is>
       </c>
-      <c r="H71" s="5" t="inlineStr"/>
-      <c r="I71" s="4" t="inlineStr">
+      <c r="H71" s="7" t="inlineStr"/>
+      <c r="I71" s="6" t="inlineStr">
         <is>
           <t>Supplied by Jess</t>
         </is>
       </c>
-      <c r="J71" s="4" t="inlineStr">
+      <c r="J71" s="6" t="inlineStr">
         <is>
           <t>Angelica Riepe</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="4" t="inlineStr">
+      <c r="A72" s="6" t="inlineStr">
         <is>
           <t>Anika</t>
         </is>
       </c>
-      <c r="B72" s="4" t="inlineStr">
+      <c r="B72" s="6" t="inlineStr">
         <is>
           <t>Cornelese</t>
         </is>
       </c>
-      <c r="C72" s="4" t="inlineStr">
+      <c r="C72" s="6" t="inlineStr">
         <is>
           <t>Encompass Health</t>
         </is>
       </c>
-      <c r="D72" s="4" t="inlineStr">
+      <c r="D72" s="6" t="inlineStr">
         <is>
           <t>HR Director</t>
         </is>
       </c>
-      <c r="E72" s="4" t="inlineStr">
+      <c r="E72" s="6" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F72" s="4" t="inlineStr"/>
-      <c r="G72" s="4" t="inlineStr">
+      <c r="F72" s="6" t="inlineStr"/>
+      <c r="G72" s="6" t="inlineStr">
         <is>
           <t>Provided</t>
         </is>
       </c>
-      <c r="H72" s="5" t="inlineStr"/>
-      <c r="I72" s="4" t="inlineStr">
+      <c r="H72" s="7" t="inlineStr"/>
+      <c r="I72" s="6" t="inlineStr">
         <is>
           <t>Supplied by Jess</t>
         </is>
       </c>
-      <c r="J72" s="4" t="inlineStr">
+      <c r="J72" s="6" t="inlineStr">
         <is>
           <t>Anika Cornelese</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="4" t="inlineStr">
+      <c r="A73" s="6" t="inlineStr">
         <is>
           <t>Anila</t>
         </is>
       </c>
-      <c r="B73" s="4" t="inlineStr">
+      <c r="B73" s="6" t="inlineStr">
         <is>
           <t>Mehdihassan</t>
         </is>
       </c>
-      <c r="C73" s="4" t="inlineStr">
+      <c r="C73" s="6" t="inlineStr">
         <is>
           <t>DTE Energy</t>
         </is>
       </c>
-      <c r="D73" s="4" t="inlineStr">
+      <c r="D73" s="6" t="inlineStr">
         <is>
           <t>Consultant - HR Client Relations</t>
         </is>
       </c>
-      <c r="E73" s="4" t="inlineStr">
+      <c r="E73" s="6" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F73" s="4" t="inlineStr"/>
-      <c r="G73" s="4" t="inlineStr">
+      <c r="F73" s="6" t="inlineStr"/>
+      <c r="G73" s="6" t="inlineStr">
         <is>
           <t>Provided</t>
         </is>
       </c>
-      <c r="H73" s="5" t="inlineStr"/>
-      <c r="I73" s="4" t="inlineStr">
+      <c r="H73" s="7" t="inlineStr"/>
+      <c r="I73" s="6" t="inlineStr">
         <is>
           <t>Supplied by Jess</t>
         </is>
       </c>
-      <c r="J73" s="4" t="inlineStr">
+      <c r="J73" s="6" t="inlineStr">
         <is>
           <t>Anila Mehdihassan</t>
         </is>
@@ -2995,44 +3051,44 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="4" t="inlineStr">
+      <c r="A75" s="6" t="inlineStr">
         <is>
           <t>Ann</t>
         </is>
       </c>
-      <c r="B75" s="4" t="inlineStr">
+      <c r="B75" s="6" t="inlineStr">
         <is>
           <t>Bakken</t>
         </is>
       </c>
-      <c r="C75" s="4" t="inlineStr">
+      <c r="C75" s="6" t="inlineStr">
         <is>
           <t>Springs Window Fashions</t>
         </is>
       </c>
-      <c r="D75" s="4" t="inlineStr">
+      <c r="D75" s="6" t="inlineStr">
         <is>
           <t>Benefits Manager</t>
         </is>
       </c>
-      <c r="E75" s="4" t="inlineStr">
+      <c r="E75" s="6" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F75" s="4" t="inlineStr"/>
-      <c r="G75" s="4" t="inlineStr">
+      <c r="F75" s="6" t="inlineStr"/>
+      <c r="G75" s="6" t="inlineStr">
         <is>
           <t>Provided</t>
         </is>
       </c>
-      <c r="H75" s="5" t="inlineStr"/>
-      <c r="I75" s="4" t="inlineStr">
+      <c r="H75" s="7" t="inlineStr"/>
+      <c r="I75" s="6" t="inlineStr">
         <is>
           <t>Supplied by Jess</t>
         </is>
       </c>
-      <c r="J75" s="4" t="inlineStr">
+      <c r="J75" s="6" t="inlineStr">
         <is>
           <t>Ann Bakken</t>
         </is>
@@ -3087,44 +3143,44 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="4" t="inlineStr">
+      <c r="A78" s="6" t="inlineStr">
         <is>
           <t>Anna</t>
         </is>
       </c>
-      <c r="B78" s="4" t="inlineStr">
+      <c r="B78" s="6" t="inlineStr">
         <is>
           <t>Anderson</t>
         </is>
       </c>
-      <c r="C78" s="4" t="inlineStr">
+      <c r="C78" s="6" t="inlineStr">
         <is>
           <t>Capital Group</t>
         </is>
       </c>
-      <c r="D78" s="4" t="inlineStr">
+      <c r="D78" s="6" t="inlineStr">
         <is>
           <t>Director, Talent Acquisition</t>
         </is>
       </c>
-      <c r="E78" s="4" t="inlineStr">
+      <c r="E78" s="6" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F78" s="4" t="inlineStr"/>
-      <c r="G78" s="4" t="inlineStr">
+      <c r="F78" s="6" t="inlineStr"/>
+      <c r="G78" s="6" t="inlineStr">
         <is>
           <t>Provided</t>
         </is>
       </c>
-      <c r="H78" s="5" t="inlineStr"/>
-      <c r="I78" s="4" t="inlineStr">
+      <c r="H78" s="7" t="inlineStr"/>
+      <c r="I78" s="6" t="inlineStr">
         <is>
           <t>Supplied by Jess</t>
         </is>
       </c>
-      <c r="J78" s="4" t="inlineStr">
+      <c r="J78" s="6" t="inlineStr">
         <is>
           <t>Anna Anderson</t>
         </is>
@@ -3155,44 +3211,44 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="4" t="inlineStr">
+      <c r="A80" s="6" t="inlineStr">
         <is>
           <t>Anna Maria</t>
         </is>
       </c>
-      <c r="B80" s="4" t="inlineStr">
+      <c r="B80" s="6" t="inlineStr">
         <is>
           <t>Scillia</t>
         </is>
       </c>
-      <c r="C80" s="4" t="inlineStr">
+      <c r="C80" s="6" t="inlineStr">
         <is>
           <t>Marchesini Group</t>
         </is>
       </c>
-      <c r="D80" s="4" t="inlineStr">
+      <c r="D80" s="6" t="inlineStr">
         <is>
           <t>Office Manager / HR Manager</t>
         </is>
       </c>
-      <c r="E80" s="4" t="inlineStr">
+      <c r="E80" s="6" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F80" s="4" t="inlineStr"/>
-      <c r="G80" s="4" t="inlineStr">
+      <c r="F80" s="6" t="inlineStr"/>
+      <c r="G80" s="6" t="inlineStr">
         <is>
           <t>Provided</t>
         </is>
       </c>
-      <c r="H80" s="5" t="inlineStr"/>
-      <c r="I80" s="4" t="inlineStr">
+      <c r="H80" s="7" t="inlineStr"/>
+      <c r="I80" s="6" t="inlineStr">
         <is>
           <t>Supplied by Jess</t>
         </is>
       </c>
-      <c r="J80" s="4" t="inlineStr">
+      <c r="J80" s="6" t="inlineStr">
         <is>
           <t>Anna Maria Scillia</t>
         </is>
@@ -3247,44 +3303,44 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="4" t="inlineStr">
+      <c r="A83" s="6" t="inlineStr">
         <is>
           <t>Annabelle</t>
         </is>
       </c>
-      <c r="B83" s="4" t="inlineStr">
+      <c r="B83" s="6" t="inlineStr">
         <is>
           <t>Baltierra</t>
         </is>
       </c>
-      <c r="C83" s="4" t="inlineStr">
+      <c r="C83" s="6" t="inlineStr">
         <is>
           <t>NACPA</t>
         </is>
       </c>
-      <c r="D83" s="4" t="inlineStr">
+      <c r="D83" s="6" t="inlineStr">
         <is>
           <t>Sr. Advisor, Consultant</t>
         </is>
       </c>
-      <c r="E83" s="4" t="inlineStr">
+      <c r="E83" s="6" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F83" s="4" t="inlineStr"/>
-      <c r="G83" s="4" t="inlineStr">
+      <c r="F83" s="6" t="inlineStr"/>
+      <c r="G83" s="6" t="inlineStr">
         <is>
           <t>Provided</t>
         </is>
       </c>
-      <c r="H83" s="5" t="inlineStr"/>
-      <c r="I83" s="4" t="inlineStr">
+      <c r="H83" s="7" t="inlineStr"/>
+      <c r="I83" s="6" t="inlineStr">
         <is>
           <t>Supplied by Jess</t>
         </is>
       </c>
-      <c r="J83" s="4" t="inlineStr">
+      <c r="J83" s="6" t="inlineStr">
         <is>
           <t>Annabelle Baltierra</t>
         </is>
@@ -3315,44 +3371,44 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="4" t="inlineStr">
+      <c r="A85" s="6" t="inlineStr">
         <is>
           <t>Anne</t>
         </is>
       </c>
-      <c r="B85" s="4" t="inlineStr">
+      <c r="B85" s="6" t="inlineStr">
         <is>
           <t>St. Vil</t>
         </is>
       </c>
-      <c r="C85" s="4" t="inlineStr">
+      <c r="C85" s="6" t="inlineStr">
         <is>
           <t>The Chronicle of Higher Education</t>
         </is>
       </c>
-      <c r="D85" s="4" t="inlineStr">
+      <c r="D85" s="6" t="inlineStr">
         <is>
           <t>Sr. Payroll Manager</t>
         </is>
       </c>
-      <c r="E85" s="4" t="inlineStr">
+      <c r="E85" s="6" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F85" s="4" t="inlineStr"/>
-      <c r="G85" s="4" t="inlineStr">
+      <c r="F85" s="6" t="inlineStr"/>
+      <c r="G85" s="6" t="inlineStr">
         <is>
           <t>Provided</t>
         </is>
       </c>
-      <c r="H85" s="5" t="inlineStr"/>
-      <c r="I85" s="4" t="inlineStr">
+      <c r="H85" s="7" t="inlineStr"/>
+      <c r="I85" s="6" t="inlineStr">
         <is>
           <t>Supplied by Jess</t>
         </is>
       </c>
-      <c r="J85" s="4" t="inlineStr">
+      <c r="J85" s="6" t="inlineStr">
         <is>
           <t>Anne St. Vil</t>
         </is>
@@ -3383,44 +3439,44 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="4" t="inlineStr">
+      <c r="A87" s="6" t="inlineStr">
         <is>
           <t>AnnMarie</t>
         </is>
       </c>
-      <c r="B87" s="4" t="inlineStr">
+      <c r="B87" s="6" t="inlineStr">
         <is>
           <t>Day</t>
         </is>
       </c>
-      <c r="C87" s="4" t="inlineStr">
+      <c r="C87" s="6" t="inlineStr">
         <is>
           <t>FLENDER Corp.</t>
         </is>
       </c>
-      <c r="D87" s="4" t="inlineStr">
+      <c r="D87" s="6" t="inlineStr">
         <is>
           <t>Country Head of HR</t>
         </is>
       </c>
-      <c r="E87" s="4" t="inlineStr">
+      <c r="E87" s="6" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F87" s="4" t="inlineStr"/>
-      <c r="G87" s="4" t="inlineStr">
+      <c r="F87" s="6" t="inlineStr"/>
+      <c r="G87" s="6" t="inlineStr">
         <is>
           <t>Provided</t>
         </is>
       </c>
-      <c r="H87" s="5" t="inlineStr"/>
-      <c r="I87" s="4" t="inlineStr">
+      <c r="H87" s="7" t="inlineStr"/>
+      <c r="I87" s="6" t="inlineStr">
         <is>
           <t>Supplied by Jess</t>
         </is>
       </c>
-      <c r="J87" s="4" t="inlineStr">
+      <c r="J87" s="6" t="inlineStr">
         <is>
           <t>AnnMarie Day</t>
         </is>
@@ -3475,44 +3531,44 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="4" t="inlineStr">
+      <c r="A90" s="6" t="inlineStr">
         <is>
           <t>April</t>
         </is>
       </c>
-      <c r="B90" s="4" t="inlineStr">
+      <c r="B90" s="6" t="inlineStr">
         <is>
           <t>Chen</t>
         </is>
       </c>
-      <c r="C90" s="4" t="inlineStr">
+      <c r="C90" s="6" t="inlineStr">
         <is>
           <t>Hyundai</t>
         </is>
       </c>
-      <c r="D90" s="4" t="inlineStr">
+      <c r="D90" s="6" t="inlineStr">
         <is>
           <t>Sr. Manager, HRBP</t>
         </is>
       </c>
-      <c r="E90" s="4" t="inlineStr">
+      <c r="E90" s="6" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F90" s="4" t="inlineStr"/>
-      <c r="G90" s="4" t="inlineStr">
+      <c r="F90" s="6" t="inlineStr"/>
+      <c r="G90" s="6" t="inlineStr">
         <is>
           <t>Provided</t>
         </is>
       </c>
-      <c r="H90" s="5" t="inlineStr"/>
-      <c r="I90" s="4" t="inlineStr">
+      <c r="H90" s="7" t="inlineStr"/>
+      <c r="I90" s="6" t="inlineStr">
         <is>
           <t>Supplied by Jess</t>
         </is>
       </c>
-      <c r="J90" s="4" t="inlineStr">
+      <c r="J90" s="6" t="inlineStr">
         <is>
           <t>April Chen</t>
         </is>
@@ -3567,44 +3623,44 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="4" t="inlineStr">
+      <c r="A93" s="6" t="inlineStr">
         <is>
           <t>April</t>
         </is>
       </c>
-      <c r="B93" s="4" t="inlineStr">
+      <c r="B93" s="6" t="inlineStr">
         <is>
           <t>Willyard</t>
         </is>
       </c>
-      <c r="C93" s="4" t="inlineStr">
+      <c r="C93" s="6" t="inlineStr">
         <is>
           <t>Precision Franchising</t>
         </is>
       </c>
-      <c r="D93" s="4" t="inlineStr">
+      <c r="D93" s="6" t="inlineStr">
         <is>
           <t>HR Manager</t>
         </is>
       </c>
-      <c r="E93" s="4" t="inlineStr">
+      <c r="E93" s="6" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F93" s="4" t="inlineStr"/>
-      <c r="G93" s="4" t="inlineStr">
+      <c r="F93" s="6" t="inlineStr"/>
+      <c r="G93" s="6" t="inlineStr">
         <is>
           <t>Provided</t>
         </is>
       </c>
-      <c r="H93" s="5" t="inlineStr"/>
-      <c r="I93" s="4" t="inlineStr">
+      <c r="H93" s="7" t="inlineStr"/>
+      <c r="I93" s="6" t="inlineStr">
         <is>
           <t>Supplied by Jess</t>
         </is>
       </c>
-      <c r="J93" s="4" t="inlineStr">
+      <c r="J93" s="6" t="inlineStr">
         <is>
           <t>April Willyard</t>
         </is>
@@ -3683,44 +3739,44 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+      <c r="A97" s="6" t="inlineStr">
         <is>
           <t>Ashley</t>
         </is>
       </c>
-      <c r="B97" s="4" t="inlineStr">
+      <c r="B97" s="6" t="inlineStr">
         <is>
           <t>McGree</t>
         </is>
       </c>
-      <c r="C97" s="4" t="inlineStr">
+      <c r="C97" s="6" t="inlineStr">
         <is>
           <t>Wisconsin Department of Admin</t>
         </is>
       </c>
-      <c r="D97" s="4" t="inlineStr">
+      <c r="D97" s="6" t="inlineStr">
         <is>
           <t>Sr. HR Specialist</t>
         </is>
       </c>
-      <c r="E97" s="4" t="inlineStr">
+      <c r="E97" s="6" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F97" s="4" t="inlineStr"/>
-      <c r="G97" s="4" t="inlineStr">
+      <c r="F97" s="6" t="inlineStr"/>
+      <c r="G97" s="6" t="inlineStr">
         <is>
           <t>Provided</t>
         </is>
       </c>
-      <c r="H97" s="5" t="inlineStr"/>
-      <c r="I97" s="4" t="inlineStr">
+      <c r="H97" s="7" t="inlineStr"/>
+      <c r="I97" s="6" t="inlineStr">
         <is>
           <t>Supplied by Jess</t>
         </is>
       </c>
-      <c r="J97" s="4" t="inlineStr">
+      <c r="J97" s="6" t="inlineStr">
         <is>
           <t>Ashley McGree</t>
         </is>
@@ -3775,44 +3831,44 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="4" t="inlineStr">
+      <c r="A100" s="6" t="inlineStr">
         <is>
           <t>Ayami</t>
         </is>
       </c>
-      <c r="B100" s="4" t="inlineStr">
+      <c r="B100" s="6" t="inlineStr">
         <is>
           <t>Norton</t>
         </is>
       </c>
-      <c r="C100" s="4" t="inlineStr">
+      <c r="C100" s="6" t="inlineStr">
         <is>
           <t>FIMER</t>
         </is>
       </c>
-      <c r="D100" s="4" t="inlineStr">
+      <c r="D100" s="6" t="inlineStr">
         <is>
           <t>Global HR Director</t>
         </is>
       </c>
-      <c r="E100" s="4" t="inlineStr">
+      <c r="E100" s="6" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F100" s="4" t="inlineStr"/>
-      <c r="G100" s="4" t="inlineStr">
+      <c r="F100" s="6" t="inlineStr"/>
+      <c r="G100" s="6" t="inlineStr">
         <is>
           <t>Provided</t>
         </is>
       </c>
-      <c r="H100" s="5" t="inlineStr"/>
-      <c r="I100" s="4" t="inlineStr">
+      <c r="H100" s="7" t="inlineStr"/>
+      <c r="I100" s="6" t="inlineStr">
         <is>
           <t>Supplied by Jess</t>
         </is>
       </c>
-      <c r="J100" s="4" t="inlineStr">
+      <c r="J100" s="6" t="inlineStr">
         <is>
           <t>Ayami Norton</t>
         </is>
@@ -3867,88 +3923,88 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="4" t="inlineStr">
+      <c r="A103" s="6" t="inlineStr">
         <is>
           <t>Bailey</t>
         </is>
       </c>
-      <c r="B103" s="4" t="inlineStr">
+      <c r="B103" s="6" t="inlineStr">
         <is>
           <t>Corbin</t>
         </is>
       </c>
-      <c r="C103" s="4" t="inlineStr">
+      <c r="C103" s="6" t="inlineStr">
         <is>
           <t>AIT Worldwide Logistics</t>
         </is>
       </c>
-      <c r="D103" s="4" t="inlineStr">
+      <c r="D103" s="6" t="inlineStr">
         <is>
           <t>Global Talent Program Manager</t>
         </is>
       </c>
-      <c r="E103" s="4" t="inlineStr">
+      <c r="E103" s="6" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F103" s="4" t="inlineStr"/>
-      <c r="G103" s="4" t="inlineStr">
+      <c r="F103" s="6" t="inlineStr"/>
+      <c r="G103" s="6" t="inlineStr">
         <is>
           <t>Provided</t>
         </is>
       </c>
-      <c r="H103" s="5" t="inlineStr"/>
-      <c r="I103" s="4" t="inlineStr">
+      <c r="H103" s="7" t="inlineStr"/>
+      <c r="I103" s="6" t="inlineStr">
         <is>
           <t>Supplied by Jess</t>
         </is>
       </c>
-      <c r="J103" s="4" t="inlineStr">
+      <c r="J103" s="6" t="inlineStr">
         <is>
           <t>Bailey Corbin</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="4" t="inlineStr">
+      <c r="A104" s="6" t="inlineStr">
         <is>
           <t>Ballery</t>
         </is>
       </c>
-      <c r="B104" s="4" t="inlineStr">
+      <c r="B104" s="6" t="inlineStr">
         <is>
           <t>Guthrie</t>
         </is>
       </c>
-      <c r="C104" s="4" t="inlineStr">
+      <c r="C104" s="6" t="inlineStr">
         <is>
           <t>Tlingit Haida Tribal Business Corp.</t>
         </is>
       </c>
-      <c r="D104" s="4" t="inlineStr">
+      <c r="D104" s="6" t="inlineStr">
         <is>
           <t>HR Manager</t>
         </is>
       </c>
-      <c r="E104" s="4" t="inlineStr">
+      <c r="E104" s="6" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F104" s="4" t="inlineStr"/>
-      <c r="G104" s="4" t="inlineStr">
+      <c r="F104" s="6" t="inlineStr"/>
+      <c r="G104" s="6" t="inlineStr">
         <is>
           <t>Provided</t>
         </is>
       </c>
-      <c r="H104" s="5" t="inlineStr"/>
-      <c r="I104" s="4" t="inlineStr">
+      <c r="H104" s="7" t="inlineStr"/>
+      <c r="I104" s="6" t="inlineStr">
         <is>
           <t>Supplied by Jess</t>
         </is>
       </c>
-      <c r="J104" s="4" t="inlineStr">
+      <c r="J104" s="6" t="inlineStr">
         <is>
           <t>Ballery Guthrie</t>
         </is>
@@ -3979,264 +4035,264 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="4" t="inlineStr">
+      <c r="A106" s="6" t="inlineStr">
         <is>
           <t>Barbara</t>
         </is>
       </c>
-      <c r="B106" s="4" t="inlineStr">
+      <c r="B106" s="6" t="inlineStr">
         <is>
           <t>Bowman</t>
         </is>
       </c>
-      <c r="C106" s="4" t="inlineStr">
+      <c r="C106" s="6" t="inlineStr">
         <is>
           <t>Children's Memorial Hospital</t>
         </is>
       </c>
-      <c r="D106" s="4" t="inlineStr">
+      <c r="D106" s="6" t="inlineStr">
         <is>
           <t>CHRO</t>
         </is>
       </c>
-      <c r="E106" s="4" t="inlineStr">
+      <c r="E106" s="6" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F106" s="4" t="inlineStr"/>
-      <c r="G106" s="4" t="inlineStr">
+      <c r="F106" s="6" t="inlineStr"/>
+      <c r="G106" s="6" t="inlineStr">
         <is>
           <t>Provided</t>
         </is>
       </c>
-      <c r="H106" s="5" t="inlineStr"/>
-      <c r="I106" s="4" t="inlineStr">
+      <c r="H106" s="7" t="inlineStr"/>
+      <c r="I106" s="6" t="inlineStr">
         <is>
           <t>Supplied by Jess</t>
         </is>
       </c>
-      <c r="J106" s="4" t="inlineStr">
+      <c r="J106" s="6" t="inlineStr">
         <is>
           <t>Barbara Bowman</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="4" t="inlineStr">
+      <c r="A107" s="6" t="inlineStr">
         <is>
           <t>Barbara</t>
         </is>
       </c>
-      <c r="B107" s="4" t="inlineStr">
+      <c r="B107" s="6" t="inlineStr">
         <is>
           <t>Urbach</t>
         </is>
       </c>
-      <c r="C107" s="4" t="inlineStr">
+      <c r="C107" s="6" t="inlineStr">
         <is>
           <t>Northwest Workforce Council</t>
         </is>
       </c>
-      <c r="D107" s="4" t="inlineStr">
+      <c r="D107" s="6" t="inlineStr">
         <is>
           <t>Employment Coordinator</t>
         </is>
       </c>
-      <c r="E107" s="4" t="inlineStr">
+      <c r="E107" s="6" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F107" s="4" t="inlineStr"/>
-      <c r="G107" s="4" t="inlineStr">
+      <c r="F107" s="6" t="inlineStr"/>
+      <c r="G107" s="6" t="inlineStr">
         <is>
           <t>Provided</t>
         </is>
       </c>
-      <c r="H107" s="5" t="inlineStr"/>
-      <c r="I107" s="4" t="inlineStr">
+      <c r="H107" s="7" t="inlineStr"/>
+      <c r="I107" s="6" t="inlineStr">
         <is>
           <t>Supplied by Jess</t>
         </is>
       </c>
-      <c r="J107" s="4" t="inlineStr">
+      <c r="J107" s="6" t="inlineStr">
         <is>
           <t>Barbara Urbach</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="4" t="inlineStr">
+      <c r="A108" s="6" t="inlineStr">
         <is>
           <t>Barry</t>
         </is>
       </c>
-      <c r="B108" s="4" t="inlineStr">
+      <c r="B108" s="6" t="inlineStr">
         <is>
           <t>Lindo</t>
         </is>
       </c>
-      <c r="C108" s="4" t="inlineStr">
+      <c r="C108" s="6" t="inlineStr">
         <is>
           <t>Midwest Radiology</t>
         </is>
       </c>
-      <c r="D108" s="4" t="inlineStr">
+      <c r="D108" s="6" t="inlineStr">
         <is>
           <t>Sr. Director, HR</t>
         </is>
       </c>
-      <c r="E108" s="4" t="inlineStr">
+      <c r="E108" s="6" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F108" s="4" t="inlineStr"/>
-      <c r="G108" s="4" t="inlineStr">
+      <c r="F108" s="6" t="inlineStr"/>
+      <c r="G108" s="6" t="inlineStr">
         <is>
           <t>Provided</t>
         </is>
       </c>
-      <c r="H108" s="5" t="inlineStr"/>
-      <c r="I108" s="4" t="inlineStr">
+      <c r="H108" s="7" t="inlineStr"/>
+      <c r="I108" s="6" t="inlineStr">
         <is>
           <t>Supplied by Jess</t>
         </is>
       </c>
-      <c r="J108" s="4" t="inlineStr">
+      <c r="J108" s="6" t="inlineStr">
         <is>
           <t>Barry Lindo</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="4" t="inlineStr">
+      <c r="A109" s="6" t="inlineStr">
         <is>
           <t>Beatriz</t>
         </is>
       </c>
-      <c r="B109" s="4" t="inlineStr">
+      <c r="B109" s="6" t="inlineStr">
         <is>
           <t>Carrazana</t>
         </is>
       </c>
-      <c r="C109" s="4" t="inlineStr">
+      <c r="C109" s="6" t="inlineStr">
         <is>
           <t>Carrier Enterprises</t>
         </is>
       </c>
-      <c r="D109" s="4" t="inlineStr">
+      <c r="D109" s="6" t="inlineStr">
         <is>
           <t>Benefits Manager</t>
         </is>
       </c>
-      <c r="E109" s="4" t="inlineStr">
+      <c r="E109" s="6" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F109" s="4" t="inlineStr"/>
-      <c r="G109" s="4" t="inlineStr">
+      <c r="F109" s="6" t="inlineStr"/>
+      <c r="G109" s="6" t="inlineStr">
         <is>
           <t>Provided</t>
         </is>
       </c>
-      <c r="H109" s="5" t="inlineStr"/>
-      <c r="I109" s="4" t="inlineStr">
+      <c r="H109" s="7" t="inlineStr"/>
+      <c r="I109" s="6" t="inlineStr">
         <is>
           <t>Supplied by Jess</t>
         </is>
       </c>
-      <c r="J109" s="4" t="inlineStr">
+      <c r="J109" s="6" t="inlineStr">
         <is>
           <t>Beatriz Carrazana</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="4" t="inlineStr">
+      <c r="A110" s="6" t="inlineStr">
         <is>
           <t>Becky</t>
         </is>
       </c>
-      <c r="B110" s="4" t="inlineStr">
+      <c r="B110" s="6" t="inlineStr">
         <is>
           <t>Slade</t>
         </is>
       </c>
-      <c r="C110" s="4" t="inlineStr">
+      <c r="C110" s="6" t="inlineStr">
         <is>
           <t>Aera Technology</t>
         </is>
       </c>
-      <c r="D110" s="4" t="inlineStr">
+      <c r="D110" s="6" t="inlineStr">
         <is>
           <t>Sr. HR Generalist</t>
         </is>
       </c>
-      <c r="E110" s="4" t="inlineStr">
+      <c r="E110" s="6" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F110" s="4" t="inlineStr"/>
-      <c r="G110" s="4" t="inlineStr">
+      <c r="F110" s="6" t="inlineStr"/>
+      <c r="G110" s="6" t="inlineStr">
         <is>
           <t>Provided</t>
         </is>
       </c>
-      <c r="H110" s="5" t="inlineStr"/>
-      <c r="I110" s="4" t="inlineStr">
+      <c r="H110" s="7" t="inlineStr"/>
+      <c r="I110" s="6" t="inlineStr">
         <is>
           <t>Supplied by Jess</t>
         </is>
       </c>
-      <c r="J110" s="4" t="inlineStr">
+      <c r="J110" s="6" t="inlineStr">
         <is>
           <t>Becky Slade</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="4" t="inlineStr">
+      <c r="A111" s="6" t="inlineStr">
         <is>
           <t>Becky</t>
         </is>
       </c>
-      <c r="B111" s="4" t="inlineStr">
+      <c r="B111" s="6" t="inlineStr">
         <is>
           <t>Withstandley</t>
         </is>
       </c>
-      <c r="C111" s="4" t="inlineStr">
+      <c r="C111" s="6" t="inlineStr">
         <is>
           <t>Seacoast Bank</t>
         </is>
       </c>
-      <c r="D111" s="4" t="inlineStr">
+      <c r="D111" s="6" t="inlineStr">
         <is>
           <t>Total Rewards Manager</t>
         </is>
       </c>
-      <c r="E111" s="4" t="inlineStr">
+      <c r="E111" s="6" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F111" s="4" t="inlineStr"/>
-      <c r="G111" s="4" t="inlineStr">
+      <c r="F111" s="6" t="inlineStr"/>
+      <c r="G111" s="6" t="inlineStr">
         <is>
           <t>Provided</t>
         </is>
       </c>
-      <c r="H111" s="5" t="inlineStr"/>
-      <c r="I111" s="4" t="inlineStr">
+      <c r="H111" s="7" t="inlineStr"/>
+      <c r="I111" s="6" t="inlineStr">
         <is>
           <t>Supplied by Jess</t>
         </is>
       </c>
-      <c r="J111" s="4" t="inlineStr">
+      <c r="J111" s="6" t="inlineStr">
         <is>
           <t>Becky Withstandley</t>
         </is>
@@ -4267,264 +4323,264 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="4" t="inlineStr">
+      <c r="A113" s="6" t="inlineStr">
         <is>
           <t>Ben</t>
         </is>
       </c>
-      <c r="B113" s="4" t="inlineStr">
+      <c r="B113" s="6" t="inlineStr">
         <is>
           <t>Alberico</t>
         </is>
       </c>
-      <c r="C113" s="4" t="inlineStr">
+      <c r="C113" s="6" t="inlineStr">
         <is>
           <t>Momentum Financial Services Group</t>
         </is>
       </c>
-      <c r="D113" s="4" t="inlineStr">
+      <c r="D113" s="6" t="inlineStr">
         <is>
           <t>HRBP</t>
         </is>
       </c>
-      <c r="E113" s="4" t="inlineStr">
+      <c r="E113" s="6" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F113" s="4" t="inlineStr"/>
-      <c r="G113" s="4" t="inlineStr">
+      <c r="F113" s="6" t="inlineStr"/>
+      <c r="G113" s="6" t="inlineStr">
         <is>
           <t>Provided</t>
         </is>
       </c>
-      <c r="H113" s="5" t="inlineStr"/>
-      <c r="I113" s="4" t="inlineStr">
+      <c r="H113" s="7" t="inlineStr"/>
+      <c r="I113" s="6" t="inlineStr">
         <is>
           <t>Supplied by Jess</t>
         </is>
       </c>
-      <c r="J113" s="4" t="inlineStr">
+      <c r="J113" s="6" t="inlineStr">
         <is>
           <t>Ben Alberico</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="4" t="inlineStr">
+      <c r="A114" s="6" t="inlineStr">
         <is>
           <t>Beth</t>
         </is>
       </c>
-      <c r="B114" s="4" t="inlineStr">
+      <c r="B114" s="6" t="inlineStr">
         <is>
           <t>Andrew-Berry</t>
         </is>
       </c>
-      <c r="C114" s="4" t="inlineStr">
+      <c r="C114" s="6" t="inlineStr">
         <is>
           <t>New England Asset Management</t>
         </is>
       </c>
-      <c r="D114" s="4" t="inlineStr">
+      <c r="D114" s="6" t="inlineStr">
         <is>
           <t>Director, HR</t>
         </is>
       </c>
-      <c r="E114" s="4" t="inlineStr">
+      <c r="E114" s="6" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F114" s="4" t="inlineStr"/>
-      <c r="G114" s="4" t="inlineStr">
+      <c r="F114" s="6" t="inlineStr"/>
+      <c r="G114" s="6" t="inlineStr">
         <is>
           <t>Provided</t>
         </is>
       </c>
-      <c r="H114" s="5" t="inlineStr"/>
-      <c r="I114" s="4" t="inlineStr">
+      <c r="H114" s="7" t="inlineStr"/>
+      <c r="I114" s="6" t="inlineStr">
         <is>
           <t>Supplied by Jess</t>
         </is>
       </c>
-      <c r="J114" s="4" t="inlineStr">
+      <c r="J114" s="6" t="inlineStr">
         <is>
           <t>Beth Andrew-Berry</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="4" t="inlineStr">
+      <c r="A115" s="6" t="inlineStr">
         <is>
           <t>Beth</t>
         </is>
       </c>
-      <c r="B115" s="4" t="inlineStr">
+      <c r="B115" s="6" t="inlineStr">
         <is>
           <t>Croon</t>
         </is>
       </c>
-      <c r="C115" s="4" t="inlineStr">
+      <c r="C115" s="6" t="inlineStr">
         <is>
           <t>YMCA Seattle/King/Snohomish</t>
         </is>
       </c>
-      <c r="D115" s="4" t="inlineStr">
+      <c r="D115" s="6" t="inlineStr">
         <is>
           <t>Sr. Manager, Total Rewards &amp; HR Systems</t>
         </is>
       </c>
-      <c r="E115" s="4" t="inlineStr">
+      <c r="E115" s="6" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F115" s="4" t="inlineStr"/>
-      <c r="G115" s="4" t="inlineStr">
+      <c r="F115" s="6" t="inlineStr"/>
+      <c r="G115" s="6" t="inlineStr">
         <is>
           <t>Provided</t>
         </is>
       </c>
-      <c r="H115" s="5" t="inlineStr"/>
-      <c r="I115" s="4" t="inlineStr">
+      <c r="H115" s="7" t="inlineStr"/>
+      <c r="I115" s="6" t="inlineStr">
         <is>
           <t>Supplied by Jess</t>
         </is>
       </c>
-      <c r="J115" s="4" t="inlineStr">
+      <c r="J115" s="6" t="inlineStr">
         <is>
           <t>Beth Croon</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="4" t="inlineStr">
+      <c r="A116" s="6" t="inlineStr">
         <is>
           <t>Beth</t>
         </is>
       </c>
-      <c r="B116" s="4" t="inlineStr">
+      <c r="B116" s="6" t="inlineStr">
         <is>
           <t>Erickson</t>
         </is>
       </c>
-      <c r="C116" s="4" t="inlineStr">
+      <c r="C116" s="6" t="inlineStr">
         <is>
           <t>Simpro Software</t>
         </is>
       </c>
-      <c r="D116" s="4" t="inlineStr">
+      <c r="D116" s="6" t="inlineStr">
         <is>
           <t>CHRO</t>
         </is>
       </c>
-      <c r="E116" s="4" t="inlineStr">
+      <c r="E116" s="6" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F116" s="4" t="inlineStr"/>
-      <c r="G116" s="4" t="inlineStr">
+      <c r="F116" s="6" t="inlineStr"/>
+      <c r="G116" s="6" t="inlineStr">
         <is>
           <t>Provided</t>
         </is>
       </c>
-      <c r="H116" s="5" t="inlineStr"/>
-      <c r="I116" s="4" t="inlineStr">
+      <c r="H116" s="7" t="inlineStr"/>
+      <c r="I116" s="6" t="inlineStr">
         <is>
           <t>Supplied by Jess</t>
         </is>
       </c>
-      <c r="J116" s="4" t="inlineStr">
+      <c r="J116" s="6" t="inlineStr">
         <is>
           <t>Beth Erickson</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="4" t="inlineStr">
+      <c r="A117" s="6" t="inlineStr">
         <is>
           <t>Beth</t>
         </is>
       </c>
-      <c r="B117" s="4" t="inlineStr">
+      <c r="B117" s="6" t="inlineStr">
         <is>
           <t>Farris</t>
         </is>
       </c>
-      <c r="C117" s="4" t="inlineStr">
+      <c r="C117" s="6" t="inlineStr">
         <is>
           <t>Mellow Mushroom</t>
         </is>
       </c>
-      <c r="D117" s="4" t="inlineStr">
+      <c r="D117" s="6" t="inlineStr">
         <is>
           <t>HR Consultant</t>
         </is>
       </c>
-      <c r="E117" s="4" t="inlineStr">
+      <c r="E117" s="6" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F117" s="4" t="inlineStr"/>
-      <c r="G117" s="4" t="inlineStr">
+      <c r="F117" s="6" t="inlineStr"/>
+      <c r="G117" s="6" t="inlineStr">
         <is>
           <t>Provided</t>
         </is>
       </c>
-      <c r="H117" s="5" t="inlineStr"/>
-      <c r="I117" s="4" t="inlineStr">
+      <c r="H117" s="7" t="inlineStr"/>
+      <c r="I117" s="6" t="inlineStr">
         <is>
           <t>Supplied by Jess</t>
         </is>
       </c>
-      <c r="J117" s="4" t="inlineStr">
+      <c r="J117" s="6" t="inlineStr">
         <is>
           <t>Beth Farris</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="4" t="inlineStr">
+      <c r="A118" s="6" t="inlineStr">
         <is>
           <t>Beth</t>
         </is>
       </c>
-      <c r="B118" s="4" t="inlineStr">
+      <c r="B118" s="6" t="inlineStr">
         <is>
           <t>Florek-Chiang</t>
         </is>
       </c>
-      <c r="C118" s="4" t="inlineStr">
+      <c r="C118" s="6" t="inlineStr">
         <is>
           <t>Child Care Resource Center</t>
         </is>
       </c>
-      <c r="D118" s="4" t="inlineStr">
+      <c r="D118" s="6" t="inlineStr">
         <is>
           <t>HR Benefits Specialist</t>
         </is>
       </c>
-      <c r="E118" s="4" t="inlineStr">
+      <c r="E118" s="6" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F118" s="4" t="inlineStr"/>
-      <c r="G118" s="4" t="inlineStr">
+      <c r="F118" s="6" t="inlineStr"/>
+      <c r="G118" s="6" t="inlineStr">
         <is>
           <t>Provided</t>
         </is>
       </c>
-      <c r="H118" s="5" t="inlineStr"/>
-      <c r="I118" s="4" t="inlineStr">
+      <c r="H118" s="7" t="inlineStr"/>
+      <c r="I118" s="6" t="inlineStr">
         <is>
           <t>Supplied by Jess</t>
         </is>
       </c>
-      <c r="J118" s="4" t="inlineStr">
+      <c r="J118" s="6" t="inlineStr">
         <is>
           <t>Beth Florek-Chiang</t>
         </is>
@@ -4555,68 +4611,96 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+      <c r="A120" s="4" t="inlineStr">
         <is>
           <t>Beulah</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
+      <c r="B120" s="4" t="inlineStr">
         <is>
           <t>Kyei-Mensah</t>
         </is>
       </c>
-      <c r="C120" s="2" t="inlineStr"/>
-      <c r="D120" s="2" t="inlineStr"/>
-      <c r="E120" s="2" t="inlineStr"/>
-      <c r="F120" s="2" t="inlineStr"/>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="3" t="inlineStr"/>
-      <c r="I120" s="2" t="inlineStr"/>
-      <c r="J120" s="2" t="inlineStr">
+      <c r="C120" s="4" t="inlineStr">
+        <is>
+          <t>TDC Development</t>
+        </is>
+      </c>
+      <c r="D120" s="4" t="inlineStr">
+        <is>
+          <t>HR Administrator</t>
+        </is>
+      </c>
+      <c r="E120" s="4" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F120" s="4" t="inlineStr">
+        <is>
+          <t>Tema, Ghana</t>
+        </is>
+      </c>
+      <c r="G120" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H120" s="5" t="inlineStr">
+        <is>
+          <t>Civil engineering / construction sector.</t>
+        </is>
+      </c>
+      <c r="I120" s="4" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
+      <c r="J120" s="4" t="inlineStr">
         <is>
           <t>Beulah Kyei-Mensah</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="4" t="inlineStr">
+      <c r="A121" s="6" t="inlineStr">
         <is>
           <t>Billie</t>
         </is>
       </c>
-      <c r="B121" s="4" t="inlineStr">
+      <c r="B121" s="6" t="inlineStr">
         <is>
           <t>Llewellyn</t>
         </is>
       </c>
-      <c r="C121" s="4" t="inlineStr">
+      <c r="C121" s="6" t="inlineStr">
         <is>
           <t>Massage Envy Franchising</t>
         </is>
       </c>
-      <c r="D121" s="4" t="inlineStr">
+      <c r="D121" s="6" t="inlineStr">
         <is>
           <t>Talent Acquisition Manager</t>
         </is>
       </c>
-      <c r="E121" s="4" t="inlineStr">
+      <c r="E121" s="6" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F121" s="4" t="inlineStr"/>
-      <c r="G121" s="4" t="inlineStr">
+      <c r="F121" s="6" t="inlineStr"/>
+      <c r="G121" s="6" t="inlineStr">
         <is>
           <t>Provided</t>
         </is>
       </c>
-      <c r="H121" s="5" t="inlineStr"/>
-      <c r="I121" s="4" t="inlineStr">
+      <c r="H121" s="7" t="inlineStr"/>
+      <c r="I121" s="6" t="inlineStr">
         <is>
           <t>Supplied by Jess</t>
         </is>
       </c>
-      <c r="J121" s="4" t="inlineStr">
+      <c r="J121" s="6" t="inlineStr">
         <is>
           <t>Billie Llewellyn</t>
         </is>
@@ -4671,88 +4755,88 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="4" t="inlineStr">
+      <c r="A124" s="6" t="inlineStr">
         <is>
           <t>Bonike</t>
         </is>
       </c>
-      <c r="B124" s="4" t="inlineStr">
+      <c r="B124" s="6" t="inlineStr">
         <is>
           <t>Akinsanya</t>
         </is>
       </c>
-      <c r="C124" s="4" t="inlineStr">
+      <c r="C124" s="6" t="inlineStr">
         <is>
           <t>CannonDesign</t>
         </is>
       </c>
-      <c r="D124" s="4" t="inlineStr">
+      <c r="D124" s="6" t="inlineStr">
         <is>
           <t>Sr. Associate, Sr. Recruiter</t>
         </is>
       </c>
-      <c r="E124" s="4" t="inlineStr">
+      <c r="E124" s="6" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F124" s="4" t="inlineStr"/>
-      <c r="G124" s="4" t="inlineStr">
+      <c r="F124" s="6" t="inlineStr"/>
+      <c r="G124" s="6" t="inlineStr">
         <is>
           <t>Provided</t>
         </is>
       </c>
-      <c r="H124" s="5" t="inlineStr"/>
-      <c r="I124" s="4" t="inlineStr">
+      <c r="H124" s="7" t="inlineStr"/>
+      <c r="I124" s="6" t="inlineStr">
         <is>
           <t>Supplied by Jess</t>
         </is>
       </c>
-      <c r="J124" s="4" t="inlineStr">
+      <c r="J124" s="6" t="inlineStr">
         <is>
           <t>Bonike Akinsanya</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="4" t="inlineStr">
+      <c r="A125" s="6" t="inlineStr">
         <is>
           <t>Bonnie</t>
         </is>
       </c>
-      <c r="B125" s="4" t="inlineStr">
+      <c r="B125" s="6" t="inlineStr">
         <is>
           <t>Hayward</t>
         </is>
       </c>
-      <c r="C125" s="4" t="inlineStr">
+      <c r="C125" s="6" t="inlineStr">
         <is>
           <t>Communitas Supportive Care Society</t>
         </is>
       </c>
-      <c r="D125" s="4" t="inlineStr">
+      <c r="D125" s="6" t="inlineStr">
         <is>
           <t>Safety, Health &amp; Wellness Coordinator</t>
         </is>
       </c>
-      <c r="E125" s="4" t="inlineStr">
+      <c r="E125" s="6" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F125" s="4" t="inlineStr"/>
-      <c r="G125" s="4" t="inlineStr">
+      <c r="F125" s="6" t="inlineStr"/>
+      <c r="G125" s="6" t="inlineStr">
         <is>
           <t>Provided</t>
         </is>
       </c>
-      <c r="H125" s="5" t="inlineStr"/>
-      <c r="I125" s="4" t="inlineStr">
+      <c r="H125" s="7" t="inlineStr"/>
+      <c r="I125" s="6" t="inlineStr">
         <is>
           <t>Supplied by Jess</t>
         </is>
       </c>
-      <c r="J125" s="4" t="inlineStr">
+      <c r="J125" s="6" t="inlineStr">
         <is>
           <t>Bonnie Hayward</t>
         </is>
@@ -4783,44 +4867,44 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="4" t="inlineStr">
+      <c r="A127" s="6" t="inlineStr">
         <is>
           <t>Brad</t>
         </is>
       </c>
-      <c r="B127" s="4" t="inlineStr">
+      <c r="B127" s="6" t="inlineStr">
         <is>
           <t>Sheasley</t>
         </is>
       </c>
-      <c r="C127" s="4" t="inlineStr">
+      <c r="C127" s="6" t="inlineStr">
         <is>
           <t>Baker Tilly</t>
         </is>
       </c>
-      <c r="D127" s="4" t="inlineStr">
+      <c r="D127" s="6" t="inlineStr">
         <is>
           <t>Sr. Manager, HR &amp; Payroll Managed Services</t>
         </is>
       </c>
-      <c r="E127" s="4" t="inlineStr">
+      <c r="E127" s="6" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F127" s="4" t="inlineStr"/>
-      <c r="G127" s="4" t="inlineStr">
+      <c r="F127" s="6" t="inlineStr"/>
+      <c r="G127" s="6" t="inlineStr">
         <is>
           <t>Provided</t>
         </is>
       </c>
-      <c r="H127" s="5" t="inlineStr"/>
-      <c r="I127" s="4" t="inlineStr">
+      <c r="H127" s="7" t="inlineStr"/>
+      <c r="I127" s="6" t="inlineStr">
         <is>
           <t>Supplied by Jess</t>
         </is>
       </c>
-      <c r="J127" s="4" t="inlineStr">
+      <c r="J127" s="6" t="inlineStr">
         <is>
           <t>Brad Sheasley</t>
         </is>
@@ -5043,24 +5127,52 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+      <c r="A137" s="4" t="inlineStr">
         <is>
           <t>Brijuan</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
+      <c r="B137" s="4" t="inlineStr">
         <is>
           <t>Phillips</t>
         </is>
       </c>
-      <c r="C137" s="2" t="inlineStr"/>
-      <c r="D137" s="2" t="inlineStr"/>
-      <c r="E137" s="2" t="inlineStr"/>
-      <c r="F137" s="2" t="inlineStr"/>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="3" t="inlineStr"/>
-      <c r="I137" s="2" t="inlineStr"/>
-      <c r="J137" s="2" t="inlineStr">
+      <c r="C137" s="4" t="inlineStr">
+        <is>
+          <t>BeWELL Psychotherapy and Wellness</t>
+        </is>
+      </c>
+      <c r="D137" s="4" t="inlineStr">
+        <is>
+          <t>Therapist (LMSW)</t>
+        </is>
+      </c>
+      <c r="E137" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F137" s="4" t="inlineStr">
+        <is>
+          <t>New York, NY / Hoboken, NJ</t>
+        </is>
+      </c>
+      <c r="G137" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H137" s="5" t="inlineStr">
+        <is>
+          <t>NOT HR - behavioural health clinician. NYU MSW, CSWE Minority Fellow. EMDR/CBT/DBT.</t>
+        </is>
+      </c>
+      <c r="I137" s="4" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
+      <c r="J137" s="4" t="inlineStr">
         <is>
           <t>Brijuan Phillips</t>
         </is>
@@ -5091,48 +5203,104 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+      <c r="A139" s="4" t="inlineStr">
         <is>
           <t>Britaney</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
+      <c r="B139" s="4" t="inlineStr">
         <is>
           <t>Francis</t>
         </is>
       </c>
-      <c r="C139" s="2" t="inlineStr"/>
-      <c r="D139" s="2" t="inlineStr"/>
-      <c r="E139" s="2" t="inlineStr"/>
-      <c r="F139" s="2" t="inlineStr"/>
-      <c r="G139" s="2" t="inlineStr"/>
-      <c r="H139" s="3" t="inlineStr"/>
-      <c r="I139" s="2" t="inlineStr"/>
-      <c r="J139" s="2" t="inlineStr">
+      <c r="C139" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D139" s="4" t="inlineStr">
+        <is>
+          <t>HR Professional</t>
+        </is>
+      </c>
+      <c r="E139" s="4" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="F139" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G139" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H139" s="5" t="inlineStr">
+        <is>
+          <t>LinkedIn confirms HR; no employer found.</t>
+        </is>
+      </c>
+      <c r="I139" s="4" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
+      <c r="J139" s="4" t="inlineStr">
         <is>
           <t>Britaney Francis</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+      <c r="A140" s="4" t="inlineStr">
         <is>
           <t>Britta</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
+      <c r="B140" s="4" t="inlineStr">
         <is>
           <t>Kallunki</t>
         </is>
       </c>
-      <c r="C140" s="2" t="inlineStr"/>
-      <c r="D140" s="2" t="inlineStr"/>
-      <c r="E140" s="2" t="inlineStr"/>
-      <c r="F140" s="2" t="inlineStr"/>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="3" t="inlineStr"/>
-      <c r="I140" s="2" t="inlineStr"/>
-      <c r="J140" s="2" t="inlineStr">
+      <c r="C140" s="4" t="inlineStr">
+        <is>
+          <t>Republic Services</t>
+        </is>
+      </c>
+      <c r="D140" s="4" t="inlineStr">
+        <is>
+          <t>HR Systems Analyst</t>
+        </is>
+      </c>
+      <c r="E140" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F140" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G140" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H140" s="5" t="inlineStr">
+        <is>
+          <t>Prior: US Ecology (HRIS, Shared Services Mgr, HR Generalist).</t>
+        </is>
+      </c>
+      <c r="I140" s="4" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
+      <c r="J140" s="4" t="inlineStr">
         <is>
           <t>Britta Kallunki</t>
         </is>
@@ -5307,24 +5475,52 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+      <c r="A148" s="4" t="inlineStr">
         <is>
           <t>Brooke</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
+      <c r="B148" s="4" t="inlineStr">
         <is>
           <t>Janoski</t>
         </is>
       </c>
-      <c r="C148" s="2" t="inlineStr"/>
-      <c r="D148" s="2" t="inlineStr"/>
-      <c r="E148" s="2" t="inlineStr"/>
-      <c r="F148" s="2" t="inlineStr"/>
-      <c r="G148" s="2" t="inlineStr"/>
-      <c r="H148" s="3" t="inlineStr"/>
-      <c r="I148" s="2" t="inlineStr"/>
-      <c r="J148" s="2" t="inlineStr">
+      <c r="C148" s="4" t="inlineStr">
+        <is>
+          <t>Pinnacle Plan Design</t>
+        </is>
+      </c>
+      <c r="D148" s="4" t="inlineStr">
+        <is>
+          <t>HR Supervisor / Coordinator</t>
+        </is>
+      </c>
+      <c r="E148" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F148" s="4" t="inlineStr">
+        <is>
+          <t>Tucson, AZ</t>
+        </is>
+      </c>
+      <c r="G148" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H148" s="5" t="inlineStr">
+        <is>
+          <t>Retirement plan actuaries/administrators. Prior: BELFOR, GEICO.</t>
+        </is>
+      </c>
+      <c r="I148" s="4" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
+      <c r="J148" s="4" t="inlineStr">
         <is>
           <t>Brooke Janoski</t>
         </is>
@@ -5403,24 +5599,52 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+      <c r="A152" s="4" t="inlineStr">
         <is>
           <t>Camuy</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
+      <c r="B152" s="4" t="inlineStr">
         <is>
           <t>Heremuru</t>
         </is>
       </c>
-      <c r="C152" s="2" t="inlineStr"/>
-      <c r="D152" s="2" t="inlineStr"/>
-      <c r="E152" s="2" t="inlineStr"/>
-      <c r="F152" s="2" t="inlineStr"/>
-      <c r="G152" s="2" t="inlineStr"/>
-      <c r="H152" s="3" t="inlineStr"/>
-      <c r="I152" s="2" t="inlineStr"/>
-      <c r="J152" s="2" t="inlineStr">
+      <c r="C152" s="4" t="inlineStr">
+        <is>
+          <t>US Army</t>
+        </is>
+      </c>
+      <c r="D152" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager / Master Sergeant</t>
+        </is>
+      </c>
+      <c r="E152" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F152" s="4" t="inlineStr">
+        <is>
+          <t>Fort Jackson, SC</t>
+        </is>
+      </c>
+      <c r="G152" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H152" s="5" t="inlineStr">
+        <is>
+          <t>Liaison NCO, training standards for Army and Reserve Component.</t>
+        </is>
+      </c>
+      <c r="I152" s="4" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
+      <c r="J152" s="4" t="inlineStr">
         <is>
           <t>Camuy Heremuru</t>
         </is>
@@ -5571,24 +5795,52 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+      <c r="A159" s="4" t="inlineStr">
         <is>
           <t>Cariana</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
+      <c r="B159" s="4" t="inlineStr">
         <is>
           <t>Checo</t>
         </is>
       </c>
-      <c r="C159" s="2" t="inlineStr"/>
-      <c r="D159" s="2" t="inlineStr"/>
-      <c r="E159" s="2" t="inlineStr"/>
-      <c r="F159" s="2" t="inlineStr"/>
-      <c r="G159" s="2" t="inlineStr"/>
-      <c r="H159" s="3" t="inlineStr"/>
-      <c r="I159" s="2" t="inlineStr"/>
-      <c r="J159" s="2" t="inlineStr">
+      <c r="C159" s="4" t="inlineStr">
+        <is>
+          <t>The Opportunity Network</t>
+        </is>
+      </c>
+      <c r="D159" s="4" t="inlineStr">
+        <is>
+          <t>HR Assistant</t>
+        </is>
+      </c>
+      <c r="E159" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F159" s="4" t="inlineStr">
+        <is>
+          <t>New York, NY</t>
+        </is>
+      </c>
+      <c r="G159" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H159" s="5" t="inlineStr">
+        <is>
+          <t>Talent acquisition, benefits admin, onboarding. Ex-immigration paralegal.</t>
+        </is>
+      </c>
+      <c r="I159" s="4" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
+      <c r="J159" s="4" t="inlineStr">
         <is>
           <t>Cariana Checo</t>
         </is>
@@ -5955,24 +6207,52 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="inlineStr">
+      <c r="A175" s="4" t="inlineStr">
         <is>
           <t>Caylah</t>
         </is>
       </c>
-      <c r="B175" s="2" t="inlineStr">
+      <c r="B175" s="4" t="inlineStr">
         <is>
           <t>Lunardi</t>
         </is>
       </c>
-      <c r="C175" s="2" t="inlineStr"/>
-      <c r="D175" s="2" t="inlineStr"/>
-      <c r="E175" s="2" t="inlineStr"/>
-      <c r="F175" s="2" t="inlineStr"/>
-      <c r="G175" s="2" t="inlineStr"/>
-      <c r="H175" s="3" t="inlineStr"/>
-      <c r="I175" s="2" t="inlineStr"/>
-      <c r="J175" s="2" t="inlineStr">
+      <c r="C175" s="4" t="inlineStr">
+        <is>
+          <t>Summit Engineering</t>
+        </is>
+      </c>
+      <c r="D175" s="4" t="inlineStr">
+        <is>
+          <t>Human Resources Manager</t>
+        </is>
+      </c>
+      <c r="E175" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F175" s="4" t="inlineStr">
+        <is>
+          <t>Santa Rosa, CA</t>
+        </is>
+      </c>
+      <c r="G175" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H175" s="5" t="inlineStr">
+        <is>
+          <t>Joined Feb 2024. Prior: Target (Assets Protection BP).</t>
+        </is>
+      </c>
+      <c r="I175" s="4" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
+      <c r="J175" s="4" t="inlineStr">
         <is>
           <t>Caylah Lunardi</t>
         </is>
@@ -6123,24 +6403,52 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="2" t="inlineStr">
+      <c r="A182" s="4" t="inlineStr">
         <is>
           <t>Chelsea</t>
         </is>
       </c>
-      <c r="B182" s="2" t="inlineStr">
+      <c r="B182" s="4" t="inlineStr">
         <is>
           <t>Nieland</t>
         </is>
       </c>
-      <c r="C182" s="2" t="inlineStr"/>
-      <c r="D182" s="2" t="inlineStr"/>
-      <c r="E182" s="2" t="inlineStr"/>
-      <c r="F182" s="2" t="inlineStr"/>
-      <c r="G182" s="2" t="inlineStr"/>
-      <c r="H182" s="3" t="inlineStr"/>
-      <c r="I182" s="2" t="inlineStr"/>
-      <c r="J182" s="2" t="inlineStr">
+      <c r="C182" s="4" t="inlineStr">
+        <is>
+          <t>Hy-Vee</t>
+        </is>
+      </c>
+      <c r="D182" s="4" t="inlineStr">
+        <is>
+          <t>Manager, Area Human Resources (PHR)</t>
+        </is>
+      </c>
+      <c r="E182" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F182" s="4" t="inlineStr">
+        <is>
+          <t>Iowa</t>
+        </is>
+      </c>
+      <c r="G182" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H182" s="5" t="inlineStr">
+        <is>
+          <t>Prior: Cintas (Regional Recruiter, HR Manager).</t>
+        </is>
+      </c>
+      <c r="I182" s="4" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
+      <c r="J182" s="4" t="inlineStr">
         <is>
           <t>Chelsea Nieland</t>
         </is>
@@ -6195,24 +6503,52 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="2" t="inlineStr">
+      <c r="A185" s="4" t="inlineStr">
         <is>
           <t>Cheryl</t>
         </is>
       </c>
-      <c r="B185" s="2" t="inlineStr">
+      <c r="B185" s="4" t="inlineStr">
         <is>
           <t>Gurule</t>
         </is>
       </c>
-      <c r="C185" s="2" t="inlineStr"/>
-      <c r="D185" s="2" t="inlineStr"/>
-      <c r="E185" s="2" t="inlineStr"/>
-      <c r="F185" s="2" t="inlineStr"/>
-      <c r="G185" s="2" t="inlineStr"/>
-      <c r="H185" s="3" t="inlineStr"/>
-      <c r="I185" s="2" t="inlineStr"/>
-      <c r="J185" s="2" t="inlineStr">
+      <c r="C185" s="4" t="inlineStr">
+        <is>
+          <t>PCL Construction</t>
+        </is>
+      </c>
+      <c r="D185" s="4" t="inlineStr">
+        <is>
+          <t>HR Benefits Coordinator (PHR)</t>
+        </is>
+      </c>
+      <c r="E185" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F185" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G185" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H185" s="5" t="inlineStr">
+        <is>
+          <t>HIGH RELEVANCE - benefits role inside a major construction contractor. Prior: AECOM (HR Generalist 17 yrs), URS Corp.</t>
+        </is>
+      </c>
+      <c r="I185" s="4" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
+      <c r="J185" s="4" t="inlineStr">
         <is>
           <t>Cheryl Gurule</t>
         </is>
@@ -6243,52 +6579,52 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="6" t="inlineStr">
+      <c r="A187" s="4" t="inlineStr">
         <is>
           <t>Chinenye</t>
         </is>
       </c>
-      <c r="B187" s="6" t="inlineStr">
+      <c r="B187" s="4" t="inlineStr">
         <is>
           <t>Izuchukwu</t>
         </is>
       </c>
-      <c r="C187" s="6" t="inlineStr">
+      <c r="C187" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D187" s="6" t="inlineStr">
+      <c r="D187" s="4" t="inlineStr">
         <is>
           <t>Talent management / postgraduate</t>
         </is>
       </c>
-      <c r="E187" s="6" t="inlineStr">
+      <c r="E187" s="4" t="inlineStr">
         <is>
           <t>International (likely)</t>
         </is>
       </c>
-      <c r="F187" s="6" t="inlineStr">
+      <c r="F187" s="4" t="inlineStr">
         <is>
           <t>UK or Nigeria</t>
         </is>
       </c>
-      <c r="G187" s="6" t="inlineStr">
+      <c r="G187" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H187" s="7" t="inlineStr">
+      <c r="H187" s="5" t="inlineStr">
         <is>
           <t>Candidate profile is a student at Univ. of Northampton, UK.</t>
         </is>
       </c>
-      <c r="I187" s="6" t="inlineStr">
+      <c r="I187" s="4" t="inlineStr">
         <is>
           <t>Web research</t>
         </is>
       </c>
-      <c r="J187" s="6" t="inlineStr">
+      <c r="J187" s="4" t="inlineStr">
         <is>
           <t>Chinenye Izuchukwu</t>
         </is>
@@ -7159,24 +7495,52 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="2" t="inlineStr">
+      <c r="A224" s="4" t="inlineStr">
         <is>
           <t>Corina</t>
         </is>
       </c>
-      <c r="B224" s="2" t="inlineStr">
+      <c r="B224" s="4" t="inlineStr">
         <is>
           <t>Valazquez</t>
         </is>
       </c>
-      <c r="C224" s="2" t="inlineStr"/>
-      <c r="D224" s="2" t="inlineStr"/>
-      <c r="E224" s="2" t="inlineStr"/>
-      <c r="F224" s="2" t="inlineStr"/>
-      <c r="G224" s="2" t="inlineStr"/>
-      <c r="H224" s="3" t="inlineStr"/>
-      <c r="I224" s="2" t="inlineStr"/>
-      <c r="J224" s="2" t="inlineStr">
+      <c r="C224" s="4" t="inlineStr">
+        <is>
+          <t>School District of Lee County</t>
+        </is>
+      </c>
+      <c r="D224" s="4" t="inlineStr">
+        <is>
+          <t>Executive Director of Human Resources</t>
+        </is>
+      </c>
+      <c r="E224" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F224" s="4" t="inlineStr">
+        <is>
+          <t>Fort Myers, FL</t>
+        </is>
+      </c>
+      <c r="G224" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H224" s="5" t="inlineStr">
+        <is>
+          <t>Source spells surname Velasquez - verify it is the same person.</t>
+        </is>
+      </c>
+      <c r="I224" s="4" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
+      <c r="J224" s="4" t="inlineStr">
         <is>
           <t>Corina Valazquez</t>
         </is>
@@ -7207,52 +7571,52 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="6" t="inlineStr">
+      <c r="A226" s="4" t="inlineStr">
         <is>
           <t>Corinne</t>
         </is>
       </c>
-      <c r="B226" s="6" t="inlineStr">
+      <c r="B226" s="4" t="inlineStr">
         <is>
           <t>Zylstra</t>
         </is>
       </c>
-      <c r="C226" s="6" t="inlineStr">
+      <c r="C226" s="4" t="inlineStr">
         <is>
           <t>Symetra</t>
         </is>
       </c>
-      <c r="D226" s="6" t="inlineStr">
+      <c r="D226" s="4" t="inlineStr">
         <is>
           <t>HR Coordinator</t>
         </is>
       </c>
-      <c r="E226" s="6" t="inlineStr">
+      <c r="E226" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F226" s="6" t="inlineStr">
+      <c r="F226" s="4" t="inlineStr">
         <is>
           <t>Bellevue, WA</t>
         </is>
       </c>
-      <c r="G226" s="6" t="inlineStr">
+      <c r="G226" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H226" s="7" t="inlineStr">
+      <c r="H226" s="5" t="inlineStr">
         <is>
           <t>Prior: Starbucks contact centre (pay/benefits/HR policy).</t>
         </is>
       </c>
-      <c r="I226" s="6" t="inlineStr">
+      <c r="I226" s="4" t="inlineStr">
         <is>
           <t>Web research</t>
         </is>
       </c>
-      <c r="J226" s="6" t="inlineStr">
+      <c r="J226" s="4" t="inlineStr">
         <is>
           <t>Corinne Zylstra</t>
         </is>
@@ -7379,52 +7743,52 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="6" t="inlineStr">
+      <c r="A232" s="4" t="inlineStr">
         <is>
           <t>Cynthia</t>
         </is>
       </c>
-      <c r="B232" s="6" t="inlineStr">
+      <c r="B232" s="4" t="inlineStr">
         <is>
           <t>Osei-owusu</t>
         </is>
       </c>
-      <c r="C232" s="6" t="inlineStr">
+      <c r="C232" s="4" t="inlineStr">
         <is>
           <t>Broadcast/media sector (Adventist Radio London)</t>
         </is>
       </c>
-      <c r="D232" s="6" t="inlineStr">
+      <c r="D232" s="4" t="inlineStr">
         <is>
           <t>Head of HR (CIPD)</t>
         </is>
       </c>
-      <c r="E232" s="6" t="inlineStr">
+      <c r="E232" s="4" t="inlineStr">
         <is>
           <t>International</t>
         </is>
       </c>
-      <c r="F232" s="6" t="inlineStr">
+      <c r="F232" s="4" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="G232" s="6" t="inlineStr">
+      <c r="G232" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H232" s="7" t="inlineStr">
+      <c r="H232" s="5" t="inlineStr">
         <is>
           <t>Union chair, Unite. Hosts "WorkLife" show.</t>
         </is>
       </c>
-      <c r="I232" s="6" t="inlineStr">
+      <c r="I232" s="4" t="inlineStr">
         <is>
           <t>Web research</t>
         </is>
       </c>
-      <c r="J232" s="6" t="inlineStr">
+      <c r="J232" s="4" t="inlineStr">
         <is>
           <t>Cynthia Osei-owusu</t>
         </is>
@@ -7455,24 +7819,52 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="2" t="inlineStr">
+      <c r="A234" s="4" t="inlineStr">
         <is>
           <t>Cynthia</t>
         </is>
       </c>
-      <c r="B234" s="2" t="inlineStr">
+      <c r="B234" s="4" t="inlineStr">
         <is>
           <t>Ramnarinne</t>
         </is>
       </c>
-      <c r="C234" s="2" t="inlineStr"/>
-      <c r="D234" s="2" t="inlineStr"/>
-      <c r="E234" s="2" t="inlineStr"/>
-      <c r="F234" s="2" t="inlineStr"/>
-      <c r="G234" s="2" t="inlineStr"/>
-      <c r="H234" s="3" t="inlineStr"/>
-      <c r="I234" s="2" t="inlineStr"/>
-      <c r="J234" s="2" t="inlineStr">
+      <c r="C234" s="4" t="inlineStr">
+        <is>
+          <t>Brosnan Risk Consultants</t>
+        </is>
+      </c>
+      <c r="D234" s="4" t="inlineStr">
+        <is>
+          <t>Director of HR, Eastern Division (PHR, SHRM)</t>
+        </is>
+      </c>
+      <c r="E234" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F234" s="4" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="G234" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H234" s="5" t="inlineStr">
+        <is>
+          <t>Prior: The Roosevelt Hotel, NY Hilton Midtown, Empire City Casino.</t>
+        </is>
+      </c>
+      <c r="I234" s="4" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
+      <c r="J234" s="4" t="inlineStr">
         <is>
           <t>Cynthia Ramnarinne</t>
         </is>
@@ -7575,24 +7967,52 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="2" t="inlineStr">
+      <c r="A239" s="4" t="inlineStr">
         <is>
           <t>Damilare</t>
         </is>
       </c>
-      <c r="B239" s="2" t="inlineStr">
+      <c r="B239" s="4" t="inlineStr">
         <is>
           <t>Olumeko</t>
         </is>
       </c>
-      <c r="C239" s="2" t="inlineStr"/>
-      <c r="D239" s="2" t="inlineStr"/>
-      <c r="E239" s="2" t="inlineStr"/>
-      <c r="F239" s="2" t="inlineStr"/>
-      <c r="G239" s="2" t="inlineStr"/>
-      <c r="H239" s="3" t="inlineStr"/>
-      <c r="I239" s="2" t="inlineStr"/>
-      <c r="J239" s="2" t="inlineStr">
+      <c r="C239" s="4" t="inlineStr">
+        <is>
+          <t>Insight Redefini (also listed at PwC)</t>
+        </is>
+      </c>
+      <c r="D239" s="4" t="inlineStr">
+        <is>
+          <t>Manager, Human Resources (ACIPM, PHRi)</t>
+        </is>
+      </c>
+      <c r="E239" s="4" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F239" s="4" t="inlineStr">
+        <is>
+          <t>Lagos, Nigeria</t>
+        </is>
+      </c>
+      <c r="G239" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H239" s="5" t="inlineStr">
+        <is>
+          <t>Prior: Consultant, Talent Acquisition, Stanbic IBTC Capital. Two employers in sources - verify current.</t>
+        </is>
+      </c>
+      <c r="I239" s="4" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
+      <c r="J239" s="4" t="inlineStr">
         <is>
           <t>Damilare Olumeko</t>
         </is>
@@ -7935,24 +8355,52 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="2" t="inlineStr">
+      <c r="A254" s="4" t="inlineStr">
         <is>
           <t>Dariana</t>
         </is>
       </c>
-      <c r="B254" s="2" t="inlineStr">
+      <c r="B254" s="4" t="inlineStr">
         <is>
           <t>Rivera</t>
         </is>
       </c>
-      <c r="C254" s="2" t="inlineStr"/>
-      <c r="D254" s="2" t="inlineStr"/>
-      <c r="E254" s="2" t="inlineStr"/>
-      <c r="F254" s="2" t="inlineStr"/>
-      <c r="G254" s="2" t="inlineStr"/>
-      <c r="H254" s="3" t="inlineStr"/>
-      <c r="I254" s="2" t="inlineStr"/>
-      <c r="J254" s="2" t="inlineStr">
+      <c r="C254" s="4" t="inlineStr">
+        <is>
+          <t>Jacobs Entertainment, Inc.</t>
+        </is>
+      </c>
+      <c r="D254" s="4" t="inlineStr">
+        <is>
+          <t>Human Resources Manager</t>
+        </is>
+      </c>
+      <c r="E254" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F254" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G254" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H254" s="5" t="inlineStr">
+        <is>
+          <t>Background recruiting in food production.</t>
+        </is>
+      </c>
+      <c r="I254" s="4" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
+      <c r="J254" s="4" t="inlineStr">
         <is>
           <t>Dariana Rivera</t>
         </is>
@@ -9423,52 +9871,52 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="6" t="inlineStr">
+      <c r="A316" s="4" t="inlineStr">
         <is>
           <t>Drexetta</t>
         </is>
       </c>
-      <c r="B316" s="6" t="inlineStr">
+      <c r="B316" s="4" t="inlineStr">
         <is>
           <t>Perez</t>
         </is>
       </c>
-      <c r="C316" s="6" t="inlineStr">
+      <c r="C316" s="4" t="inlineStr">
         <is>
           <t>DePaul University</t>
         </is>
       </c>
-      <c r="D316" s="6" t="inlineStr">
+      <c r="D316" s="4" t="inlineStr">
         <is>
           <t>HR Professional (PHR)</t>
         </is>
       </c>
-      <c r="E316" s="6" t="inlineStr">
+      <c r="E316" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F316" s="6" t="inlineStr">
+      <c r="F316" s="4" t="inlineStr">
         <is>
           <t>Chicago, IL</t>
         </is>
       </c>
-      <c r="G316" s="6" t="inlineStr">
+      <c r="G316" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H316" s="7" t="inlineStr">
+      <c r="H316" s="5" t="inlineStr">
         <is>
           <t>Prior: Sr. HR Generalist, FreightCar America.</t>
         </is>
       </c>
-      <c r="I316" s="6" t="inlineStr">
+      <c r="I316" s="4" t="inlineStr">
         <is>
           <t>Web research</t>
         </is>
       </c>
-      <c r="J316" s="6" t="inlineStr">
+      <c r="J316" s="4" t="inlineStr">
         <is>
           <t>Drexetta Perez</t>
         </is>
@@ -9763,52 +10211,52 @@
       </c>
     </row>
     <row r="329">
-      <c r="A329" s="6" t="inlineStr">
+      <c r="A329" s="4" t="inlineStr">
         <is>
           <t>Eleni</t>
         </is>
       </c>
-      <c r="B329" s="6" t="inlineStr">
+      <c r="B329" s="4" t="inlineStr">
         <is>
           <t>Papadopoullos</t>
         </is>
       </c>
-      <c r="C329" s="6" t="inlineStr">
+      <c r="C329" s="4" t="inlineStr">
         <is>
           <t>Rockefeller Group</t>
         </is>
       </c>
-      <c r="D329" s="6" t="inlineStr">
+      <c r="D329" s="4" t="inlineStr">
         <is>
           <t>Director, Talent Acquisition &amp; HR Operations (PHR)</t>
         </is>
       </c>
-      <c r="E329" s="6" t="inlineStr">
+      <c r="E329" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F329" s="6" t="inlineStr">
+      <c r="F329" s="4" t="inlineStr">
         <is>
           <t>New York, NY</t>
         </is>
       </c>
-      <c r="G329" s="6" t="inlineStr">
+      <c r="G329" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H329" s="7" t="inlineStr">
+      <c r="H329" s="5" t="inlineStr">
         <is>
           <t>Prior: AVP Employee Relations, Industrial Bank of Japan.</t>
         </is>
       </c>
-      <c r="I329" s="6" t="inlineStr">
+      <c r="I329" s="4" t="inlineStr">
         <is>
           <t>Web research</t>
         </is>
       </c>
-      <c r="J329" s="6" t="inlineStr">
+      <c r="J329" s="4" t="inlineStr">
         <is>
           <t>Eleni Papadopoullos</t>
         </is>
@@ -10943,24 +11391,52 @@
       </c>
     </row>
     <row r="377">
-      <c r="A377" s="2" t="inlineStr">
+      <c r="A377" s="4" t="inlineStr">
         <is>
           <t>Feryal</t>
         </is>
       </c>
-      <c r="B377" s="2" t="inlineStr">
+      <c r="B377" s="4" t="inlineStr">
         <is>
           <t>Firat</t>
         </is>
       </c>
-      <c r="C377" s="2" t="inlineStr"/>
-      <c r="D377" s="2" t="inlineStr"/>
-      <c r="E377" s="2" t="inlineStr"/>
-      <c r="F377" s="2" t="inlineStr"/>
-      <c r="G377" s="2" t="inlineStr"/>
-      <c r="H377" s="3" t="inlineStr"/>
-      <c r="I377" s="2" t="inlineStr"/>
-      <c r="J377" s="2" t="inlineStr">
+      <c r="C377" s="4" t="inlineStr">
+        <is>
+          <t>Hendricks &amp; Partners (also Gold Kidney Health Plan)</t>
+        </is>
+      </c>
+      <c r="D377" s="4" t="inlineStr">
+        <is>
+          <t>Director of Human Resources</t>
+        </is>
+      </c>
+      <c r="E377" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F377" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G377" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H377" s="5" t="inlineStr">
+        <is>
+          <t>Two employers across sources; likely moved. HR since 2013, started at Pearson.</t>
+        </is>
+      </c>
+      <c r="I377" s="4" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
+      <c r="J377" s="4" t="inlineStr">
         <is>
           <t>Feryal Firat</t>
         </is>
@@ -11135,24 +11611,52 @@
       </c>
     </row>
     <row r="385">
-      <c r="A385" s="2" t="inlineStr">
+      <c r="A385" s="4" t="inlineStr">
         <is>
           <t>Galina</t>
         </is>
       </c>
-      <c r="B385" s="2" t="inlineStr">
+      <c r="B385" s="4" t="inlineStr">
         <is>
           <t>Karpinska</t>
         </is>
       </c>
-      <c r="C385" s="2" t="inlineStr"/>
-      <c r="D385" s="2" t="inlineStr"/>
-      <c r="E385" s="2" t="inlineStr"/>
-      <c r="F385" s="2" t="inlineStr"/>
-      <c r="G385" s="2" t="inlineStr"/>
-      <c r="H385" s="3" t="inlineStr"/>
-      <c r="I385" s="2" t="inlineStr"/>
-      <c r="J385" s="2" t="inlineStr">
+      <c r="C385" s="4" t="inlineStr">
+        <is>
+          <t>SOAProjects, Inc.</t>
+        </is>
+      </c>
+      <c r="D385" s="4" t="inlineStr">
+        <is>
+          <t>HR Director</t>
+        </is>
+      </c>
+      <c r="E385" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F385" s="4" t="inlineStr">
+        <is>
+          <t>SF Bay Area, CA</t>
+        </is>
+      </c>
+      <c r="G385" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H385" s="5" t="inlineStr">
+        <is>
+          <t>Prior: Aiver, Codeminders/Tristero, Luxoft. Kyiv Polytechnic background.</t>
+        </is>
+      </c>
+      <c r="I385" s="4" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
+      <c r="J385" s="4" t="inlineStr">
         <is>
           <t>Galina Karpinska</t>
         </is>
@@ -11327,24 +11831,52 @@
       </c>
     </row>
     <row r="393">
-      <c r="A393" s="2" t="inlineStr">
+      <c r="A393" s="4" t="inlineStr">
         <is>
           <t>Gifty</t>
         </is>
       </c>
-      <c r="B393" s="2" t="inlineStr">
+      <c r="B393" s="4" t="inlineStr">
         <is>
           <t>Adjei-Danso</t>
         </is>
       </c>
-      <c r="C393" s="2" t="inlineStr"/>
-      <c r="D393" s="2" t="inlineStr"/>
-      <c r="E393" s="2" t="inlineStr"/>
-      <c r="F393" s="2" t="inlineStr"/>
-      <c r="G393" s="2" t="inlineStr"/>
-      <c r="H393" s="3" t="inlineStr"/>
-      <c r="I393" s="2" t="inlineStr"/>
-      <c r="J393" s="2" t="inlineStr">
+      <c r="C393" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D393" s="4" t="inlineStr">
+        <is>
+          <t>Senior Human Resources Officer (SPHRi)</t>
+        </is>
+      </c>
+      <c r="E393" s="4" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F393" s="4" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="G393" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H393" s="5" t="inlineStr">
+        <is>
+          <t>Canadian LinkedIn profile; no employer found.</t>
+        </is>
+      </c>
+      <c r="I393" s="4" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
+      <c r="J393" s="4" t="inlineStr">
         <is>
           <t>Gifty Adjei-Danso</t>
         </is>
@@ -12503,52 +13035,52 @@
       </c>
     </row>
     <row r="442">
-      <c r="A442" s="6" t="inlineStr">
+      <c r="A442" s="4" t="inlineStr">
         <is>
           <t>Jamelia</t>
         </is>
       </c>
-      <c r="B442" s="6" t="inlineStr">
+      <c r="B442" s="4" t="inlineStr">
         <is>
           <t>Hand</t>
         </is>
       </c>
-      <c r="C442" s="6" t="inlineStr">
+      <c r="C442" s="4" t="inlineStr">
         <is>
           <t>Vantage Clinical Consulting LLC</t>
         </is>
       </c>
-      <c r="D442" s="6" t="inlineStr">
+      <c r="D442" s="4" t="inlineStr">
         <is>
           <t>Founder &amp; CEO (MHS, CADC, CODP I)</t>
         </is>
       </c>
-      <c r="E442" s="6" t="inlineStr">
+      <c r="E442" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F442" s="6" t="inlineStr">
+      <c r="F442" s="4" t="inlineStr">
         <is>
           <t>Illinois</t>
         </is>
       </c>
-      <c r="G442" s="6" t="inlineStr">
+      <c r="G442" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H442" s="7" t="inlineStr">
+      <c r="H442" s="5" t="inlineStr">
         <is>
           <t>HIGH RELEVANCE - keynotes on opioids in the workplace. Referral partner, not a benefits buyer.</t>
         </is>
       </c>
-      <c r="I442" s="6" t="inlineStr">
+      <c r="I442" s="4" t="inlineStr">
         <is>
           <t>Web research</t>
         </is>
       </c>
-      <c r="J442" s="6" t="inlineStr">
+      <c r="J442" s="4" t="inlineStr">
         <is>
           <t>Jamelia Hand</t>
         </is>
@@ -13155,24 +13687,52 @@
       </c>
     </row>
     <row r="468">
-      <c r="A468" s="2" t="inlineStr">
+      <c r="A468" s="4" t="inlineStr">
         <is>
           <t>Jennica</t>
         </is>
       </c>
-      <c r="B468" s="2" t="inlineStr">
+      <c r="B468" s="4" t="inlineStr">
         <is>
           <t>Zern</t>
         </is>
       </c>
-      <c r="C468" s="2" t="inlineStr"/>
-      <c r="D468" s="2" t="inlineStr"/>
-      <c r="E468" s="2" t="inlineStr"/>
-      <c r="F468" s="2" t="inlineStr"/>
-      <c r="G468" s="2" t="inlineStr"/>
-      <c r="H468" s="3" t="inlineStr"/>
-      <c r="I468" s="2" t="inlineStr"/>
-      <c r="J468" s="2" t="inlineStr">
+      <c r="C468" s="4" t="inlineStr">
+        <is>
+          <t>Biomerics</t>
+        </is>
+      </c>
+      <c r="D468" s="4" t="inlineStr">
+        <is>
+          <t>Human Resources (SPHR)</t>
+        </is>
+      </c>
+      <c r="E468" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F468" s="4" t="inlineStr">
+        <is>
+          <t>Utah</t>
+        </is>
+      </c>
+      <c r="G468" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H468" s="5" t="inlineStr">
+        <is>
+          <t>Medical device contract manufacturer. Prior: Vivint Solar.</t>
+        </is>
+      </c>
+      <c r="I468" s="4" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
+      <c r="J468" s="4" t="inlineStr">
         <is>
           <t>Jennica Zern</t>
         </is>
@@ -15267,52 +15827,52 @@
       </c>
     </row>
     <row r="556">
-      <c r="A556" s="6" t="inlineStr">
+      <c r="A556" s="4" t="inlineStr">
         <is>
           <t>Solange</t>
         </is>
       </c>
-      <c r="B556" s="6" t="inlineStr">
+      <c r="B556" s="4" t="inlineStr">
         <is>
           <t>Corujo</t>
         </is>
       </c>
-      <c r="C556" s="6" t="inlineStr">
+      <c r="C556" s="4" t="inlineStr">
         <is>
           <t>T-Mobile</t>
         </is>
       </c>
-      <c r="D556" s="6" t="inlineStr">
+      <c r="D556" s="4" t="inlineStr">
         <is>
           <t>Director, HR &amp; Strategic Advisor (SPHR)</t>
         </is>
       </c>
-      <c r="E556" s="6" t="inlineStr">
+      <c r="E556" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F556" s="6" t="inlineStr">
+      <c r="F556" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G556" s="6" t="inlineStr">
+      <c r="G556" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H556" s="7" t="inlineStr">
+      <c r="H556" s="5" t="inlineStr">
         <is>
           <t>Large self-insured employer - core buyer persona.</t>
         </is>
       </c>
-      <c r="I556" s="6" t="inlineStr">
+      <c r="I556" s="4" t="inlineStr">
         <is>
           <t>Web research</t>
         </is>
       </c>
-      <c r="J556" s="6" t="inlineStr">
+      <c r="J556" s="4" t="inlineStr">
         <is>
           <t>Solange Corujo</t>
         </is>
@@ -15559,52 +16119,52 @@
       </c>
     </row>
     <row r="567">
-      <c r="A567" s="6" t="inlineStr">
+      <c r="A567" s="4" t="inlineStr">
         <is>
           <t>Theresa</t>
         </is>
       </c>
-      <c r="B567" s="6" t="inlineStr">
+      <c r="B567" s="4" t="inlineStr">
         <is>
           <t>Harter-Miles</t>
         </is>
       </c>
-      <c r="C567" s="6" t="inlineStr">
+      <c r="C567" s="4" t="inlineStr">
         <is>
           <t>South Plains Community Action Association</t>
         </is>
       </c>
-      <c r="D567" s="6" t="inlineStr">
+      <c r="D567" s="4" t="inlineStr">
         <is>
           <t>Home Health Aide</t>
         </is>
       </c>
-      <c r="E567" s="6" t="inlineStr">
+      <c r="E567" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F567" s="6" t="inlineStr">
+      <c r="F567" s="4" t="inlineStr">
         <is>
           <t>Levelland, TX</t>
         </is>
       </c>
-      <c r="G567" s="6" t="inlineStr">
+      <c r="G567" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H567" s="7" t="inlineStr">
+      <c r="H567" s="5" t="inlineStr">
         <is>
           <t>NOT an HR role. Prior: Orange County Public Schools.</t>
         </is>
       </c>
-      <c r="I567" s="6" t="inlineStr">
+      <c r="I567" s="4" t="inlineStr">
         <is>
           <t>Web research</t>
         </is>
       </c>
-      <c r="J567" s="6" t="inlineStr">
+      <c r="J567" s="4" t="inlineStr">
         <is>
           <t>Theresa Harter-Miles</t>
         </is>
@@ -15707,52 +16267,52 @@
       </c>
     </row>
     <row r="572">
-      <c r="A572" s="6" t="inlineStr">
+      <c r="A572" s="4" t="inlineStr">
         <is>
           <t>Tibisay</t>
         </is>
       </c>
-      <c r="B572" s="6" t="inlineStr">
+      <c r="B572" s="4" t="inlineStr">
         <is>
           <t>Lugo</t>
         </is>
       </c>
-      <c r="C572" s="6" t="inlineStr">
+      <c r="C572" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D572" s="6" t="inlineStr">
+      <c r="D572" s="4" t="inlineStr">
         <is>
           <t>HR Business Partner (20+ yrs)</t>
         </is>
       </c>
-      <c r="E572" s="6" t="inlineStr">
+      <c r="E572" s="4" t="inlineStr">
         <is>
           <t>Unconfirmed</t>
         </is>
       </c>
-      <c r="F572" s="6" t="inlineStr">
+      <c r="F572" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G572" s="6" t="inlineStr">
+      <c r="G572" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H572" s="7" t="inlineStr">
+      <c r="H572" s="5" t="inlineStr">
         <is>
           <t>Govt/NGO/private mix. Country not confirmed.</t>
         </is>
       </c>
-      <c r="I572" s="6" t="inlineStr">
+      <c r="I572" s="4" t="inlineStr">
         <is>
           <t>Web research</t>
         </is>
       </c>
-      <c r="J572" s="6" t="inlineStr">
+      <c r="J572" s="4" t="inlineStr">
         <is>
           <t>Tibisay Lugo</t>
         </is>
@@ -15927,52 +16487,52 @@
       </c>
     </row>
     <row r="580">
-      <c r="A580" s="6" t="inlineStr">
+      <c r="A580" s="4" t="inlineStr">
         <is>
           <t>Tina</t>
         </is>
       </c>
-      <c r="B580" s="6" t="inlineStr">
+      <c r="B580" s="4" t="inlineStr">
         <is>
           <t>Gemlo</t>
         </is>
       </c>
-      <c r="C580" s="6" t="inlineStr">
+      <c r="C580" s="4" t="inlineStr">
         <is>
           <t>GRE HERC Services LLC</t>
         </is>
       </c>
-      <c r="D580" s="6" t="inlineStr">
+      <c r="D580" s="4" t="inlineStr">
         <is>
           <t>Leader, HR &amp; Communications (SPHR, SHRM-SCP)</t>
         </is>
       </c>
-      <c r="E580" s="6" t="inlineStr">
+      <c r="E580" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F580" s="6" t="inlineStr">
+      <c r="F580" s="4" t="inlineStr">
         <is>
           <t>Minneapolis, MN</t>
         </is>
       </c>
-      <c r="G580" s="6" t="inlineStr">
+      <c r="G580" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H580" s="7" t="inlineStr">
+      <c r="H580" s="5" t="inlineStr">
         <is>
           <t>HIGH RELEVANCE - prior Benefits Manager, Hazelden Betty Ford Foundation.</t>
         </is>
       </c>
-      <c r="I580" s="6" t="inlineStr">
+      <c r="I580" s="4" t="inlineStr">
         <is>
           <t>Web research</t>
         </is>
       </c>
-      <c r="J580" s="6" t="inlineStr">
+      <c r="J580" s="4" t="inlineStr">
         <is>
           <t>Tina Gemlo</t>
         </is>
@@ -16459,24 +17019,52 @@
       </c>
     </row>
     <row r="601">
-      <c r="A601" s="2" t="inlineStr">
+      <c r="A601" s="4" t="inlineStr">
         <is>
           <t>Kaitlynn</t>
         </is>
       </c>
-      <c r="B601" s="2" t="inlineStr">
+      <c r="B601" s="4" t="inlineStr">
         <is>
           <t>Sedabres</t>
         </is>
       </c>
-      <c r="C601" s="2" t="inlineStr"/>
-      <c r="D601" s="2" t="inlineStr"/>
-      <c r="E601" s="2" t="inlineStr"/>
-      <c r="F601" s="2" t="inlineStr"/>
-      <c r="G601" s="2" t="inlineStr"/>
-      <c r="H601" s="3" t="inlineStr"/>
-      <c r="I601" s="2" t="inlineStr"/>
-      <c r="J601" s="2" t="inlineStr">
+      <c r="C601" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D601" s="4" t="inlineStr">
+        <is>
+          <t>HR Leader (PhD, SPHR)</t>
+        </is>
+      </c>
+      <c r="E601" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F601" s="4" t="inlineStr">
+        <is>
+          <t>Minneapolis-St. Paul, MN</t>
+        </is>
+      </c>
+      <c r="G601" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H601" s="5" t="inlineStr">
+        <is>
+          <t>Learning &amp; development, instructional design, recruiting. No employer found.</t>
+        </is>
+      </c>
+      <c r="I601" s="4" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
+      <c r="J601" s="4" t="inlineStr">
         <is>
           <t>Kaitlynn Sedabres</t>
         </is>
@@ -16699,24 +17287,48 @@
       </c>
     </row>
     <row r="611">
-      <c r="A611" s="2" t="inlineStr">
+      <c r="A611" s="4" t="inlineStr">
         <is>
           <t>LaDaura</t>
         </is>
       </c>
-      <c r="B611" s="2" t="inlineStr">
+      <c r="B611" s="4" t="inlineStr">
         <is>
           <t>Perryman</t>
         </is>
       </c>
-      <c r="C611" s="2" t="inlineStr"/>
-      <c r="D611" s="2" t="inlineStr"/>
-      <c r="E611" s="2" t="inlineStr"/>
-      <c r="F611" s="2" t="inlineStr"/>
-      <c r="G611" s="2" t="inlineStr"/>
-      <c r="H611" s="3" t="inlineStr"/>
-      <c r="I611" s="2" t="inlineStr"/>
-      <c r="J611" s="2" t="inlineStr">
+      <c r="C611" s="4" t="inlineStr">
+        <is>
+          <t>Independent</t>
+        </is>
+      </c>
+      <c r="D611" s="4" t="inlineStr">
+        <is>
+          <t>Human Resources Consultant (MA HR Mgmt)</t>
+        </is>
+      </c>
+      <c r="E611" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F611" s="4" t="inlineStr">
+        <is>
+          <t>Aurora, CO</t>
+        </is>
+      </c>
+      <c r="G611" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H611" s="5" t="inlineStr"/>
+      <c r="I611" s="4" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
+      <c r="J611" s="4" t="inlineStr">
         <is>
           <t>LaDaura Perryman</t>
         </is>
@@ -16771,24 +17383,52 @@
       </c>
     </row>
     <row r="614">
-      <c r="A614" s="2" t="inlineStr">
+      <c r="A614" s="4" t="inlineStr">
         <is>
           <t>Latocha</t>
         </is>
       </c>
-      <c r="B614" s="2" t="inlineStr">
+      <c r="B614" s="4" t="inlineStr">
         <is>
           <t>Smalls</t>
         </is>
       </c>
-      <c r="C614" s="2" t="inlineStr"/>
-      <c r="D614" s="2" t="inlineStr"/>
-      <c r="E614" s="2" t="inlineStr"/>
-      <c r="F614" s="2" t="inlineStr"/>
-      <c r="G614" s="2" t="inlineStr"/>
-      <c r="H614" s="3" t="inlineStr"/>
-      <c r="I614" s="2" t="inlineStr"/>
-      <c r="J614" s="2" t="inlineStr">
+      <c r="C614" s="4" t="inlineStr">
+        <is>
+          <t>GatherVacations</t>
+        </is>
+      </c>
+      <c r="D614" s="4" t="inlineStr">
+        <is>
+          <t>Human Resources Manager</t>
+        </is>
+      </c>
+      <c r="E614" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F614" s="4" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL</t>
+        </is>
+      </c>
+      <c r="G614" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H614" s="5" t="inlineStr">
+        <is>
+          <t>Payroll, benefits and compliance focus. MBA HR, Webster Univ.</t>
+        </is>
+      </c>
+      <c r="I614" s="4" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
+      <c r="J614" s="4" t="inlineStr">
         <is>
           <t>Latocha Smalls</t>
         </is>
@@ -17203,24 +17843,52 @@
       </c>
     </row>
     <row r="632">
-      <c r="A632" s="2" t="inlineStr">
+      <c r="A632" s="4" t="inlineStr">
         <is>
           <t>Marquita</t>
         </is>
       </c>
-      <c r="B632" s="2" t="inlineStr">
+      <c r="B632" s="4" t="inlineStr">
         <is>
           <t>Reynolds</t>
         </is>
       </c>
-      <c r="C632" s="2" t="inlineStr"/>
-      <c r="D632" s="2" t="inlineStr"/>
-      <c r="E632" s="2" t="inlineStr"/>
-      <c r="F632" s="2" t="inlineStr"/>
-      <c r="G632" s="2" t="inlineStr"/>
-      <c r="H632" s="3" t="inlineStr"/>
-      <c r="I632" s="2" t="inlineStr"/>
-      <c r="J632" s="2" t="inlineStr">
+      <c r="C632" s="4" t="inlineStr">
+        <is>
+          <t>Onin Staffing (one of several candidates)</t>
+        </is>
+      </c>
+      <c r="D632" s="4" t="inlineStr">
+        <is>
+          <t>HR Professional (MBA, PHR)</t>
+        </is>
+      </c>
+      <c r="E632" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F632" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G632" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H632" s="5" t="inlineStr">
+        <is>
+          <t>10+ LinkedIn profiles with this name - not resolvable.</t>
+        </is>
+      </c>
+      <c r="I632" s="4" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
+      <c r="J632" s="4" t="inlineStr">
         <is>
           <t>Marquita Reynolds</t>
         </is>
@@ -17635,24 +18303,52 @@
       </c>
     </row>
     <row r="650">
-      <c r="A650" s="2" t="inlineStr">
+      <c r="A650" s="4" t="inlineStr">
         <is>
           <t>Monica</t>
         </is>
       </c>
-      <c r="B650" s="2" t="inlineStr">
+      <c r="B650" s="4" t="inlineStr">
         <is>
           <t>Lynghaug</t>
         </is>
       </c>
-      <c r="C650" s="2" t="inlineStr"/>
-      <c r="D650" s="2" t="inlineStr"/>
-      <c r="E650" s="2" t="inlineStr"/>
-      <c r="F650" s="2" t="inlineStr"/>
-      <c r="G650" s="2" t="inlineStr"/>
-      <c r="H650" s="3" t="inlineStr"/>
-      <c r="I650" s="2" t="inlineStr"/>
-      <c r="J650" s="2" t="inlineStr">
+      <c r="C650" s="4" t="inlineStr">
+        <is>
+          <t>Skyline</t>
+        </is>
+      </c>
+      <c r="D650" s="4" t="inlineStr">
+        <is>
+          <t>Benefits Administrator (M.S., SHRM-CP, PHR)</t>
+        </is>
+      </c>
+      <c r="E650" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F650" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G650" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H650" s="5" t="inlineStr">
+        <is>
+          <t>Building materials. Also HR Consultant at HR Streamlined Solutions; listed at Armbruster Executive &amp; Employee Benefits.</t>
+        </is>
+      </c>
+      <c r="I650" s="4" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
+      <c r="J650" s="4" t="inlineStr">
         <is>
           <t>Monica Lynghaug</t>
         </is>
@@ -18763,24 +19459,52 @@
       </c>
     </row>
     <row r="697">
-      <c r="A697" s="2" t="inlineStr">
+      <c r="A697" s="4" t="inlineStr">
         <is>
           <t>Tosin</t>
         </is>
       </c>
-      <c r="B697" s="2" t="inlineStr">
+      <c r="B697" s="4" t="inlineStr">
         <is>
           <t>Mayowa</t>
         </is>
       </c>
-      <c r="C697" s="2" t="inlineStr"/>
-      <c r="D697" s="2" t="inlineStr"/>
-      <c r="E697" s="2" t="inlineStr"/>
-      <c r="F697" s="2" t="inlineStr"/>
-      <c r="G697" s="2" t="inlineStr"/>
-      <c r="H697" s="3" t="inlineStr"/>
-      <c r="I697" s="2" t="inlineStr"/>
-      <c r="J697" s="2" t="inlineStr">
+      <c r="C697" s="4" t="inlineStr">
+        <is>
+          <t>National Parks Conservation Association</t>
+        </is>
+      </c>
+      <c r="D697" s="4" t="inlineStr">
+        <is>
+          <t>Human Resources Director</t>
+        </is>
+      </c>
+      <c r="E697" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F697" s="4" t="inlineStr">
+        <is>
+          <t>Washington, DC</t>
+        </is>
+      </c>
+      <c r="G697" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H697" s="5" t="inlineStr">
+        <is>
+          <t>Since 2023. PRIOR: Manager of Benefits &amp; HR, Edison Electric Institute.</t>
+        </is>
+      </c>
+      <c r="I697" s="4" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
+      <c r="J697" s="4" t="inlineStr">
         <is>
           <t>Tosin Mayowa</t>
         </is>
@@ -19531,52 +20255,52 @@
       </c>
     </row>
     <row r="729">
-      <c r="A729" s="6" t="inlineStr">
+      <c r="A729" s="4" t="inlineStr">
         <is>
           <t>Jessica</t>
         </is>
       </c>
-      <c r="B729" s="6" t="inlineStr">
+      <c r="B729" s="4" t="inlineStr">
         <is>
           <t>Hulsey</t>
         </is>
       </c>
-      <c r="C729" s="6" t="inlineStr">
+      <c r="C729" s="4" t="inlineStr">
         <is>
           <t>AMBIGUOUS - two candidates</t>
         </is>
       </c>
-      <c r="D729" s="6" t="inlineStr">
+      <c r="D729" s="4" t="inlineStr">
         <is>
           <t>(a) Founder, Addiction Policy Forum  (b) Jessica-Rae Hulsey PHR, Excel HR Services</t>
         </is>
       </c>
-      <c r="E729" s="6" t="inlineStr">
+      <c r="E729" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F729" s="6" t="inlineStr">
+      <c r="F729" s="4" t="inlineStr">
         <is>
           <t>(a) DC  (b) Dallas-Fort Worth</t>
         </is>
       </c>
-      <c r="G729" s="6" t="inlineStr">
+      <c r="G729" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H729" s="7" t="inlineStr">
+      <c r="H729" s="5" t="inlineStr">
         <is>
           <t>Candidate (a) is a national SUD nonprofit founder with lived experience - verify which attended before any outreach.</t>
         </is>
       </c>
-      <c r="I729" s="6" t="inlineStr">
+      <c r="I729" s="4" t="inlineStr">
         <is>
           <t>Web research</t>
         </is>
       </c>
-      <c r="J729" s="6" t="inlineStr">
+      <c r="J729" s="4" t="inlineStr">
         <is>
           <t>Jessica Hulsey</t>
         </is>
@@ -20231,48 +20955,48 @@
       </c>
     </row>
     <row r="757">
-      <c r="A757" s="6" t="inlineStr">
+      <c r="A757" s="4" t="inlineStr">
         <is>
           <t>Jorie</t>
         </is>
       </c>
-      <c r="B757" s="6" t="inlineStr">
+      <c r="B757" s="4" t="inlineStr">
         <is>
           <t>Zakutansky</t>
         </is>
       </c>
-      <c r="C757" s="6" t="inlineStr">
+      <c r="C757" s="4" t="inlineStr">
         <is>
           <t>Ariens Company (AriensCo)</t>
         </is>
       </c>
-      <c r="D757" s="6" t="inlineStr">
+      <c r="D757" s="4" t="inlineStr">
         <is>
           <t>Sr. HR Business Partner</t>
         </is>
       </c>
-      <c r="E757" s="6" t="inlineStr">
+      <c r="E757" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F757" s="6" t="inlineStr">
+      <c r="F757" s="4" t="inlineStr">
         <is>
           <t>Brillion, WI</t>
         </is>
       </c>
-      <c r="G757" s="6" t="inlineStr">
+      <c r="G757" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H757" s="7" t="inlineStr"/>
-      <c r="I757" s="6" t="inlineStr">
+      <c r="H757" s="5" t="inlineStr"/>
+      <c r="I757" s="4" t="inlineStr">
         <is>
           <t>Web research</t>
         </is>
       </c>
-      <c r="J757" s="6" t="inlineStr">
+      <c r="J757" s="4" t="inlineStr">
         <is>
           <t>Jorie Zakutansky</t>
         </is>
@@ -20447,24 +21171,48 @@
       </c>
     </row>
     <row r="765">
-      <c r="A765" s="2" t="inlineStr">
+      <c r="A765" s="4" t="inlineStr">
         <is>
           <t>Karri</t>
         </is>
       </c>
-      <c r="B765" s="2" t="inlineStr">
+      <c r="B765" s="4" t="inlineStr">
         <is>
           <t>Markle</t>
         </is>
       </c>
-      <c r="C765" s="2" t="inlineStr"/>
-      <c r="D765" s="2" t="inlineStr"/>
-      <c r="E765" s="2" t="inlineStr"/>
-      <c r="F765" s="2" t="inlineStr"/>
-      <c r="G765" s="2" t="inlineStr"/>
-      <c r="H765" s="3" t="inlineStr"/>
-      <c r="I765" s="2" t="inlineStr"/>
-      <c r="J765" s="2" t="inlineStr">
+      <c r="C765" s="4" t="inlineStr">
+        <is>
+          <t>Virginia Department of Health</t>
+        </is>
+      </c>
+      <c r="D765" s="4" t="inlineStr">
+        <is>
+          <t>Human Resources Generalist</t>
+        </is>
+      </c>
+      <c r="E765" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F765" s="4" t="inlineStr">
+        <is>
+          <t>Virginia</t>
+        </is>
+      </c>
+      <c r="G765" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H765" s="5" t="inlineStr"/>
+      <c r="I765" s="4" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
+      <c r="J765" s="4" t="inlineStr">
         <is>
           <t>Karri Markle</t>
         </is>
@@ -20831,48 +21579,104 @@
       </c>
     </row>
     <row r="781">
-      <c r="A781" s="2" t="inlineStr">
+      <c r="A781" s="4" t="inlineStr">
         <is>
           <t>Lekisha</t>
         </is>
       </c>
-      <c r="B781" s="2" t="inlineStr">
+      <c r="B781" s="4" t="inlineStr">
         <is>
           <t>Felix</t>
         </is>
       </c>
-      <c r="C781" s="2" t="inlineStr"/>
-      <c r="D781" s="2" t="inlineStr"/>
-      <c r="E781" s="2" t="inlineStr"/>
-      <c r="F781" s="2" t="inlineStr"/>
-      <c r="G781" s="2" t="inlineStr"/>
-      <c r="H781" s="3" t="inlineStr"/>
-      <c r="I781" s="2" t="inlineStr"/>
-      <c r="J781" s="2" t="inlineStr">
+      <c r="C781" s="4" t="inlineStr">
+        <is>
+          <t>Town of Chapel Hill, NC</t>
+        </is>
+      </c>
+      <c r="D781" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E781" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F781" s="4" t="inlineStr">
+        <is>
+          <t>Chapel Hill, NC</t>
+        </is>
+      </c>
+      <c r="G781" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H781" s="5" t="inlineStr">
+        <is>
+          <t>Role not confirmed as HR.</t>
+        </is>
+      </c>
+      <c r="I781" s="4" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
+      <c r="J781" s="4" t="inlineStr">
         <is>
           <t>Lekisha Felix</t>
         </is>
       </c>
     </row>
     <row r="782">
-      <c r="A782" s="2" t="inlineStr">
+      <c r="A782" s="4" t="inlineStr">
         <is>
           <t>Lesia</t>
         </is>
       </c>
-      <c r="B782" s="2" t="inlineStr">
+      <c r="B782" s="4" t="inlineStr">
         <is>
           <t>Van Den Heuvel</t>
         </is>
       </c>
-      <c r="C782" s="2" t="inlineStr"/>
-      <c r="D782" s="2" t="inlineStr"/>
-      <c r="E782" s="2" t="inlineStr"/>
-      <c r="F782" s="2" t="inlineStr"/>
-      <c r="G782" s="2" t="inlineStr"/>
-      <c r="H782" s="3" t="inlineStr"/>
-      <c r="I782" s="2" t="inlineStr"/>
-      <c r="J782" s="2" t="inlineStr">
+      <c r="C782" s="4" t="inlineStr">
+        <is>
+          <t>Parametric Solutions, Inc.</t>
+        </is>
+      </c>
+      <c r="D782" s="4" t="inlineStr">
+        <is>
+          <t>Human Resources Manager (SPHR)</t>
+        </is>
+      </c>
+      <c r="E782" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F782" s="4" t="inlineStr">
+        <is>
+          <t>Jupiter, FL</t>
+        </is>
+      </c>
+      <c r="G782" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H782" s="5" t="inlineStr">
+        <is>
+          <t>Aerospace engineering firm.</t>
+        </is>
+      </c>
+      <c r="I782" s="4" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
+      <c r="J782" s="4" t="inlineStr">
         <is>
           <t>Lesia Van Den Heuvel</t>
         </is>
@@ -21407,24 +22211,52 @@
       </c>
     </row>
     <row r="805">
-      <c r="A805" s="2" t="inlineStr">
+      <c r="A805" s="4" t="inlineStr">
         <is>
           <t>Ken</t>
         </is>
       </c>
-      <c r="B805" s="2" t="inlineStr">
+      <c r="B805" s="4" t="inlineStr">
         <is>
           <t>DeCoteau</t>
         </is>
       </c>
-      <c r="C805" s="2" t="inlineStr"/>
-      <c r="D805" s="2" t="inlineStr"/>
-      <c r="E805" s="2" t="inlineStr"/>
-      <c r="F805" s="2" t="inlineStr"/>
-      <c r="G805" s="2" t="inlineStr"/>
-      <c r="H805" s="3" t="inlineStr"/>
-      <c r="I805" s="2" t="inlineStr"/>
-      <c r="J805" s="2" t="inlineStr">
+      <c r="C805" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D805" s="4" t="inlineStr">
+        <is>
+          <t>HR / DEIB Leader (CDP, PHR)</t>
+        </is>
+      </c>
+      <c r="E805" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F805" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G805" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H805" s="5" t="inlineStr">
+        <is>
+          <t>10+ yrs; corporate and military. Founded ERGs in public and private sector. No current employer found.</t>
+        </is>
+      </c>
+      <c r="I805" s="4" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
+      <c r="J805" s="4" t="inlineStr">
         <is>
           <t>Ken DeCoteau</t>
         </is>
@@ -21479,124 +22311,152 @@
       </c>
     </row>
     <row r="808">
-      <c r="A808" s="6" t="inlineStr">
+      <c r="A808" s="4" t="inlineStr">
         <is>
           <t>Kerdetra</t>
         </is>
       </c>
-      <c r="B808" s="6" t="inlineStr">
+      <c r="B808" s="4" t="inlineStr">
         <is>
           <t>Osborne</t>
         </is>
       </c>
-      <c r="C808" s="6" t="inlineStr">
+      <c r="C808" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D808" s="6" t="inlineStr">
-        <is>
-          <t>HR (HR.com member profile)</t>
-        </is>
-      </c>
-      <c r="E808" s="6" t="inlineStr">
-        <is>
-          <t>Unconfirmed</t>
-        </is>
-      </c>
-      <c r="F808" s="6" t="inlineStr">
+      <c r="D808" s="4" t="inlineStr">
+        <is>
+          <t>HR Technology Leader (20+ yrs)</t>
+        </is>
+      </c>
+      <c r="E808" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F808" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G808" s="6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H808" s="7" t="inlineStr">
-        <is>
-          <t>No employer found.</t>
-        </is>
-      </c>
-      <c r="I808" s="6" t="inlineStr">
+      <c r="G808" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H808" s="5" t="inlineStr">
+        <is>
+          <t>Global HR systems implementation across multiple platforms. Employer still not found.</t>
+        </is>
+      </c>
+      <c r="I808" s="4" t="inlineStr">
         <is>
           <t>Web research</t>
         </is>
       </c>
-      <c r="J808" s="6" t="inlineStr">
+      <c r="J808" s="4" t="inlineStr">
         <is>
           <t>Kerdetra Osborne</t>
         </is>
       </c>
     </row>
     <row r="809">
-      <c r="A809" s="2" t="inlineStr">
+      <c r="A809" s="4" t="inlineStr">
         <is>
           <t>Kerri</t>
         </is>
       </c>
-      <c r="B809" s="2" t="inlineStr">
+      <c r="B809" s="4" t="inlineStr">
         <is>
           <t>Brach</t>
         </is>
       </c>
-      <c r="C809" s="2" t="inlineStr"/>
-      <c r="D809" s="2" t="inlineStr"/>
-      <c r="E809" s="2" t="inlineStr"/>
-      <c r="F809" s="2" t="inlineStr"/>
-      <c r="G809" s="2" t="inlineStr"/>
-      <c r="H809" s="3" t="inlineStr"/>
-      <c r="I809" s="2" t="inlineStr"/>
-      <c r="J809" s="2" t="inlineStr">
+      <c r="C809" s="4" t="inlineStr">
+        <is>
+          <t>Manning Elliott LLP</t>
+        </is>
+      </c>
+      <c r="D809" s="4" t="inlineStr">
+        <is>
+          <t>Director of Human Resources</t>
+        </is>
+      </c>
+      <c r="E809" s="4" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F809" s="4" t="inlineStr">
+        <is>
+          <t>Vancouver, BC, Canada</t>
+        </is>
+      </c>
+      <c r="G809" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H809" s="5" t="inlineStr">
+        <is>
+          <t>20+ yrs HR &amp; ops across professional services, IT, hospitality.</t>
+        </is>
+      </c>
+      <c r="I809" s="4" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
+      <c r="J809" s="4" t="inlineStr">
         <is>
           <t>Kerri Brach</t>
         </is>
       </c>
     </row>
     <row r="810">
-      <c r="A810" s="6" t="inlineStr">
+      <c r="A810" s="4" t="inlineStr">
         <is>
           <t>Kerri</t>
         </is>
       </c>
-      <c r="B810" s="6" t="inlineStr">
+      <c r="B810" s="4" t="inlineStr">
         <is>
           <t>Pierceson</t>
         </is>
       </c>
-      <c r="C810" s="6" t="inlineStr">
+      <c r="C810" s="4" t="inlineStr">
         <is>
           <t>VeriFacts, LLC</t>
         </is>
       </c>
-      <c r="D810" s="6" t="inlineStr">
+      <c r="D810" s="4" t="inlineStr">
         <is>
           <t>Director of Labor Relations</t>
         </is>
       </c>
-      <c r="E810" s="6" t="inlineStr">
+      <c r="E810" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F810" s="6" t="inlineStr">
+      <c r="F810" s="4" t="inlineStr">
         <is>
           <t>Sterling, VA</t>
         </is>
       </c>
-      <c r="G810" s="6" t="inlineStr">
+      <c r="G810" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H810" s="7" t="inlineStr"/>
-      <c r="I810" s="6" t="inlineStr">
+      <c r="H810" s="5" t="inlineStr"/>
+      <c r="I810" s="4" t="inlineStr">
         <is>
           <t>Web research</t>
         </is>
       </c>
-      <c r="J810" s="6" t="inlineStr">
+      <c r="J810" s="4" t="inlineStr">
         <is>
           <t>Kerri Pierceson</t>
         </is>
@@ -22011,24 +22871,52 @@
       </c>
     </row>
     <row r="828">
-      <c r="A828" s="2" t="inlineStr">
+      <c r="A828" s="4" t="inlineStr">
         <is>
           <t>Kraig</t>
         </is>
       </c>
-      <c r="B828" s="2" t="inlineStr">
+      <c r="B828" s="4" t="inlineStr">
         <is>
           <t>Kistinger</t>
         </is>
       </c>
-      <c r="C828" s="2" t="inlineStr"/>
-      <c r="D828" s="2" t="inlineStr"/>
-      <c r="E828" s="2" t="inlineStr"/>
-      <c r="F828" s="2" t="inlineStr"/>
-      <c r="G828" s="2" t="inlineStr"/>
-      <c r="H828" s="3" t="inlineStr"/>
-      <c r="I828" s="2" t="inlineStr"/>
-      <c r="J828" s="2" t="inlineStr">
+      <c r="C828" s="4" t="inlineStr">
+        <is>
+          <t>National Tube Supply</t>
+        </is>
+      </c>
+      <c r="D828" s="4" t="inlineStr">
+        <is>
+          <t>Director of Human Resources (SPHR, MBA)</t>
+        </is>
+      </c>
+      <c r="E828" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F828" s="4" t="inlineStr">
+        <is>
+          <t>Chicago, IL</t>
+        </is>
+      </c>
+      <c r="G828" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H828" s="5" t="inlineStr">
+        <is>
+          <t>Full HR scope across 8 locations. SHRM24 speaker. 25+ yrs.</t>
+        </is>
+      </c>
+      <c r="I828" s="4" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
+      <c r="J828" s="4" t="inlineStr">
         <is>
           <t>Kraig Kistinger</t>
         </is>
@@ -22803,24 +23691,48 @@
       </c>
     </row>
     <row r="861">
-      <c r="A861" s="2" t="inlineStr">
+      <c r="A861" s="4" t="inlineStr">
         <is>
           <t>Lucinda</t>
         </is>
       </c>
-      <c r="B861" s="2" t="inlineStr">
+      <c r="B861" s="4" t="inlineStr">
         <is>
           <t>Gaisor</t>
         </is>
       </c>
-      <c r="C861" s="2" t="inlineStr"/>
-      <c r="D861" s="2" t="inlineStr"/>
-      <c r="E861" s="2" t="inlineStr"/>
-      <c r="F861" s="2" t="inlineStr"/>
-      <c r="G861" s="2" t="inlineStr"/>
-      <c r="H861" s="3" t="inlineStr"/>
-      <c r="I861" s="2" t="inlineStr"/>
-      <c r="J861" s="2" t="inlineStr">
+      <c r="C861" s="4" t="inlineStr">
+        <is>
+          <t>City of Alexandria, Virginia</t>
+        </is>
+      </c>
+      <c r="D861" s="4" t="inlineStr">
+        <is>
+          <t>HR Analyst</t>
+        </is>
+      </c>
+      <c r="E861" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F861" s="4" t="inlineStr">
+        <is>
+          <t>Alexandria, VA</t>
+        </is>
+      </c>
+      <c r="G861" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H861" s="5" t="inlineStr"/>
+      <c r="I861" s="4" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
+      <c r="J861" s="4" t="inlineStr">
         <is>
           <t>Lucinda Gaisor</t>
         </is>
@@ -22971,24 +23883,52 @@
       </c>
     </row>
     <row r="868">
-      <c r="A868" s="2" t="inlineStr">
+      <c r="A868" s="4" t="inlineStr">
         <is>
           <t>Mahtab</t>
         </is>
       </c>
-      <c r="B868" s="2" t="inlineStr">
+      <c r="B868" s="4" t="inlineStr">
         <is>
           <t>Peimany</t>
         </is>
       </c>
-      <c r="C868" s="2" t="inlineStr"/>
-      <c r="D868" s="2" t="inlineStr"/>
-      <c r="E868" s="2" t="inlineStr"/>
-      <c r="F868" s="2" t="inlineStr"/>
-      <c r="G868" s="2" t="inlineStr"/>
-      <c r="H868" s="3" t="inlineStr"/>
-      <c r="I868" s="2" t="inlineStr"/>
-      <c r="J868" s="2" t="inlineStr">
+      <c r="C868" s="4" t="inlineStr">
+        <is>
+          <t>DoubleStar, Inc. (also Frantz Dental)</t>
+        </is>
+      </c>
+      <c r="D868" s="4" t="inlineStr">
+        <is>
+          <t>HR / Recruiting (MBA, PHR, SHRM-CP)</t>
+        </is>
+      </c>
+      <c r="E868" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F868" s="4" t="inlineStr">
+        <is>
+          <t>Pennsylvania</t>
+        </is>
+      </c>
+      <c r="G868" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H868" s="5" t="inlineStr">
+        <is>
+          <t>Two employers across sources. Prior: Grange Insurance, Macy's.</t>
+        </is>
+      </c>
+      <c r="I868" s="4" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
+      <c r="J868" s="4" t="inlineStr">
         <is>
           <t>Mahtab Peimany</t>
         </is>
@@ -23523,24 +24463,52 @@
       </c>
     </row>
     <row r="891">
-      <c r="A891" s="2" t="inlineStr">
+      <c r="A891" s="4" t="inlineStr">
         <is>
           <t>Melicia</t>
         </is>
       </c>
-      <c r="B891" s="2" t="inlineStr">
+      <c r="B891" s="4" t="inlineStr">
         <is>
           <t>McCain</t>
         </is>
       </c>
-      <c r="C891" s="2" t="inlineStr"/>
-      <c r="D891" s="2" t="inlineStr"/>
-      <c r="E891" s="2" t="inlineStr"/>
-      <c r="F891" s="2" t="inlineStr"/>
-      <c r="G891" s="2" t="inlineStr"/>
-      <c r="H891" s="3" t="inlineStr"/>
-      <c r="I891" s="2" t="inlineStr"/>
-      <c r="J891" s="2" t="inlineStr">
+      <c r="C891" s="4" t="inlineStr">
+        <is>
+          <t>Beazer Homes</t>
+        </is>
+      </c>
+      <c r="D891" s="4" t="inlineStr">
+        <is>
+          <t>HR Professional</t>
+        </is>
+      </c>
+      <c r="E891" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F891" s="4" t="inlineStr">
+        <is>
+          <t>Charlotte, NC</t>
+        </is>
+      </c>
+      <c r="G891" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H891" s="5" t="inlineStr">
+        <is>
+          <t>PRIOR: HR Business Partner at OrthoCarolina (healthcare). Homebuilder - construction-adjacent.</t>
+        </is>
+      </c>
+      <c r="I891" s="4" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
+      <c r="J891" s="4" t="inlineStr">
         <is>
           <t>Melicia McCain</t>
         </is>
@@ -23691,24 +24659,52 @@
       </c>
     </row>
     <row r="898">
-      <c r="A898" s="2" t="inlineStr">
+      <c r="A898" s="4" t="inlineStr">
         <is>
           <t>Melissa</t>
         </is>
       </c>
-      <c r="B898" s="2" t="inlineStr">
+      <c r="B898" s="4" t="inlineStr">
         <is>
           <t>Henowitz</t>
         </is>
       </c>
-      <c r="C898" s="2" t="inlineStr"/>
-      <c r="D898" s="2" t="inlineStr"/>
-      <c r="E898" s="2" t="inlineStr"/>
-      <c r="F898" s="2" t="inlineStr"/>
-      <c r="G898" s="2" t="inlineStr"/>
-      <c r="H898" s="3" t="inlineStr"/>
-      <c r="I898" s="2" t="inlineStr"/>
-      <c r="J898" s="2" t="inlineStr">
+      <c r="C898" s="4" t="inlineStr">
+        <is>
+          <t>Town of West Hartford / Hartford-Bloomfield Health District</t>
+        </is>
+      </c>
+      <c r="D898" s="4" t="inlineStr">
+        <is>
+          <t>HR Specialist</t>
+        </is>
+      </c>
+      <c r="E898" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F898" s="4" t="inlineStr">
+        <is>
+          <t>West Hartford, CT</t>
+        </is>
+      </c>
+      <c r="G898" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H898" s="5" t="inlineStr">
+        <is>
+          <t>Prior: HR Business Partner, Pratt &amp; Whitney.</t>
+        </is>
+      </c>
+      <c r="I898" s="4" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
+      <c r="J898" s="4" t="inlineStr">
         <is>
           <t>Melissa Henowitz</t>
         </is>
@@ -23763,52 +24759,52 @@
       </c>
     </row>
     <row r="901">
-      <c r="A901" s="6" t="inlineStr">
+      <c r="A901" s="4" t="inlineStr">
         <is>
           <t>Melissa</t>
         </is>
       </c>
-      <c r="B901" s="6" t="inlineStr">
+      <c r="B901" s="4" t="inlineStr">
         <is>
           <t>Lupisella-Kaplan</t>
         </is>
       </c>
-      <c r="C901" s="6" t="inlineStr">
+      <c r="C901" s="4" t="inlineStr">
         <is>
           <t>Baptist Health</t>
         </is>
       </c>
-      <c r="D901" s="6" t="inlineStr">
+      <c r="D901" s="4" t="inlineStr">
         <is>
           <t>Manager, Human Resources (PHR)</t>
         </is>
       </c>
-      <c r="E901" s="6" t="inlineStr">
+      <c r="E901" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F901" s="6" t="inlineStr">
+      <c r="F901" s="4" t="inlineStr">
         <is>
           <t>Miami, FL</t>
         </is>
       </c>
-      <c r="G901" s="6" t="inlineStr">
+      <c r="G901" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H901" s="7" t="inlineStr">
+      <c r="H901" s="5" t="inlineStr">
         <is>
           <t>Large self-insured health system.</t>
         </is>
       </c>
-      <c r="I901" s="6" t="inlineStr">
+      <c r="I901" s="4" t="inlineStr">
         <is>
           <t>Web research</t>
         </is>
       </c>
-      <c r="J901" s="6" t="inlineStr">
+      <c r="J901" s="4" t="inlineStr">
         <is>
           <t>Melissa Lupisella-Kaplan</t>
         </is>
@@ -23935,24 +24931,48 @@
       </c>
     </row>
     <row r="907">
-      <c r="A907" s="2" t="inlineStr">
+      <c r="A907" s="4" t="inlineStr">
         <is>
           <t>Meranda</t>
         </is>
       </c>
-      <c r="B907" s="2" t="inlineStr">
+      <c r="B907" s="4" t="inlineStr">
         <is>
           <t>Tho</t>
         </is>
       </c>
-      <c r="C907" s="2" t="inlineStr"/>
-      <c r="D907" s="2" t="inlineStr"/>
-      <c r="E907" s="2" t="inlineStr"/>
-      <c r="F907" s="2" t="inlineStr"/>
-      <c r="G907" s="2" t="inlineStr"/>
-      <c r="H907" s="3" t="inlineStr"/>
-      <c r="I907" s="2" t="inlineStr"/>
-      <c r="J907" s="2" t="inlineStr">
+      <c r="C907" s="4" t="inlineStr">
+        <is>
+          <t>Orb Group</t>
+        </is>
+      </c>
+      <c r="D907" s="4" t="inlineStr">
+        <is>
+          <t>HR Manager, AMER (PHR)</t>
+        </is>
+      </c>
+      <c r="E907" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F907" s="4" t="inlineStr">
+        <is>
+          <t>San Diego, CA</t>
+        </is>
+      </c>
+      <c r="G907" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H907" s="5" t="inlineStr"/>
+      <c r="I907" s="4" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
+      <c r="J907" s="4" t="inlineStr">
         <is>
           <t>Meranda Tho</t>
         </is>
@@ -24007,104 +25027,104 @@
       </c>
     </row>
     <row r="910">
-      <c r="A910" s="6" t="inlineStr">
+      <c r="A910" s="4" t="inlineStr">
         <is>
           <t>Meredith</t>
         </is>
       </c>
-      <c r="B910" s="6" t="inlineStr">
+      <c r="B910" s="4" t="inlineStr">
         <is>
           <t>Gorniak</t>
         </is>
       </c>
-      <c r="C910" s="6" t="inlineStr">
+      <c r="C910" s="4" t="inlineStr">
         <is>
           <t>Academy of General Dentistry</t>
         </is>
       </c>
-      <c r="D910" s="6" t="inlineStr">
+      <c r="D910" s="4" t="inlineStr">
         <is>
           <t>HR Director (MSHRM, SPHR)</t>
         </is>
       </c>
-      <c r="E910" s="6" t="inlineStr">
+      <c r="E910" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F910" s="6" t="inlineStr">
+      <c r="F910" s="4" t="inlineStr">
         <is>
           <t>Chicago, IL</t>
         </is>
       </c>
-      <c r="G910" s="6" t="inlineStr">
+      <c r="G910" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H910" s="7" t="inlineStr">
+      <c r="H910" s="5" t="inlineStr">
         <is>
           <t>Prior: HR Director, Regular Baptist Ministries (13 yrs).</t>
         </is>
       </c>
-      <c r="I910" s="6" t="inlineStr">
+      <c r="I910" s="4" t="inlineStr">
         <is>
           <t>Web research</t>
         </is>
       </c>
-      <c r="J910" s="6" t="inlineStr">
+      <c r="J910" s="4" t="inlineStr">
         <is>
           <t>Meredith Gorniak</t>
         </is>
       </c>
     </row>
     <row r="911">
-      <c r="A911" s="6" t="inlineStr">
+      <c r="A911" s="4" t="inlineStr">
         <is>
           <t>Meredith</t>
         </is>
       </c>
-      <c r="B911" s="6" t="inlineStr">
+      <c r="B911" s="4" t="inlineStr">
         <is>
           <t>Hicks-Ogburn</t>
         </is>
       </c>
-      <c r="C911" s="6" t="inlineStr">
+      <c r="C911" s="4" t="inlineStr">
         <is>
           <t>Tufts University</t>
         </is>
       </c>
-      <c r="D911" s="6" t="inlineStr">
+      <c r="D911" s="4" t="inlineStr">
         <is>
           <t>Talent Acquisition Specialist</t>
         </is>
       </c>
-      <c r="E911" s="6" t="inlineStr">
+      <c r="E911" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F911" s="6" t="inlineStr">
+      <c r="F911" s="4" t="inlineStr">
         <is>
           <t>Boston, MA</t>
         </is>
       </c>
-      <c r="G911" s="6" t="inlineStr">
+      <c r="G911" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H911" s="7" t="inlineStr">
+      <c r="H911" s="5" t="inlineStr">
         <is>
           <t>MPS HR Mgmt, Georgetown. Prior: Deloitte, 12 yrs.</t>
         </is>
       </c>
-      <c r="I911" s="6" t="inlineStr">
+      <c r="I911" s="4" t="inlineStr">
         <is>
           <t>Web research</t>
         </is>
       </c>
-      <c r="J911" s="6" t="inlineStr">
+      <c r="J911" s="4" t="inlineStr">
         <is>
           <t>Meredith Hicks-Ogburn</t>
         </is>
@@ -24279,24 +25299,52 @@
       </c>
     </row>
     <row r="919">
-      <c r="A919" s="2" t="inlineStr">
+      <c r="A919" s="4" t="inlineStr">
         <is>
           <t>Monica</t>
         </is>
       </c>
-      <c r="B919" s="2" t="inlineStr">
+      <c r="B919" s="4" t="inlineStr">
         <is>
           <t>Lynghaug</t>
         </is>
       </c>
-      <c r="C919" s="2" t="inlineStr"/>
-      <c r="D919" s="2" t="inlineStr"/>
-      <c r="E919" s="2" t="inlineStr"/>
-      <c r="F919" s="2" t="inlineStr"/>
-      <c r="G919" s="2" t="inlineStr"/>
-      <c r="H919" s="3" t="inlineStr"/>
-      <c r="I919" s="2" t="inlineStr"/>
-      <c r="J919" s="2" t="inlineStr">
+      <c r="C919" s="4" t="inlineStr">
+        <is>
+          <t>Skyline</t>
+        </is>
+      </c>
+      <c r="D919" s="4" t="inlineStr">
+        <is>
+          <t>Benefits Administrator (M.S., SHRM-CP, PHR)</t>
+        </is>
+      </c>
+      <c r="E919" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F919" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G919" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H919" s="5" t="inlineStr">
+        <is>
+          <t>Building materials. Also HR Consultant at HR Streamlined Solutions; listed at Armbruster Executive &amp; Employee Benefits.</t>
+        </is>
+      </c>
+      <c r="I919" s="4" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
+      <c r="J919" s="4" t="inlineStr">
         <is>
           <t>Monica Lynghaug</t>
         </is>
@@ -24543,100 +25591,156 @@
       </c>
     </row>
     <row r="930">
-      <c r="A930" s="6" t="inlineStr">
+      <c r="A930" s="4" t="inlineStr">
         <is>
           <t>Naomi</t>
         </is>
       </c>
-      <c r="B930" s="6" t="inlineStr">
+      <c r="B930" s="4" t="inlineStr">
         <is>
           <t>DuCharme</t>
         </is>
       </c>
-      <c r="C930" s="6" t="inlineStr">
+      <c r="C930" s="4" t="inlineStr">
         <is>
           <t>Alaska Safety Alliance / Integrating Wellness Solutions LLC</t>
         </is>
       </c>
-      <c r="D930" s="6" t="inlineStr">
+      <c r="D930" s="4" t="inlineStr">
         <is>
           <t>Executive Director; Founder &amp; Recovery/Leadership Coach</t>
         </is>
       </c>
-      <c r="E930" s="6" t="inlineStr">
+      <c r="E930" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F930" s="6" t="inlineStr">
+      <c r="F930" s="4" t="inlineStr">
         <is>
           <t>Alaska</t>
         </is>
       </c>
-      <c r="G930" s="6" t="inlineStr">
+      <c r="G930" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H930" s="7" t="inlineStr">
+      <c r="H930" s="5" t="inlineStr">
         <is>
           <t>HIGH RELEVANCE - workplace substance-use and burnout in construction, oil &amp; gas, mining, maritime.</t>
         </is>
       </c>
-      <c r="I930" s="6" t="inlineStr">
+      <c r="I930" s="4" t="inlineStr">
         <is>
           <t>Web research</t>
         </is>
       </c>
-      <c r="J930" s="6" t="inlineStr">
+      <c r="J930" s="4" t="inlineStr">
         <is>
           <t>Naomi DuCharme</t>
         </is>
       </c>
     </row>
     <row r="931">
-      <c r="A931" s="2" t="inlineStr">
+      <c r="A931" s="4" t="inlineStr">
         <is>
           <t>Natacha</t>
         </is>
       </c>
-      <c r="B931" s="2" t="inlineStr">
+      <c r="B931" s="4" t="inlineStr">
         <is>
           <t>Paultre</t>
         </is>
       </c>
-      <c r="C931" s="2" t="inlineStr"/>
-      <c r="D931" s="2" t="inlineStr"/>
-      <c r="E931" s="2" t="inlineStr"/>
-      <c r="F931" s="2" t="inlineStr"/>
-      <c r="G931" s="2" t="inlineStr"/>
-      <c r="H931" s="3" t="inlineStr"/>
-      <c r="I931" s="2" t="inlineStr"/>
-      <c r="J931" s="2" t="inlineStr">
+      <c r="C931" s="4" t="inlineStr">
+        <is>
+          <t>Delta Dental Plans Association</t>
+        </is>
+      </c>
+      <c r="D931" s="4" t="inlineStr">
+        <is>
+          <t>HR Talent Acquisition Partner</t>
+        </is>
+      </c>
+      <c r="E931" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F931" s="4" t="inlineStr">
+        <is>
+          <t>Chicago, IL</t>
+        </is>
+      </c>
+      <c r="G931" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H931" s="5" t="inlineStr">
+        <is>
+          <t>Benefits carrier.</t>
+        </is>
+      </c>
+      <c r="I931" s="4" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
+      <c r="J931" s="4" t="inlineStr">
         <is>
           <t>Natacha Paultre</t>
         </is>
       </c>
     </row>
     <row r="932">
-      <c r="A932" s="2" t="inlineStr">
+      <c r="A932" s="4" t="inlineStr">
         <is>
           <t>Natalia</t>
         </is>
       </c>
-      <c r="B932" s="2" t="inlineStr">
+      <c r="B932" s="4" t="inlineStr">
         <is>
           <t>Betancur Serna</t>
         </is>
       </c>
-      <c r="C932" s="2" t="inlineStr"/>
-      <c r="D932" s="2" t="inlineStr"/>
-      <c r="E932" s="2" t="inlineStr"/>
-      <c r="F932" s="2" t="inlineStr"/>
-      <c r="G932" s="2" t="inlineStr"/>
-      <c r="H932" s="3" t="inlineStr"/>
-      <c r="I932" s="2" t="inlineStr"/>
-      <c r="J932" s="2" t="inlineStr">
+      <c r="C932" s="4" t="inlineStr">
+        <is>
+          <t>Catholic Charities, Archdiocese of Galveston-Houston</t>
+        </is>
+      </c>
+      <c r="D932" s="4" t="inlineStr">
+        <is>
+          <t>HR (PHR)</t>
+        </is>
+      </c>
+      <c r="E932" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F932" s="4" t="inlineStr">
+        <is>
+          <t>Cypress, TX</t>
+        </is>
+      </c>
+      <c r="G932" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H932" s="5" t="inlineStr">
+        <is>
+          <t>Source lists her as Natalia Betancur.</t>
+        </is>
+      </c>
+      <c r="I932" s="4" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
+      <c r="J932" s="4" t="inlineStr">
         <is>
           <t>Natalia Betancur Serna</t>
         </is>
@@ -24859,24 +25963,52 @@
       </c>
     </row>
     <row r="942">
-      <c r="A942" s="2" t="inlineStr">
+      <c r="A942" s="4" t="inlineStr">
         <is>
           <t>Necia</t>
         </is>
       </c>
-      <c r="B942" s="2" t="inlineStr">
+      <c r="B942" s="4" t="inlineStr">
         <is>
           <t>Razzano</t>
         </is>
       </c>
-      <c r="C942" s="2" t="inlineStr"/>
-      <c r="D942" s="2" t="inlineStr"/>
-      <c r="E942" s="2" t="inlineStr"/>
-      <c r="F942" s="2" t="inlineStr"/>
-      <c r="G942" s="2" t="inlineStr"/>
-      <c r="H942" s="3" t="inlineStr"/>
-      <c r="I942" s="2" t="inlineStr"/>
-      <c r="J942" s="2" t="inlineStr">
+      <c r="C942" s="4" t="inlineStr">
+        <is>
+          <t>Gannett / USA TODAY Network</t>
+        </is>
+      </c>
+      <c r="D942" s="4" t="inlineStr">
+        <is>
+          <t>Manager, Recruitment Operations (PHR)</t>
+        </is>
+      </c>
+      <c r="E942" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F942" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G942" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H942" s="5" t="inlineStr">
+        <is>
+          <t>Prior: GateHouse Media (Talent Acq. Mgr; HR &amp; Circulation Mgr).</t>
+        </is>
+      </c>
+      <c r="I942" s="4" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
+      <c r="J942" s="4" t="inlineStr">
         <is>
           <t>Necia Razzano</t>
         </is>
@@ -24907,24 +26039,52 @@
       </c>
     </row>
     <row r="944">
-      <c r="A944" s="2" t="inlineStr">
+      <c r="A944" s="4" t="inlineStr">
         <is>
           <t>Nedra</t>
         </is>
       </c>
-      <c r="B944" s="2" t="inlineStr">
+      <c r="B944" s="4" t="inlineStr">
         <is>
           <t>Washington</t>
         </is>
       </c>
-      <c r="C944" s="2" t="inlineStr"/>
-      <c r="D944" s="2" t="inlineStr"/>
-      <c r="E944" s="2" t="inlineStr"/>
-      <c r="F944" s="2" t="inlineStr"/>
-      <c r="G944" s="2" t="inlineStr"/>
-      <c r="H944" s="3" t="inlineStr"/>
-      <c r="I944" s="2" t="inlineStr"/>
-      <c r="J944" s="2" t="inlineStr">
+      <c r="C944" s="4" t="inlineStr">
+        <is>
+          <t>ENGIE North America</t>
+        </is>
+      </c>
+      <c r="D944" s="4" t="inlineStr">
+        <is>
+          <t>Senior HR Business Partner (MSHRD, PHR)</t>
+        </is>
+      </c>
+      <c r="E944" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F944" s="4" t="inlineStr">
+        <is>
+          <t>Houston, TX</t>
+        </is>
+      </c>
+      <c r="G944" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H944" s="5" t="inlineStr">
+        <is>
+          <t>Prior: Olin, Stage Stores, CenterPoint Energy, KBR, Baker Hughes.</t>
+        </is>
+      </c>
+      <c r="I944" s="4" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
+      <c r="J944" s="4" t="inlineStr">
         <is>
           <t>Nedra Washington</t>
         </is>
@@ -24955,52 +26115,52 @@
       </c>
     </row>
     <row r="946">
-      <c r="A946" s="6" t="inlineStr">
+      <c r="A946" s="4" t="inlineStr">
         <is>
           <t>Nelsion</t>
         </is>
       </c>
-      <c r="B946" s="6" t="inlineStr">
+      <c r="B946" s="4" t="inlineStr">
         <is>
           <t>Singsomphong</t>
         </is>
       </c>
-      <c r="C946" s="6" t="inlineStr">
+      <c r="C946" s="4" t="inlineStr">
         <is>
           <t>UC Berkeley Law</t>
         </is>
       </c>
-      <c r="D946" s="6" t="inlineStr">
+      <c r="D946" s="4" t="inlineStr">
         <is>
           <t>Staff HR Partner</t>
         </is>
       </c>
-      <c r="E946" s="6" t="inlineStr">
+      <c r="E946" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F946" s="6" t="inlineStr">
+      <c r="F946" s="4" t="inlineStr">
         <is>
           <t>Berkeley, CA</t>
         </is>
       </c>
-      <c r="G946" s="6" t="inlineStr">
+      <c r="G946" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H946" s="7" t="inlineStr">
+      <c r="H946" s="5" t="inlineStr">
         <is>
           <t>Name is Nelson in sources; list has a typo.</t>
         </is>
       </c>
-      <c r="I946" s="6" t="inlineStr">
+      <c r="I946" s="4" t="inlineStr">
         <is>
           <t>Web research</t>
         </is>
       </c>
-      <c r="J946" s="6" t="inlineStr">
+      <c r="J946" s="4" t="inlineStr">
         <is>
           <t>Nelsion Singsomphong</t>
         </is>
@@ -25223,48 +26383,104 @@
       </c>
     </row>
     <row r="956">
-      <c r="A956" s="2" t="inlineStr">
+      <c r="A956" s="4" t="inlineStr">
         <is>
           <t>Nikkia</t>
         </is>
       </c>
-      <c r="B956" s="2" t="inlineStr">
+      <c r="B956" s="4" t="inlineStr">
         <is>
           <t>McCalla</t>
         </is>
       </c>
-      <c r="C956" s="2" t="inlineStr"/>
-      <c r="D956" s="2" t="inlineStr"/>
-      <c r="E956" s="2" t="inlineStr"/>
-      <c r="F956" s="2" t="inlineStr"/>
-      <c r="G956" s="2" t="inlineStr"/>
-      <c r="H956" s="3" t="inlineStr"/>
-      <c r="I956" s="2" t="inlineStr"/>
-      <c r="J956" s="2" t="inlineStr">
+      <c r="C956" s="4" t="inlineStr">
+        <is>
+          <t>Precision Medicine Group</t>
+        </is>
+      </c>
+      <c r="D956" s="4" t="inlineStr">
+        <is>
+          <t>Manager, People &amp; Office Services (MHA, PHR)</t>
+        </is>
+      </c>
+      <c r="E956" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F956" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G956" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H956" s="5" t="inlineStr">
+        <is>
+          <t>10+ yrs healthcare HR.</t>
+        </is>
+      </c>
+      <c r="I956" s="4" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
+      <c r="J956" s="4" t="inlineStr">
         <is>
           <t>Nikkia McCalla</t>
         </is>
       </c>
     </row>
     <row r="957">
-      <c r="A957" s="2" t="inlineStr">
+      <c r="A957" s="4" t="inlineStr">
         <is>
           <t>Nina</t>
         </is>
       </c>
-      <c r="B957" s="2" t="inlineStr">
+      <c r="B957" s="4" t="inlineStr">
         <is>
           <t>Izaguirre</t>
         </is>
       </c>
-      <c r="C957" s="2" t="inlineStr"/>
-      <c r="D957" s="2" t="inlineStr"/>
-      <c r="E957" s="2" t="inlineStr"/>
-      <c r="F957" s="2" t="inlineStr"/>
-      <c r="G957" s="2" t="inlineStr"/>
-      <c r="H957" s="3" t="inlineStr"/>
-      <c r="I957" s="2" t="inlineStr"/>
-      <c r="J957" s="2" t="inlineStr">
+      <c r="C957" s="4" t="inlineStr">
+        <is>
+          <t>InSite Consulting Architects</t>
+        </is>
+      </c>
+      <c r="D957" s="4" t="inlineStr">
+        <is>
+          <t>Marketing Assistant</t>
+        </is>
+      </c>
+      <c r="E957" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F957" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G957" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H957" s="5" t="inlineStr">
+        <is>
+          <t>NOT an HR role.</t>
+        </is>
+      </c>
+      <c r="I957" s="4" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
+      <c r="J957" s="4" t="inlineStr">
         <is>
           <t>Nina Izaguirre</t>
         </is>
@@ -25511,24 +26727,52 @@
       </c>
     </row>
     <row r="968">
-      <c r="A968" s="2" t="inlineStr">
+      <c r="A968" s="4" t="inlineStr">
         <is>
           <t>Oyinlola</t>
         </is>
       </c>
-      <c r="B968" s="2" t="inlineStr">
+      <c r="B968" s="4" t="inlineStr">
         <is>
           <t>Ojudbele</t>
         </is>
       </c>
-      <c r="C968" s="2" t="inlineStr"/>
-      <c r="D968" s="2" t="inlineStr"/>
-      <c r="E968" s="2" t="inlineStr"/>
-      <c r="F968" s="2" t="inlineStr"/>
-      <c r="G968" s="2" t="inlineStr"/>
-      <c r="H968" s="3" t="inlineStr"/>
-      <c r="I968" s="2" t="inlineStr"/>
-      <c r="J968" s="2" t="inlineStr">
+      <c r="C968" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D968" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E968" s="4" t="inlineStr">
+        <is>
+          <t>International (likely)</t>
+        </is>
+      </c>
+      <c r="F968" s="4" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="G968" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H968" s="5" t="inlineStr">
+        <is>
+          <t>Closest match is Oyinlola Omoboye, HR Officer, Rellies Works - different surname, do not assume.</t>
+        </is>
+      </c>
+      <c r="I968" s="4" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
+      <c r="J968" s="4" t="inlineStr">
         <is>
           <t>Oyinlola Ojudbele</t>
         </is>
@@ -25607,24 +26851,52 @@
       </c>
     </row>
     <row r="972">
-      <c r="A972" s="2" t="inlineStr">
+      <c r="A972" s="4" t="inlineStr">
         <is>
           <t>Ponnette</t>
         </is>
       </c>
-      <c r="B972" s="2" t="inlineStr">
+      <c r="B972" s="4" t="inlineStr">
         <is>
           <t>Smith</t>
         </is>
       </c>
-      <c r="C972" s="2" t="inlineStr"/>
-      <c r="D972" s="2" t="inlineStr"/>
-      <c r="E972" s="2" t="inlineStr"/>
-      <c r="F972" s="2" t="inlineStr"/>
-      <c r="G972" s="2" t="inlineStr"/>
-      <c r="H972" s="3" t="inlineStr"/>
-      <c r="I972" s="2" t="inlineStr"/>
-      <c r="J972" s="2" t="inlineStr">
+      <c r="C972" s="4" t="inlineStr">
+        <is>
+          <t>Virginia Department of Human Resource Management</t>
+        </is>
+      </c>
+      <c r="D972" s="4" t="inlineStr">
+        <is>
+          <t>HR (SPHR, SHRM-SCP)</t>
+        </is>
+      </c>
+      <c r="E972" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F972" s="4" t="inlineStr">
+        <is>
+          <t>Virginia</t>
+        </is>
+      </c>
+      <c r="G972" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H972" s="5" t="inlineStr">
+        <is>
+          <t>State government HR - large public employer.</t>
+        </is>
+      </c>
+      <c r="I972" s="4" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
+      <c r="J972" s="4" t="inlineStr">
         <is>
           <t>Ponnette Smith</t>
         </is>
@@ -25703,24 +26975,52 @@
       </c>
     </row>
     <row r="976">
-      <c r="A976" s="2" t="inlineStr">
+      <c r="A976" s="4" t="inlineStr">
         <is>
           <t>Racheal</t>
         </is>
       </c>
-      <c r="B976" s="2" t="inlineStr">
+      <c r="B976" s="4" t="inlineStr">
         <is>
           <t>Prutch</t>
         </is>
       </c>
-      <c r="C976" s="2" t="inlineStr"/>
-      <c r="D976" s="2" t="inlineStr"/>
-      <c r="E976" s="2" t="inlineStr"/>
-      <c r="F976" s="2" t="inlineStr"/>
-      <c r="G976" s="2" t="inlineStr"/>
-      <c r="H976" s="3" t="inlineStr"/>
-      <c r="I976" s="2" t="inlineStr"/>
-      <c r="J976" s="2" t="inlineStr">
+      <c r="C976" s="4" t="inlineStr">
+        <is>
+          <t>IH Services, Inc. (also Melton Truck Lines)</t>
+        </is>
+      </c>
+      <c r="D976" s="4" t="inlineStr">
+        <is>
+          <t>Manager, Human Resources; Facility Security Officer</t>
+        </is>
+      </c>
+      <c r="E976" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F976" s="4" t="inlineStr">
+        <is>
+          <t>Greenville, SC</t>
+        </is>
+      </c>
+      <c r="G976" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H976" s="5" t="inlineStr">
+        <is>
+          <t>Also listed as Manager, Benefits at Melton Truck Lines (Tulsa, OK) - verify which is current.</t>
+        </is>
+      </c>
+      <c r="I976" s="4" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
+      <c r="J976" s="4" t="inlineStr">
         <is>
           <t>Racheal Prutch</t>
         </is>
@@ -25943,24 +27243,52 @@
       </c>
     </row>
     <row r="986">
-      <c r="A986" s="2" t="inlineStr">
+      <c r="A986" s="4" t="inlineStr">
         <is>
           <t>Randis</t>
         </is>
       </c>
-      <c r="B986" s="2" t="inlineStr">
+      <c r="B986" s="4" t="inlineStr">
         <is>
           <t>Silas</t>
         </is>
       </c>
-      <c r="C986" s="2" t="inlineStr"/>
-      <c r="D986" s="2" t="inlineStr"/>
-      <c r="E986" s="2" t="inlineStr"/>
-      <c r="F986" s="2" t="inlineStr"/>
-      <c r="G986" s="2" t="inlineStr"/>
-      <c r="H986" s="3" t="inlineStr"/>
-      <c r="I986" s="2" t="inlineStr"/>
-      <c r="J986" s="2" t="inlineStr">
+      <c r="C986" s="4" t="inlineStr">
+        <is>
+          <t>Abrazo Health</t>
+        </is>
+      </c>
+      <c r="D986" s="4" t="inlineStr">
+        <is>
+          <t>HR Generalist (MBA)</t>
+        </is>
+      </c>
+      <c r="E986" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F986" s="4" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ</t>
+        </is>
+      </c>
+      <c r="G986" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H986" s="5" t="inlineStr">
+        <is>
+          <t>Prior: Manager HR, Heart One Associates.</t>
+        </is>
+      </c>
+      <c r="I986" s="4" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
+      <c r="J986" s="4" t="inlineStr">
         <is>
           <t>Randis Silas</t>
         </is>
@@ -26399,24 +27727,52 @@
       </c>
     </row>
     <row r="1005">
-      <c r="A1005" s="2" t="inlineStr">
+      <c r="A1005" s="4" t="inlineStr">
         <is>
           <t>Rhonda</t>
         </is>
       </c>
-      <c r="B1005" s="2" t="inlineStr">
+      <c r="B1005" s="4" t="inlineStr">
         <is>
           <t>Deann Stamps</t>
         </is>
       </c>
-      <c r="C1005" s="2" t="inlineStr"/>
-      <c r="D1005" s="2" t="inlineStr"/>
-      <c r="E1005" s="2" t="inlineStr"/>
-      <c r="F1005" s="2" t="inlineStr"/>
-      <c r="G1005" s="2" t="inlineStr"/>
-      <c r="H1005" s="3" t="inlineStr"/>
-      <c r="I1005" s="2" t="inlineStr"/>
-      <c r="J1005" s="2" t="inlineStr">
+      <c r="C1005" s="4" t="inlineStr">
+        <is>
+          <t>Midland College</t>
+        </is>
+      </c>
+      <c r="D1005" s="4" t="inlineStr">
+        <is>
+          <t>Associate Director, Human Resources</t>
+        </is>
+      </c>
+      <c r="E1005" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F1005" s="4" t="inlineStr">
+        <is>
+          <t>Midland, TX</t>
+        </is>
+      </c>
+      <c r="G1005" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H1005" s="5" t="inlineStr">
+        <is>
+          <t>Source lists her as Deann Stamps - verify name match.</t>
+        </is>
+      </c>
+      <c r="I1005" s="4" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
+      <c r="J1005" s="4" t="inlineStr">
         <is>
           <t>Rhonda Deann Stamps</t>
         </is>
@@ -26519,24 +27875,52 @@
       </c>
     </row>
     <row r="1010">
-      <c r="A1010" s="2" t="inlineStr">
+      <c r="A1010" s="4" t="inlineStr">
         <is>
           <t>Ritsuko</t>
         </is>
       </c>
-      <c r="B1010" s="2" t="inlineStr">
+      <c r="B1010" s="4" t="inlineStr">
         <is>
           <t>Hamagami</t>
         </is>
       </c>
-      <c r="C1010" s="2" t="inlineStr"/>
-      <c r="D1010" s="2" t="inlineStr"/>
-      <c r="E1010" s="2" t="inlineStr"/>
-      <c r="F1010" s="2" t="inlineStr"/>
-      <c r="G1010" s="2" t="inlineStr"/>
-      <c r="H1010" s="3" t="inlineStr"/>
-      <c r="I1010" s="2" t="inlineStr"/>
-      <c r="J1010" s="2" t="inlineStr">
+      <c r="C1010" s="4" t="inlineStr">
+        <is>
+          <t>JTB Americas, Ltd.</t>
+        </is>
+      </c>
+      <c r="D1010" s="4" t="inlineStr">
+        <is>
+          <t>Chief Human Resources Officer (SPHR, SHRM-SCP)</t>
+        </is>
+      </c>
+      <c r="E1010" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F1010" s="4" t="inlineStr">
+        <is>
+          <t>Torrance, CA</t>
+        </is>
+      </c>
+      <c r="G1010" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H1010" s="5" t="inlineStr">
+        <is>
+          <t>Prior: Sr. HR Consultant &amp; Partner, HRM Partners.</t>
+        </is>
+      </c>
+      <c r="I1010" s="4" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
+      <c r="J1010" s="4" t="inlineStr">
         <is>
           <t>Ritsuko Hamagami</t>
         </is>
@@ -27119,24 +28503,48 @@
       </c>
     </row>
     <row r="1035">
-      <c r="A1035" s="2" t="inlineStr">
+      <c r="A1035" s="4" t="inlineStr">
         <is>
           <t>Savannah</t>
         </is>
       </c>
-      <c r="B1035" s="2" t="inlineStr">
+      <c r="B1035" s="4" t="inlineStr">
         <is>
           <t>Gatton</t>
         </is>
       </c>
-      <c r="C1035" s="2" t="inlineStr"/>
-      <c r="D1035" s="2" t="inlineStr"/>
-      <c r="E1035" s="2" t="inlineStr"/>
-      <c r="F1035" s="2" t="inlineStr"/>
-      <c r="G1035" s="2" t="inlineStr"/>
-      <c r="H1035" s="3" t="inlineStr"/>
-      <c r="I1035" s="2" t="inlineStr"/>
-      <c r="J1035" s="2" t="inlineStr">
+      <c r="C1035" s="4" t="inlineStr">
+        <is>
+          <t>FRESHFARM</t>
+        </is>
+      </c>
+      <c r="D1035" s="4" t="inlineStr">
+        <is>
+          <t>People Operations (PHR)</t>
+        </is>
+      </c>
+      <c r="E1035" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F1035" s="4" t="inlineStr">
+        <is>
+          <t>Washington, DC</t>
+        </is>
+      </c>
+      <c r="G1035" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H1035" s="5" t="inlineStr"/>
+      <c r="I1035" s="4" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
+      <c r="J1035" s="4" t="inlineStr">
         <is>
           <t>Savannah Gatton</t>
         </is>
@@ -27335,24 +28743,52 @@
       </c>
     </row>
     <row r="1044">
-      <c r="A1044" s="2" t="inlineStr">
+      <c r="A1044" s="4" t="inlineStr">
         <is>
           <t>Shanika</t>
         </is>
       </c>
-      <c r="B1044" s="2" t="inlineStr">
+      <c r="B1044" s="4" t="inlineStr">
         <is>
           <t>Robinson</t>
         </is>
       </c>
-      <c r="C1044" s="2" t="inlineStr"/>
-      <c r="D1044" s="2" t="inlineStr"/>
-      <c r="E1044" s="2" t="inlineStr"/>
-      <c r="F1044" s="2" t="inlineStr"/>
-      <c r="G1044" s="2" t="inlineStr"/>
-      <c r="H1044" s="3" t="inlineStr"/>
-      <c r="I1044" s="2" t="inlineStr"/>
-      <c r="J1044" s="2" t="inlineStr">
+      <c r="C1044" s="4" t="inlineStr">
+        <is>
+          <t>PrismHR</t>
+        </is>
+      </c>
+      <c r="D1044" s="4" t="inlineStr">
+        <is>
+          <t>EDI Integration, Support &amp; Vendor Management</t>
+        </is>
+      </c>
+      <c r="E1044" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F1044" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G1044" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H1044" s="5" t="inlineStr">
+        <is>
+          <t>20+ yrs. HR technology/payroll platform.</t>
+        </is>
+      </c>
+      <c r="I1044" s="4" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
+      <c r="J1044" s="4" t="inlineStr">
         <is>
           <t>Shanika Robinson</t>
         </is>
@@ -27671,52 +29107,52 @@
       </c>
     </row>
     <row r="1058">
-      <c r="A1058" s="6" t="inlineStr">
+      <c r="A1058" s="4" t="inlineStr">
         <is>
           <t>Shauna</t>
         </is>
       </c>
-      <c r="B1058" s="6" t="inlineStr">
+      <c r="B1058" s="4" t="inlineStr">
         <is>
           <t>Holman-Harries</t>
         </is>
       </c>
-      <c r="C1058" s="6" t="inlineStr">
+      <c r="C1058" s="4" t="inlineStr">
         <is>
           <t>Oracle</t>
         </is>
       </c>
-      <c r="D1058" s="6" t="inlineStr">
+      <c r="D1058" s="4" t="inlineStr">
         <is>
           <t>Sr. Director, Human Resources / Culture &amp; Inclusion Compliance</t>
         </is>
       </c>
-      <c r="E1058" s="6" t="inlineStr">
+      <c r="E1058" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F1058" s="6" t="inlineStr">
+      <c r="F1058" s="4" t="inlineStr">
         <is>
           <t>Pacific region</t>
         </is>
       </c>
-      <c r="G1058" s="6" t="inlineStr">
+      <c r="G1058" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H1058" s="7" t="inlineStr">
+      <c r="H1058" s="5" t="inlineStr">
         <is>
           <t>Prior: Berkeley Lab, NRG Energy, United Space Alliance.</t>
         </is>
       </c>
-      <c r="I1058" s="6" t="inlineStr">
+      <c r="I1058" s="4" t="inlineStr">
         <is>
           <t>Web research</t>
         </is>
       </c>
-      <c r="J1058" s="6" t="inlineStr">
+      <c r="J1058" s="4" t="inlineStr">
         <is>
           <t>Shauna Holman-Harries</t>
         </is>
@@ -27771,24 +29207,52 @@
       </c>
     </row>
     <row r="1061">
-      <c r="A1061" s="2" t="inlineStr">
+      <c r="A1061" s="4" t="inlineStr">
         <is>
           <t>Shayla</t>
         </is>
       </c>
-      <c r="B1061" s="2" t="inlineStr">
+      <c r="B1061" s="4" t="inlineStr">
         <is>
           <t>Matono</t>
         </is>
       </c>
-      <c r="C1061" s="2" t="inlineStr"/>
-      <c r="D1061" s="2" t="inlineStr"/>
-      <c r="E1061" s="2" t="inlineStr"/>
-      <c r="F1061" s="2" t="inlineStr"/>
-      <c r="G1061" s="2" t="inlineStr"/>
-      <c r="H1061" s="3" t="inlineStr"/>
-      <c r="I1061" s="2" t="inlineStr"/>
-      <c r="J1061" s="2" t="inlineStr">
+      <c r="C1061" s="4" t="inlineStr">
+        <is>
+          <t>'ike (IKE Group Inc) / DataHouse</t>
+        </is>
+      </c>
+      <c r="D1061" s="4" t="inlineStr">
+        <is>
+          <t>Senior Manager, Total Rewards (PHR)</t>
+        </is>
+      </c>
+      <c r="E1061" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F1061" s="4" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="G1061" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H1061" s="5" t="inlineStr">
+        <is>
+          <t>Total rewards, benefits admin, payroll, compliance.</t>
+        </is>
+      </c>
+      <c r="I1061" s="4" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
+      <c r="J1061" s="4" t="inlineStr">
         <is>
           <t>Shayla Matono</t>
         </is>
@@ -27939,52 +29403,52 @@
       </c>
     </row>
     <row r="1068">
-      <c r="A1068" s="6" t="inlineStr">
+      <c r="A1068" s="4" t="inlineStr">
         <is>
           <t>Shemeka</t>
         </is>
       </c>
-      <c r="B1068" s="6" t="inlineStr">
+      <c r="B1068" s="4" t="inlineStr">
         <is>
           <t>Browne-Pohlman</t>
         </is>
       </c>
-      <c r="C1068" s="6" t="inlineStr">
+      <c r="C1068" s="4" t="inlineStr">
         <is>
           <t>HUB International</t>
         </is>
       </c>
-      <c r="D1068" s="6" t="inlineStr">
+      <c r="D1068" s="4" t="inlineStr">
         <is>
           <t>Group Benefits / ACA Compliance</t>
         </is>
       </c>
-      <c r="E1068" s="6" t="inlineStr">
+      <c r="E1068" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F1068" s="6" t="inlineStr">
+      <c r="F1068" s="4" t="inlineStr">
         <is>
           <t>New England</t>
         </is>
       </c>
-      <c r="G1068" s="6" t="inlineStr">
+      <c r="G1068" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H1068" s="7" t="inlineStr">
+      <c r="H1068" s="5" t="inlineStr">
         <is>
           <t>~9 yrs group benefits. Prior: Insurance Center of New England.</t>
         </is>
       </c>
-      <c r="I1068" s="6" t="inlineStr">
+      <c r="I1068" s="4" t="inlineStr">
         <is>
           <t>Web research</t>
         </is>
       </c>
-      <c r="J1068" s="6" t="inlineStr">
+      <c r="J1068" s="4" t="inlineStr">
         <is>
           <t>Shemeka Browne-Pohlman</t>
         </is>
@@ -28015,104 +29479,104 @@
       </c>
     </row>
     <row r="1070">
-      <c r="A1070" s="6" t="inlineStr">
+      <c r="A1070" s="4" t="inlineStr">
         <is>
           <t>Sheri</t>
         </is>
       </c>
-      <c r="B1070" s="6" t="inlineStr">
+      <c r="B1070" s="4" t="inlineStr">
         <is>
           <t>Velastegui</t>
         </is>
       </c>
-      <c r="C1070" s="6" t="inlineStr">
+      <c r="C1070" s="4" t="inlineStr">
         <is>
           <t>TransPerfect</t>
         </is>
       </c>
-      <c r="D1070" s="6" t="inlineStr">
+      <c r="D1070" s="4" t="inlineStr">
         <is>
           <t>Sr. Manager, Human Resources (SHRM-SCP)</t>
         </is>
       </c>
-      <c r="E1070" s="6" t="inlineStr">
+      <c r="E1070" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F1070" s="6" t="inlineStr">
+      <c r="F1070" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G1070" s="6" t="inlineStr">
+      <c r="G1070" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H1070" s="7" t="inlineStr">
+      <c r="H1070" s="5" t="inlineStr">
         <is>
           <t>Explicit focus on workplace wellbeing, benefits optimisation, total rewards.</t>
         </is>
       </c>
-      <c r="I1070" s="6" t="inlineStr">
+      <c r="I1070" s="4" t="inlineStr">
         <is>
           <t>Web research</t>
         </is>
       </c>
-      <c r="J1070" s="6" t="inlineStr">
+      <c r="J1070" s="4" t="inlineStr">
         <is>
           <t>Sheri Velastegui</t>
         </is>
       </c>
     </row>
     <row r="1071">
-      <c r="A1071" s="6" t="inlineStr">
+      <c r="A1071" s="4" t="inlineStr">
         <is>
           <t>Sheridan</t>
         </is>
       </c>
-      <c r="B1071" s="6" t="inlineStr">
+      <c r="B1071" s="4" t="inlineStr">
         <is>
           <t>Chelberg</t>
         </is>
       </c>
-      <c r="C1071" s="6" t="inlineStr">
+      <c r="C1071" s="4" t="inlineStr">
         <is>
           <t>The Tile Shop</t>
         </is>
       </c>
-      <c r="D1071" s="6" t="inlineStr">
+      <c r="D1071" s="4" t="inlineStr">
         <is>
           <t>HR Assistant</t>
         </is>
       </c>
-      <c r="E1071" s="6" t="inlineStr">
+      <c r="E1071" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F1071" s="6" t="inlineStr">
+      <c r="F1071" s="4" t="inlineStr">
         <is>
           <t>Plymouth, MN</t>
         </is>
       </c>
-      <c r="G1071" s="6" t="inlineStr">
+      <c r="G1071" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H1071" s="7" t="inlineStr">
+      <c r="H1071" s="5" t="inlineStr">
         <is>
           <t>Prior: Aston Carter.</t>
         </is>
       </c>
-      <c r="I1071" s="6" t="inlineStr">
+      <c r="I1071" s="4" t="inlineStr">
         <is>
           <t>Web research</t>
         </is>
       </c>
-      <c r="J1071" s="6" t="inlineStr">
+      <c r="J1071" s="4" t="inlineStr">
         <is>
           <t>Sheridan Chelberg</t>
         </is>
@@ -28143,24 +29607,52 @@
       </c>
     </row>
     <row r="1073">
-      <c r="A1073" s="2" t="inlineStr">
+      <c r="A1073" s="4" t="inlineStr">
         <is>
           <t>Sherri</t>
         </is>
       </c>
-      <c r="B1073" s="2" t="inlineStr">
+      <c r="B1073" s="4" t="inlineStr">
         <is>
           <t>Toebe</t>
         </is>
       </c>
-      <c r="C1073" s="2" t="inlineStr"/>
-      <c r="D1073" s="2" t="inlineStr"/>
-      <c r="E1073" s="2" t="inlineStr"/>
-      <c r="F1073" s="2" t="inlineStr"/>
-      <c r="G1073" s="2" t="inlineStr"/>
-      <c r="H1073" s="3" t="inlineStr"/>
-      <c r="I1073" s="2" t="inlineStr"/>
-      <c r="J1073" s="2" t="inlineStr">
+      <c r="C1073" s="4" t="inlineStr">
+        <is>
+          <t>Gannett Fleming</t>
+        </is>
+      </c>
+      <c r="D1073" s="4" t="inlineStr">
+        <is>
+          <t>Talent Acquisition Specialist (PHR)</t>
+        </is>
+      </c>
+      <c r="E1073" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F1073" s="4" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="G1073" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H1073" s="5" t="inlineStr">
+        <is>
+          <t>RELEVANT - Women in Construction ambassador, NY Build. Construction/engineering firm.</t>
+        </is>
+      </c>
+      <c r="I1073" s="4" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
+      <c r="J1073" s="4" t="inlineStr">
         <is>
           <t>Sherri Toebe</t>
         </is>
@@ -28455,24 +29947,48 @@
       </c>
     </row>
     <row r="1086">
-      <c r="A1086" s="2" t="inlineStr">
+      <c r="A1086" s="4" t="inlineStr">
         <is>
           <t>Steven</t>
         </is>
       </c>
-      <c r="B1086" s="2" t="inlineStr">
+      <c r="B1086" s="4" t="inlineStr">
         <is>
           <t>Torchio</t>
         </is>
       </c>
-      <c r="C1086" s="2" t="inlineStr"/>
-      <c r="D1086" s="2" t="inlineStr"/>
-      <c r="E1086" s="2" t="inlineStr"/>
-      <c r="F1086" s="2" t="inlineStr"/>
-      <c r="G1086" s="2" t="inlineStr"/>
-      <c r="H1086" s="3" t="inlineStr"/>
-      <c r="I1086" s="2" t="inlineStr"/>
-      <c r="J1086" s="2" t="inlineStr">
+      <c r="C1086" s="4" t="inlineStr">
+        <is>
+          <t>UNC School of Medicine</t>
+        </is>
+      </c>
+      <c r="D1086" s="4" t="inlineStr">
+        <is>
+          <t>Human Resources Consultant (PHR)</t>
+        </is>
+      </c>
+      <c r="E1086" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F1086" s="4" t="inlineStr">
+        <is>
+          <t>Chapel Hill, NC</t>
+        </is>
+      </c>
+      <c r="G1086" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H1086" s="5" t="inlineStr"/>
+      <c r="I1086" s="4" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
+      <c r="J1086" s="4" t="inlineStr">
         <is>
           <t>Steven Torchio</t>
         </is>
@@ -28791,52 +30307,52 @@
       </c>
     </row>
     <row r="1100">
-      <c r="A1100" s="6" t="inlineStr">
+      <c r="A1100" s="4" t="inlineStr">
         <is>
           <t>Svetlana</t>
         </is>
       </c>
-      <c r="B1100" s="6" t="inlineStr">
+      <c r="B1100" s="4" t="inlineStr">
         <is>
           <t>Scutelnicius</t>
         </is>
       </c>
-      <c r="C1100" s="6" t="inlineStr">
+      <c r="C1100" s="4" t="inlineStr">
         <is>
           <t>Smart Solver / Best People (owner)</t>
         </is>
       </c>
-      <c r="D1100" s="6" t="inlineStr">
+      <c r="D1100" s="4" t="inlineStr">
         <is>
           <t>HR Consultant (PHRi, CIPD, WorldatWork)</t>
         </is>
       </c>
-      <c r="E1100" s="6" t="inlineStr">
+      <c r="E1100" s="4" t="inlineStr">
         <is>
           <t>International</t>
         </is>
       </c>
-      <c r="F1100" s="6" t="inlineStr">
+      <c r="F1100" s="4" t="inlineStr">
         <is>
           <t>Moldova</t>
         </is>
       </c>
-      <c r="G1100" s="6" t="inlineStr">
+      <c r="G1100" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H1100" s="7" t="inlineStr">
+      <c r="H1100" s="5" t="inlineStr">
         <is>
           <t>Spelled Scutelniciuc. Consultant to EBRD, UNFPA, Chamber of Commerce Moldova, People 1st Intl (London).</t>
         </is>
       </c>
-      <c r="I1100" s="6" t="inlineStr">
+      <c r="I1100" s="4" t="inlineStr">
         <is>
           <t>Web research</t>
         </is>
       </c>
-      <c r="J1100" s="6" t="inlineStr">
+      <c r="J1100" s="4" t="inlineStr">
         <is>
           <t>Svetlana Scutelnicius</t>
         </is>
@@ -28867,24 +30383,52 @@
       </c>
     </row>
     <row r="1102">
-      <c r="A1102" s="2" t="inlineStr">
+      <c r="A1102" s="4" t="inlineStr">
         <is>
           <t>Sylda</t>
         </is>
       </c>
-      <c r="B1102" s="2" t="inlineStr">
+      <c r="B1102" s="4" t="inlineStr">
         <is>
           <t>Roldan Suarez</t>
         </is>
       </c>
-      <c r="C1102" s="2" t="inlineStr"/>
-      <c r="D1102" s="2" t="inlineStr"/>
-      <c r="E1102" s="2" t="inlineStr"/>
-      <c r="F1102" s="2" t="inlineStr"/>
-      <c r="G1102" s="2" t="inlineStr"/>
-      <c r="H1102" s="3" t="inlineStr"/>
-      <c r="I1102" s="2" t="inlineStr"/>
-      <c r="J1102" s="2" t="inlineStr">
+      <c r="C1102" s="4" t="inlineStr">
+        <is>
+          <t>AbbVie</t>
+        </is>
+      </c>
+      <c r="D1102" s="4" t="inlineStr">
+        <is>
+          <t>Human Resources Business Manager (SHRM-CP, PHR)</t>
+        </is>
+      </c>
+      <c r="E1102" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F1102" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G1102" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H1102" s="5" t="inlineStr">
+        <is>
+          <t>Surname listed as Roldan in sources. Healthcare/aerospace regulated industries; former HR Director, LatAm emerging markets.</t>
+        </is>
+      </c>
+      <c r="I1102" s="4" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
+      <c r="J1102" s="4" t="inlineStr">
         <is>
           <t>Sylda Roldan Suarez</t>
         </is>
@@ -28915,24 +30459,52 @@
       </c>
     </row>
     <row r="1104">
-      <c r="A1104" s="2" t="inlineStr">
+      <c r="A1104" s="4" t="inlineStr">
         <is>
           <t>Symone</t>
         </is>
       </c>
-      <c r="B1104" s="2" t="inlineStr">
+      <c r="B1104" s="4" t="inlineStr">
         <is>
           <t>Prude</t>
         </is>
       </c>
-      <c r="C1104" s="2" t="inlineStr"/>
-      <c r="D1104" s="2" t="inlineStr"/>
-      <c r="E1104" s="2" t="inlineStr"/>
-      <c r="F1104" s="2" t="inlineStr"/>
-      <c r="G1104" s="2" t="inlineStr"/>
-      <c r="H1104" s="3" t="inlineStr"/>
-      <c r="I1104" s="2" t="inlineStr"/>
-      <c r="J1104" s="2" t="inlineStr">
+      <c r="C1104" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D1104" s="4" t="inlineStr">
+        <is>
+          <t>Human Resources Generalist (PHR)</t>
+        </is>
+      </c>
+      <c r="E1104" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F1104" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G1104" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H1104" s="5" t="inlineStr">
+        <is>
+          <t>No employer found.</t>
+        </is>
+      </c>
+      <c r="I1104" s="4" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
+      <c r="J1104" s="4" t="inlineStr">
         <is>
           <t>Symone Prude</t>
         </is>
@@ -29011,24 +30583,52 @@
       </c>
     </row>
     <row r="1108">
-      <c r="A1108" s="2" t="inlineStr">
+      <c r="A1108" s="4" t="inlineStr">
         <is>
           <t>Tamara</t>
         </is>
       </c>
-      <c r="B1108" s="2" t="inlineStr">
+      <c r="B1108" s="4" t="inlineStr">
         <is>
           <t>Sutyak</t>
         </is>
       </c>
-      <c r="C1108" s="2" t="inlineStr"/>
-      <c r="D1108" s="2" t="inlineStr"/>
-      <c r="E1108" s="2" t="inlineStr"/>
-      <c r="F1108" s="2" t="inlineStr"/>
-      <c r="G1108" s="2" t="inlineStr"/>
-      <c r="H1108" s="3" t="inlineStr"/>
-      <c r="I1108" s="2" t="inlineStr"/>
-      <c r="J1108" s="2" t="inlineStr">
+      <c r="C1108" s="4" t="inlineStr">
+        <is>
+          <t>AC Martin</t>
+        </is>
+      </c>
+      <c r="D1108" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E1108" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F1108" s="4" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA</t>
+        </is>
+      </c>
+      <c r="G1108" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H1108" s="5" t="inlineStr">
+        <is>
+          <t>Architecture firm; role not confirmed as HR.</t>
+        </is>
+      </c>
+      <c r="I1108" s="4" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
+      <c r="J1108" s="4" t="inlineStr">
         <is>
           <t>Tamara Sutyak</t>
         </is>
@@ -29107,24 +30707,52 @@
       </c>
     </row>
     <row r="1112">
-      <c r="A1112" s="2" t="inlineStr">
+      <c r="A1112" s="4" t="inlineStr">
         <is>
           <t>Tamisha</t>
         </is>
       </c>
-      <c r="B1112" s="2" t="inlineStr">
+      <c r="B1112" s="4" t="inlineStr">
         <is>
           <t>Boleware</t>
         </is>
       </c>
-      <c r="C1112" s="2" t="inlineStr"/>
-      <c r="D1112" s="2" t="inlineStr"/>
-      <c r="E1112" s="2" t="inlineStr"/>
-      <c r="F1112" s="2" t="inlineStr"/>
-      <c r="G1112" s="2" t="inlineStr"/>
-      <c r="H1112" s="3" t="inlineStr"/>
-      <c r="I1112" s="2" t="inlineStr"/>
-      <c r="J1112" s="2" t="inlineStr">
+      <c r="C1112" s="4" t="inlineStr">
+        <is>
+          <t>Malone Workforce Solutions</t>
+        </is>
+      </c>
+      <c r="D1112" s="4" t="inlineStr">
+        <is>
+          <t>Director, Human Resources</t>
+        </is>
+      </c>
+      <c r="E1112" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F1112" s="4" t="inlineStr">
+        <is>
+          <t>Louisville, KY</t>
+        </is>
+      </c>
+      <c r="G1112" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H1112" s="5" t="inlineStr">
+        <is>
+          <t>Prior: Director Recruitment &amp; Talent Dev, Malone; Enterprise Mobility.</t>
+        </is>
+      </c>
+      <c r="I1112" s="4" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
+      <c r="J1112" s="4" t="inlineStr">
         <is>
           <t>Tamisha Boleware</t>
         </is>
@@ -29227,24 +30855,52 @@
       </c>
     </row>
     <row r="1117">
-      <c r="A1117" s="2" t="inlineStr">
+      <c r="A1117" s="4" t="inlineStr">
         <is>
           <t>Tanisha</t>
         </is>
       </c>
-      <c r="B1117" s="2" t="inlineStr">
+      <c r="B1117" s="4" t="inlineStr">
         <is>
           <t>Sewell</t>
         </is>
       </c>
-      <c r="C1117" s="2" t="inlineStr"/>
-      <c r="D1117" s="2" t="inlineStr"/>
-      <c r="E1117" s="2" t="inlineStr"/>
-      <c r="F1117" s="2" t="inlineStr"/>
-      <c r="G1117" s="2" t="inlineStr"/>
-      <c r="H1117" s="3" t="inlineStr"/>
-      <c r="I1117" s="2" t="inlineStr"/>
-      <c r="J1117" s="2" t="inlineStr">
+      <c r="C1117" s="4" t="inlineStr">
+        <is>
+          <t>University of North Carolina at Charlotte</t>
+        </is>
+      </c>
+      <c r="D1117" s="4" t="inlineStr">
+        <is>
+          <t>Director, Finance &amp; Human Resources</t>
+        </is>
+      </c>
+      <c r="E1117" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F1117" s="4" t="inlineStr">
+        <is>
+          <t>Charlotte, NC</t>
+        </is>
+      </c>
+      <c r="G1117" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H1117" s="5" t="inlineStr">
+        <is>
+          <t>Division of University Advancement.</t>
+        </is>
+      </c>
+      <c r="I1117" s="4" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
+      <c r="J1117" s="4" t="inlineStr">
         <is>
           <t>Tanisha Sewell</t>
         </is>
@@ -29611,52 +31267,52 @@
       </c>
     </row>
     <row r="1133">
-      <c r="A1133" s="6" t="inlineStr">
+      <c r="A1133" s="4" t="inlineStr">
         <is>
           <t>Thaddeus</t>
         </is>
       </c>
-      <c r="B1133" s="6" t="inlineStr">
+      <c r="B1133" s="4" t="inlineStr">
         <is>
           <t>Figlock</t>
         </is>
       </c>
-      <c r="C1133" s="6" t="inlineStr">
+      <c r="C1133" s="4" t="inlineStr">
         <is>
           <t>PRIDE</t>
         </is>
       </c>
-      <c r="D1133" s="6" t="inlineStr">
+      <c r="D1133" s="4" t="inlineStr">
         <is>
           <t>Director, Human Resources</t>
         </is>
       </c>
-      <c r="E1133" s="6" t="inlineStr">
+      <c r="E1133" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F1133" s="6" t="inlineStr">
+      <c r="F1133" s="4" t="inlineStr">
         <is>
           <t>Providence, RI</t>
         </is>
       </c>
-      <c r="G1133" s="6" t="inlineStr">
+      <c r="G1133" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H1133" s="7" t="inlineStr">
+      <c r="H1133" s="5" t="inlineStr">
         <is>
           <t>SHRM MA State Council; Suicide Prevention Task Force steering cmte. Prior interim HR, Nelipak Healthcare Packaging.</t>
         </is>
       </c>
-      <c r="I1133" s="6" t="inlineStr">
+      <c r="I1133" s="4" t="inlineStr">
         <is>
           <t>Web research</t>
         </is>
       </c>
-      <c r="J1133" s="6" t="inlineStr">
+      <c r="J1133" s="4" t="inlineStr">
         <is>
           <t>Thaddeus Figlock</t>
         </is>
@@ -29783,24 +31439,52 @@
       </c>
     </row>
     <row r="1139">
-      <c r="A1139" s="2" t="inlineStr">
+      <c r="A1139" s="4" t="inlineStr">
         <is>
           <t>Utamu</t>
         </is>
       </c>
-      <c r="B1139" s="2" t="inlineStr">
+      <c r="B1139" s="4" t="inlineStr">
         <is>
           <t>Lackey</t>
         </is>
       </c>
-      <c r="C1139" s="2" t="inlineStr"/>
-      <c r="D1139" s="2" t="inlineStr"/>
-      <c r="E1139" s="2" t="inlineStr"/>
-      <c r="F1139" s="2" t="inlineStr"/>
-      <c r="G1139" s="2" t="inlineStr"/>
-      <c r="H1139" s="3" t="inlineStr"/>
-      <c r="I1139" s="2" t="inlineStr"/>
-      <c r="J1139" s="2" t="inlineStr">
+      <c r="C1139" s="4" t="inlineStr">
+        <is>
+          <t>AdventHealth</t>
+        </is>
+      </c>
+      <c r="D1139" s="4" t="inlineStr">
+        <is>
+          <t>Director, HR Business Partner</t>
+        </is>
+      </c>
+      <c r="E1139" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F1139" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G1139" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H1139" s="5" t="inlineStr">
+        <is>
+          <t>Large non-profit health system.</t>
+        </is>
+      </c>
+      <c r="I1139" s="4" t="inlineStr">
+        <is>
+          <t>Web research</t>
+        </is>
+      </c>
+      <c r="J1139" s="4" t="inlineStr">
         <is>
           <t>Utamu Lackey</t>
         </is>
@@ -29855,48 +31539,48 @@
       </c>
     </row>
     <row r="1142">
-      <c r="A1142" s="6" t="inlineStr">
+      <c r="A1142" s="4" t="inlineStr">
         <is>
           <t>Vanessa</t>
         </is>
       </c>
-      <c r="B1142" s="6" t="inlineStr">
+      <c r="B1142" s="4" t="inlineStr">
         <is>
           <t>Hoercher</t>
         </is>
       </c>
-      <c r="C1142" s="6" t="inlineStr">
+      <c r="C1142" s="4" t="inlineStr">
         <is>
           <t>Acumen Medical Communications</t>
         </is>
       </c>
-      <c r="D1142" s="6" t="inlineStr">
+      <c r="D1142" s="4" t="inlineStr">
         <is>
           <t>Human Resources (SPHR)</t>
         </is>
       </c>
-      <c r="E1142" s="6" t="inlineStr">
+      <c r="E1142" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F1142" s="6" t="inlineStr">
+      <c r="F1142" s="4" t="inlineStr">
         <is>
           <t>Greater Boston, MA</t>
         </is>
       </c>
-      <c r="G1142" s="6" t="inlineStr">
+      <c r="G1142" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H1142" s="7" t="inlineStr"/>
-      <c r="I1142" s="6" t="inlineStr">
+      <c r="H1142" s="5" t="inlineStr"/>
+      <c r="I1142" s="4" t="inlineStr">
         <is>
           <t>Web research</t>
         </is>
       </c>
-      <c r="J1142" s="6" t="inlineStr">
+      <c r="J1142" s="4" t="inlineStr">
         <is>
           <t>Vanessa Hoercher</t>
         </is>
@@ -29951,52 +31635,52 @@
       </c>
     </row>
     <row r="1145">
-      <c r="A1145" s="6" t="inlineStr">
+      <c r="A1145" s="4" t="inlineStr">
         <is>
           <t>Verlinda</t>
         </is>
       </c>
-      <c r="B1145" s="6" t="inlineStr">
+      <c r="B1145" s="4" t="inlineStr">
         <is>
           <t>Henning</t>
         </is>
       </c>
-      <c r="C1145" s="6" t="inlineStr">
+      <c r="C1145" s="4" t="inlineStr">
         <is>
           <t>Memphis Light, Gas &amp; Water (MLGW)</t>
         </is>
       </c>
-      <c r="D1145" s="6" t="inlineStr">
+      <c r="D1145" s="4" t="inlineStr">
         <is>
           <t>Sr. HR Representative (SPHR, SHRM-SCP)</t>
         </is>
       </c>
-      <c r="E1145" s="6" t="inlineStr">
+      <c r="E1145" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F1145" s="6" t="inlineStr">
+      <c r="F1145" s="4" t="inlineStr">
         <is>
           <t>Memphis, TN</t>
         </is>
       </c>
-      <c r="G1145" s="6" t="inlineStr">
+      <c r="G1145" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H1145" s="7" t="inlineStr">
+      <c r="H1145" s="5" t="inlineStr">
         <is>
           <t>Also runs own HR consultancy for faith-based orgs.</t>
         </is>
       </c>
-      <c r="I1145" s="6" t="inlineStr">
+      <c r="I1145" s="4" t="inlineStr">
         <is>
           <t>Web research</t>
         </is>
       </c>
-      <c r="J1145" s="6" t="inlineStr">
+      <c r="J1145" s="4" t="inlineStr">
         <is>
           <t>Verlinda Henning</t>
         </is>
@@ -30579,52 +32263,52 @@
       </c>
     </row>
     <row r="1170">
-      <c r="A1170" s="6" t="inlineStr">
+      <c r="A1170" s="4" t="inlineStr">
         <is>
           <t>Zipporah</t>
         </is>
       </c>
-      <c r="B1170" s="6" t="inlineStr">
+      <c r="B1170" s="4" t="inlineStr">
         <is>
           <t>Chatman</t>
         </is>
       </c>
-      <c r="C1170" s="6" t="inlineStr">
+      <c r="C1170" s="4" t="inlineStr">
         <is>
           <t>Habitat for Humanity</t>
         </is>
       </c>
-      <c r="D1170" s="6" t="inlineStr">
+      <c r="D1170" s="4" t="inlineStr">
         <is>
           <t>Nonprofit Leadership / Operations</t>
         </is>
       </c>
-      <c r="E1170" s="6" t="inlineStr">
+      <c r="E1170" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F1170" s="6" t="inlineStr">
+      <c r="F1170" s="4" t="inlineStr">
         <is>
           <t>Memphis, TN</t>
         </is>
       </c>
-      <c r="G1170" s="6" t="inlineStr">
+      <c r="G1170" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H1170" s="7" t="inlineStr">
+      <c r="H1170" s="5" t="inlineStr">
         <is>
           <t>Small nonprofit; likely fully insured.</t>
         </is>
       </c>
-      <c r="I1170" s="6" t="inlineStr">
+      <c r="I1170" s="4" t="inlineStr">
         <is>
           <t>Web research</t>
         </is>
       </c>
-      <c r="J1170" s="6" t="inlineStr">
+      <c r="J1170" s="4" t="inlineStr">
         <is>
           <t>Zipporah Chatman</t>
         </is>
